--- a/recipes/Recipe_Template.xlsx
+++ b/recipes/Recipe_Template.xlsx
@@ -208,7 +208,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>단계 번호(1,2,3…). 대기(delay) 행은 비움</t>
+        <t>단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -353,13 +353,13 @@
     <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
-T=DC2 연속 파워 사용</t>
+DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력</t>
       </text>
     </comment>
     <comment ref="AA1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
-DC2 설정 파워(&gt;0)</t>
+DC2 폐지 — 비워 두세요</t>
       </text>
     </comment>
     <comment ref="AB1" authorId="0" shapeId="0">
@@ -420,6 +420,24 @@
       <text>
         <t>단위: %
 정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)</t>
+      </text>
+    </comment>
+    <comment ref="AL1" authorId="0" shapeId="0">
+      <text>
+        <t>단위: T/F
+T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올린 뒤 유지. CH1 은 사용 불가</t>
+      </text>
+    </comment>
+    <comment ref="AM1" authorId="0" shapeId="0">
+      <text>
+        <t>단위: °C
+목표 온도 1~500 (HEATER_MAX_TEMP). use_heater=T 이면 필수</t>
+      </text>
+    </comment>
+    <comment ref="AN1" authorId="0" shapeId="0">
+      <text>
+        <t>단위: °C/min
+승온 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 12)</t>
       </text>
     </comment>
   </commentList>
@@ -715,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK61"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -755,6 +773,9 @@
     <col width="17" customWidth="1" min="35" max="35"/>
     <col width="16" customWidth="1" min="36" max="36"/>
     <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="13" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -941,6 +962,21 @@
       <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_duty_cycle</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>use_heater</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>heater_temp</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>heater_ramp</t>
         </is>
       </c>
     </row>
@@ -990,6 +1026,9 @@
       <c r="AI2" s="2" t="n"/>
       <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n"/>
+      <c r="AL2" s="2" t="n"/>
+      <c r="AM2" s="2" t="n"/>
+      <c r="AN2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -1113,6 +1152,9 @@
       <c r="AI3" s="2" t="n"/>
       <c r="AJ3" s="4" t="n"/>
       <c r="AK3" s="4" t="n"/>
+      <c r="AL3" s="2" t="n"/>
+      <c r="AM3" s="2" t="n"/>
+      <c r="AN3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -1152,6 +1194,9 @@
       <c r="AI4" s="2" t="n"/>
       <c r="AJ4" s="4" t="n"/>
       <c r="AK4" s="4" t="n"/>
+      <c r="AL4" s="2" t="n"/>
+      <c r="AM4" s="2" t="n"/>
+      <c r="AN4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -1191,6 +1236,9 @@
       <c r="AI5" s="2" t="n"/>
       <c r="AJ5" s="4" t="n"/>
       <c r="AK5" s="4" t="n"/>
+      <c r="AL5" s="2" t="n"/>
+      <c r="AM5" s="2" t="n"/>
+      <c r="AN5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -1230,6 +1278,9 @@
       <c r="AI6" s="2" t="n"/>
       <c r="AJ6" s="4" t="n"/>
       <c r="AK6" s="4" t="n"/>
+      <c r="AL6" s="2" t="n"/>
+      <c r="AM6" s="2" t="n"/>
+      <c r="AN6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1269,6 +1320,9 @@
       <c r="AI7" s="2" t="n"/>
       <c r="AJ7" s="4" t="n"/>
       <c r="AK7" s="4" t="n"/>
+      <c r="AL7" s="2" t="n"/>
+      <c r="AM7" s="2" t="n"/>
+      <c r="AN7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1308,6 +1362,9 @@
       <c r="AI8" s="2" t="n"/>
       <c r="AJ8" s="4" t="n"/>
       <c r="AK8" s="4" t="n"/>
+      <c r="AL8" s="2" t="n"/>
+      <c r="AM8" s="2" t="n"/>
+      <c r="AN8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1347,6 +1404,9 @@
       <c r="AI9" s="2" t="n"/>
       <c r="AJ9" s="4" t="n"/>
       <c r="AK9" s="4" t="n"/>
+      <c r="AL9" s="2" t="n"/>
+      <c r="AM9" s="2" t="n"/>
+      <c r="AN9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1386,6 +1446,9 @@
       <c r="AI10" s="2" t="n"/>
       <c r="AJ10" s="4" t="n"/>
       <c r="AK10" s="4" t="n"/>
+      <c r="AL10" s="2" t="n"/>
+      <c r="AM10" s="2" t="n"/>
+      <c r="AN10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1425,6 +1488,9 @@
       <c r="AI11" s="2" t="n"/>
       <c r="AJ11" s="4" t="n"/>
       <c r="AK11" s="4" t="n"/>
+      <c r="AL11" s="2" t="n"/>
+      <c r="AM11" s="2" t="n"/>
+      <c r="AN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1464,6 +1530,9 @@
       <c r="AI12" s="2" t="n"/>
       <c r="AJ12" s="4" t="n"/>
       <c r="AK12" s="4" t="n"/>
+      <c r="AL12" s="2" t="n"/>
+      <c r="AM12" s="2" t="n"/>
+      <c r="AN12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1503,6 +1572,9 @@
       <c r="AI13" s="2" t="n"/>
       <c r="AJ13" s="4" t="n"/>
       <c r="AK13" s="4" t="n"/>
+      <c r="AL13" s="2" t="n"/>
+      <c r="AM13" s="2" t="n"/>
+      <c r="AN13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1542,6 +1614,9 @@
       <c r="AI14" s="2" t="n"/>
       <c r="AJ14" s="4" t="n"/>
       <c r="AK14" s="4" t="n"/>
+      <c r="AL14" s="2" t="n"/>
+      <c r="AM14" s="2" t="n"/>
+      <c r="AN14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1581,6 +1656,9 @@
       <c r="AI15" s="2" t="n"/>
       <c r="AJ15" s="4" t="n"/>
       <c r="AK15" s="4" t="n"/>
+      <c r="AL15" s="2" t="n"/>
+      <c r="AM15" s="2" t="n"/>
+      <c r="AN15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1620,6 +1698,9 @@
       <c r="AI16" s="2" t="n"/>
       <c r="AJ16" s="4" t="n"/>
       <c r="AK16" s="4" t="n"/>
+      <c r="AL16" s="2" t="n"/>
+      <c r="AM16" s="2" t="n"/>
+      <c r="AN16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1659,6 +1740,9 @@
       <c r="AI17" s="2" t="n"/>
       <c r="AJ17" s="4" t="n"/>
       <c r="AK17" s="4" t="n"/>
+      <c r="AL17" s="2" t="n"/>
+      <c r="AM17" s="2" t="n"/>
+      <c r="AN17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1698,6 +1782,9 @@
       <c r="AI18" s="2" t="n"/>
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
+      <c r="AL18" s="2" t="n"/>
+      <c r="AM18" s="2" t="n"/>
+      <c r="AN18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1737,6 +1824,9 @@
       <c r="AI19" s="2" t="n"/>
       <c r="AJ19" s="4" t="n"/>
       <c r="AK19" s="4" t="n"/>
+      <c r="AL19" s="2" t="n"/>
+      <c r="AM19" s="2" t="n"/>
+      <c r="AN19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1776,6 +1866,9 @@
       <c r="AI20" s="2" t="n"/>
       <c r="AJ20" s="4" t="n"/>
       <c r="AK20" s="4" t="n"/>
+      <c r="AL20" s="2" t="n"/>
+      <c r="AM20" s="2" t="n"/>
+      <c r="AN20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1815,6 +1908,9 @@
       <c r="AI21" s="2" t="n"/>
       <c r="AJ21" s="4" t="n"/>
       <c r="AK21" s="4" t="n"/>
+      <c r="AL21" s="2" t="n"/>
+      <c r="AM21" s="2" t="n"/>
+      <c r="AN21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1854,6 +1950,9 @@
       <c r="AI22" s="2" t="n"/>
       <c r="AJ22" s="4" t="n"/>
       <c r="AK22" s="4" t="n"/>
+      <c r="AL22" s="2" t="n"/>
+      <c r="AM22" s="2" t="n"/>
+      <c r="AN22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -1893,6 +1992,9 @@
       <c r="AI23" s="2" t="n"/>
       <c r="AJ23" s="4" t="n"/>
       <c r="AK23" s="4" t="n"/>
+      <c r="AL23" s="2" t="n"/>
+      <c r="AM23" s="2" t="n"/>
+      <c r="AN23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -1932,6 +2034,9 @@
       <c r="AI24" s="2" t="n"/>
       <c r="AJ24" s="4" t="n"/>
       <c r="AK24" s="4" t="n"/>
+      <c r="AL24" s="2" t="n"/>
+      <c r="AM24" s="2" t="n"/>
+      <c r="AN24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1971,6 +2076,9 @@
       <c r="AI25" s="2" t="n"/>
       <c r="AJ25" s="4" t="n"/>
       <c r="AK25" s="4" t="n"/>
+      <c r="AL25" s="2" t="n"/>
+      <c r="AM25" s="2" t="n"/>
+      <c r="AN25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2010,6 +2118,9 @@
       <c r="AI26" s="2" t="n"/>
       <c r="AJ26" s="4" t="n"/>
       <c r="AK26" s="4" t="n"/>
+      <c r="AL26" s="2" t="n"/>
+      <c r="AM26" s="2" t="n"/>
+      <c r="AN26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2049,6 +2160,9 @@
       <c r="AI27" s="2" t="n"/>
       <c r="AJ27" s="4" t="n"/>
       <c r="AK27" s="4" t="n"/>
+      <c r="AL27" s="2" t="n"/>
+      <c r="AM27" s="2" t="n"/>
+      <c r="AN27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2088,6 +2202,9 @@
       <c r="AI28" s="2" t="n"/>
       <c r="AJ28" s="4" t="n"/>
       <c r="AK28" s="4" t="n"/>
+      <c r="AL28" s="2" t="n"/>
+      <c r="AM28" s="2" t="n"/>
+      <c r="AN28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2127,6 +2244,9 @@
       <c r="AI29" s="2" t="n"/>
       <c r="AJ29" s="4" t="n"/>
       <c r="AK29" s="4" t="n"/>
+      <c r="AL29" s="2" t="n"/>
+      <c r="AM29" s="2" t="n"/>
+      <c r="AN29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2166,6 +2286,9 @@
       <c r="AI30" s="2" t="n"/>
       <c r="AJ30" s="4" t="n"/>
       <c r="AK30" s="4" t="n"/>
+      <c r="AL30" s="2" t="n"/>
+      <c r="AM30" s="2" t="n"/>
+      <c r="AN30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2205,6 +2328,9 @@
       <c r="AI31" s="2" t="n"/>
       <c r="AJ31" s="4" t="n"/>
       <c r="AK31" s="4" t="n"/>
+      <c r="AL31" s="2" t="n"/>
+      <c r="AM31" s="2" t="n"/>
+      <c r="AN31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2244,6 +2370,9 @@
       <c r="AI32" s="2" t="n"/>
       <c r="AJ32" s="4" t="n"/>
       <c r="AK32" s="4" t="n"/>
+      <c r="AL32" s="2" t="n"/>
+      <c r="AM32" s="2" t="n"/>
+      <c r="AN32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2283,6 +2412,9 @@
       <c r="AI33" s="2" t="n"/>
       <c r="AJ33" s="4" t="n"/>
       <c r="AK33" s="4" t="n"/>
+      <c r="AL33" s="2" t="n"/>
+      <c r="AM33" s="2" t="n"/>
+      <c r="AN33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2322,6 +2454,9 @@
       <c r="AI34" s="2" t="n"/>
       <c r="AJ34" s="4" t="n"/>
       <c r="AK34" s="4" t="n"/>
+      <c r="AL34" s="2" t="n"/>
+      <c r="AM34" s="2" t="n"/>
+      <c r="AN34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2361,6 +2496,9 @@
       <c r="AI35" s="2" t="n"/>
       <c r="AJ35" s="4" t="n"/>
       <c r="AK35" s="4" t="n"/>
+      <c r="AL35" s="2" t="n"/>
+      <c r="AM35" s="2" t="n"/>
+      <c r="AN35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2400,6 +2538,9 @@
       <c r="AI36" s="2" t="n"/>
       <c r="AJ36" s="4" t="n"/>
       <c r="AK36" s="4" t="n"/>
+      <c r="AL36" s="2" t="n"/>
+      <c r="AM36" s="2" t="n"/>
+      <c r="AN36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -2439,6 +2580,9 @@
       <c r="AI37" s="2" t="n"/>
       <c r="AJ37" s="4" t="n"/>
       <c r="AK37" s="4" t="n"/>
+      <c r="AL37" s="2" t="n"/>
+      <c r="AM37" s="2" t="n"/>
+      <c r="AN37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -2478,6 +2622,9 @@
       <c r="AI38" s="2" t="n"/>
       <c r="AJ38" s="4" t="n"/>
       <c r="AK38" s="4" t="n"/>
+      <c r="AL38" s="2" t="n"/>
+      <c r="AM38" s="2" t="n"/>
+      <c r="AN38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -2517,6 +2664,9 @@
       <c r="AI39" s="2" t="n"/>
       <c r="AJ39" s="4" t="n"/>
       <c r="AK39" s="4" t="n"/>
+      <c r="AL39" s="2" t="n"/>
+      <c r="AM39" s="2" t="n"/>
+      <c r="AN39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2556,6 +2706,9 @@
       <c r="AI40" s="2" t="n"/>
       <c r="AJ40" s="4" t="n"/>
       <c r="AK40" s="4" t="n"/>
+      <c r="AL40" s="2" t="n"/>
+      <c r="AM40" s="2" t="n"/>
+      <c r="AN40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -2595,6 +2748,9 @@
       <c r="AI41" s="2" t="n"/>
       <c r="AJ41" s="4" t="n"/>
       <c r="AK41" s="4" t="n"/>
+      <c r="AL41" s="2" t="n"/>
+      <c r="AM41" s="2" t="n"/>
+      <c r="AN41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2634,6 +2790,9 @@
       <c r="AI42" s="2" t="n"/>
       <c r="AJ42" s="4" t="n"/>
       <c r="AK42" s="4" t="n"/>
+      <c r="AL42" s="2" t="n"/>
+      <c r="AM42" s="2" t="n"/>
+      <c r="AN42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -2673,6 +2832,9 @@
       <c r="AI43" s="2" t="n"/>
       <c r="AJ43" s="4" t="n"/>
       <c r="AK43" s="4" t="n"/>
+      <c r="AL43" s="2" t="n"/>
+      <c r="AM43" s="2" t="n"/>
+      <c r="AN43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2712,6 +2874,9 @@
       <c r="AI44" s="2" t="n"/>
       <c r="AJ44" s="4" t="n"/>
       <c r="AK44" s="4" t="n"/>
+      <c r="AL44" s="2" t="n"/>
+      <c r="AM44" s="2" t="n"/>
+      <c r="AN44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -2751,6 +2916,9 @@
       <c r="AI45" s="2" t="n"/>
       <c r="AJ45" s="4" t="n"/>
       <c r="AK45" s="4" t="n"/>
+      <c r="AL45" s="2" t="n"/>
+      <c r="AM45" s="2" t="n"/>
+      <c r="AN45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -2790,6 +2958,9 @@
       <c r="AI46" s="2" t="n"/>
       <c r="AJ46" s="4" t="n"/>
       <c r="AK46" s="4" t="n"/>
+      <c r="AL46" s="2" t="n"/>
+      <c r="AM46" s="2" t="n"/>
+      <c r="AN46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -2829,6 +3000,9 @@
       <c r="AI47" s="2" t="n"/>
       <c r="AJ47" s="4" t="n"/>
       <c r="AK47" s="4" t="n"/>
+      <c r="AL47" s="2" t="n"/>
+      <c r="AM47" s="2" t="n"/>
+      <c r="AN47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -2868,6 +3042,9 @@
       <c r="AI48" s="2" t="n"/>
       <c r="AJ48" s="4" t="n"/>
       <c r="AK48" s="4" t="n"/>
+      <c r="AL48" s="2" t="n"/>
+      <c r="AM48" s="2" t="n"/>
+      <c r="AN48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -2907,6 +3084,9 @@
       <c r="AI49" s="2" t="n"/>
       <c r="AJ49" s="4" t="n"/>
       <c r="AK49" s="4" t="n"/>
+      <c r="AL49" s="2" t="n"/>
+      <c r="AM49" s="2" t="n"/>
+      <c r="AN49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -2946,6 +3126,9 @@
       <c r="AI50" s="2" t="n"/>
       <c r="AJ50" s="4" t="n"/>
       <c r="AK50" s="4" t="n"/>
+      <c r="AL50" s="2" t="n"/>
+      <c r="AM50" s="2" t="n"/>
+      <c r="AN50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -2985,6 +3168,9 @@
       <c r="AI51" s="2" t="n"/>
       <c r="AJ51" s="4" t="n"/>
       <c r="AK51" s="4" t="n"/>
+      <c r="AL51" s="2" t="n"/>
+      <c r="AM51" s="2" t="n"/>
+      <c r="AN51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -3024,6 +3210,9 @@
       <c r="AI52" s="2" t="n"/>
       <c r="AJ52" s="4" t="n"/>
       <c r="AK52" s="4" t="n"/>
+      <c r="AL52" s="2" t="n"/>
+      <c r="AM52" s="2" t="n"/>
+      <c r="AN52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -3063,6 +3252,9 @@
       <c r="AI53" s="2" t="n"/>
       <c r="AJ53" s="4" t="n"/>
       <c r="AK53" s="4" t="n"/>
+      <c r="AL53" s="2" t="n"/>
+      <c r="AM53" s="2" t="n"/>
+      <c r="AN53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -3102,6 +3294,9 @@
       <c r="AI54" s="2" t="n"/>
       <c r="AJ54" s="4" t="n"/>
       <c r="AK54" s="4" t="n"/>
+      <c r="AL54" s="2" t="n"/>
+      <c r="AM54" s="2" t="n"/>
+      <c r="AN54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -3141,6 +3336,9 @@
       <c r="AI55" s="2" t="n"/>
       <c r="AJ55" s="4" t="n"/>
       <c r="AK55" s="4" t="n"/>
+      <c r="AL55" s="2" t="n"/>
+      <c r="AM55" s="2" t="n"/>
+      <c r="AN55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -3180,6 +3378,9 @@
       <c r="AI56" s="2" t="n"/>
       <c r="AJ56" s="4" t="n"/>
       <c r="AK56" s="4" t="n"/>
+      <c r="AL56" s="2" t="n"/>
+      <c r="AM56" s="2" t="n"/>
+      <c r="AN56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -3219,6 +3420,9 @@
       <c r="AI57" s="2" t="n"/>
       <c r="AJ57" s="4" t="n"/>
       <c r="AK57" s="4" t="n"/>
+      <c r="AL57" s="2" t="n"/>
+      <c r="AM57" s="2" t="n"/>
+      <c r="AN57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -3258,6 +3462,9 @@
       <c r="AI58" s="2" t="n"/>
       <c r="AJ58" s="4" t="n"/>
       <c r="AK58" s="4" t="n"/>
+      <c r="AL58" s="2" t="n"/>
+      <c r="AM58" s="2" t="n"/>
+      <c r="AN58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -3297,6 +3504,9 @@
       <c r="AI59" s="2" t="n"/>
       <c r="AJ59" s="4" t="n"/>
       <c r="AK59" s="4" t="n"/>
+      <c r="AL59" s="2" t="n"/>
+      <c r="AM59" s="2" t="n"/>
+      <c r="AN59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -3336,6 +3546,9 @@
       <c r="AI60" s="2" t="n"/>
       <c r="AJ60" s="4" t="n"/>
       <c r="AK60" s="4" t="n"/>
+      <c r="AL60" s="2" t="n"/>
+      <c r="AM60" s="2" t="n"/>
+      <c r="AN60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -3375,6 +3588,9 @@
       <c r="AI61" s="2" t="n"/>
       <c r="AJ61" s="4" t="n"/>
       <c r="AK61" s="4" t="n"/>
+      <c r="AL61" s="2" t="n"/>
+      <c r="AM61" s="2" t="n"/>
+      <c r="AN61" s="2" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="AG2:AG61">
@@ -3387,10 +3603,9 @@
       <formula>AND(ISNUMBER(AK2),ISNUMBER(AJ2),OR(AK2&lt;1.6*AJ2,AK2&gt;100-1.6*AJ2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="37">
-    <dataValidation sqref="A2:A61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="단계 번호(1,2,3…). 대기(delay) 행은 비움" promptTitle="#" prompt="단계 번호(1,2,3…). 대기(delay) 행은 비움" type="whole" errorStyle="stop" operator="between">
-      <formula1>1</formula1>
-      <formula2>999</formula2>
+  <dataValidations count="40">
+    <dataValidation sqref="A2:A61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행" promptTitle="#" prompt="단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행" type="custom" errorStyle="stop">
+      <formula1>IF(ISNUMBER(A2),AND(A2&gt;=1,A2&lt;=999,A2=INT(A2)),LOWER(A2)="test")</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="공정 이름(로그·챗·CSV에 표시). 대기 행은 '예열 대기' 등 자유" promptTitle="Process_name" prompt="공정 이름(로그·챗·CSV에 표시). 대기 행은 '예열 대기' 등 자유" type="textLength" errorStyle="information" operator="between">
       <formula1>0</formula1>
@@ -3478,10 +3693,10 @@
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="Z2:Z61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=DC2 연속 파워 사용" promptTitle="use_dc_power2 [T/F]" prompt="T=DC2 연속 파워 사용" type="list" errorStyle="stop">
-      <formula1>"T,F"</formula1>
+    <dataValidation sqref="Z2:Z61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" promptTitle="use_dc_power2 [T/F]" prompt="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" type="list" errorStyle="stop">
+      <formula1>"F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA2:AA61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 설정 파워(&gt;0)" promptTitle="dc_power2 [W]" prompt="DC2 설정 파워(&gt;0)" type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="AA2:AA61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 비워 두세요" promptTitle="dc_power2 [W]" prompt="DC2 폐지 — 비워 두세요" type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
@@ -3521,6 +3736,17 @@
       <formula1>1</formula1>
       <formula2>99</formula2>
     </dataValidation>
+    <dataValidation sqref="AL2:AL61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올린 뒤 유지. CH1 은 사용 불가" promptTitle="use_heater [T/F]" prompt="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올린 뒤 유지. CH1 은 사용 불가" type="list" errorStyle="stop">
+      <formula1>"T,F"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AM2:AM61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="목표 온도 1~500 (HEATER_MAX_TEMP). use_heater=T 이면 필수" promptTitle="heater_temp [°C]" prompt="목표 온도 1~500 (HEATER_MAX_TEMP). use_heater=T 이면 필수" type="decimal" errorStyle="stop" operator="between">
+      <formula1>1</formula1>
+      <formula2>500</formula2>
+    </dataValidation>
+    <dataValidation sqref="AN2:AN61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="승온 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 12)" promptTitle="heater_ramp [°C/min]" prompt="승온 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 12)" type="decimal" errorStyle="stop" operator="between">
+      <formula1>0.1</formula1>
+      <formula2>60</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -3533,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3587,10 +3813,14 @@
       <c r="B5" s="8" t="inlineStr"/>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>단계 번호(1,2,3…). 대기(delay) 행은 비움</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr"/>
+          <t>단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>test 행은 장비를 쓰지 않는다(로봇·큐 동작 시험용)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -4025,10 +4255,14 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>T=DC2 연속 파워 사용</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr"/>
+          <t>DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10 CH2 히터 추가로 D/A CH3 를 히터가 씀</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -4043,7 +4277,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>DC2 설정 파워(&gt;0)</t>
+          <t>DC2 폐지 — 비워 두세요</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
@@ -4237,6 +4471,72 @@
       <c r="D41" s="8" t="inlineStr">
         <is>
           <t>범위 밖이면 장비가 CSR 51로 거부함</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>use_heater</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올린 뒤 유지. CH1 은 사용 불가</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>다음 공정 행도 use_heater=T 면 히터를 켠 채 넘어가고, 아니면 공정이 끝날 때 끈다</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>heater_temp</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>목표 온도 1~500 (HEATER_MAX_TEMP). use_heater=T 이면 필수</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>목표 ±2°C 안에 60초 머물면 준비 완료로 보고 공정을 시작(HEATER_SOAK_*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>heater_ramp</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>°C/min</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>승온 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 12)</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>목표 20°C 앞부터 감속해 1°C/min 로 도착(HEATER_APPROACH_*)</t>
         </is>
       </c>
     </row>

--- a/recipes/Recipe_Template.xlsx
+++ b/recipes/Recipe_Template.xlsx
@@ -441,7 +441,7 @@
     <comment ref="AL1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
-T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
+T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
       </text>
     </comment>
     <comment ref="AM1" authorId="0" shapeId="0">
@@ -459,7 +459,7 @@
     <comment ref="AO1" authorId="0" shapeId="0">
       <text>
         <t>단위: min
-도달 후 SOAK 0~480분 — 목표 ±2°C(HEATER_SOAK_TOLERANCE) 안에 이만큼 연속으로 머물면 공정 시작. 공란 = 기본값(HEATER_SOAK_TIME_SEC, 60초)</t>
+도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)</t>
       </text>
     </comment>
   </commentList>
@@ -3812,7 +3812,7 @@
       <formula1>1</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation sqref="AL2:AL61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" promptTitle="use_heater [T/F]" prompt="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" type="list">
+    <dataValidation sqref="AL2:AL61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" promptTitle="use_heater [T/F]" prompt="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
     <dataValidation sqref="AM2:AM61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" promptTitle="heater_temp [°C]" prompt="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" type="decimal">
@@ -3823,7 +3823,7 @@
       <formula1>0.1</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation sqref="AO2:AO61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="도달 후 SOAK 0~480분 — 목표 ±2°C(HEATER_SOAK_TOLERANCE) 안에 이만큼 연속으로 머물면 공정 시작. 공란 = 기본값(HEATER_SOAK_TIME_SEC, 60초)" promptTitle="heater_soak [min]" prompt="도달 후 SOAK 0~480분 — 목표 ±2°C(HEATER_SOAK_TOLERANCE) 안에 이만큼 연속으로 머물면 공정 시작. 공란 = 기본값(HEATER_SOAK_TIME_SEC, 60초)" type="decimal">
+    <dataValidation sqref="AO2:AO61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" promptTitle="heater_soak [min]" prompt="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" type="decimal">
       <formula1>0</formula1>
       <formula2>480</formula2>
     </dataValidation>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
+          <t>T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>도달 후 대기 시간은 heater_soak</t>
+          <t>목표 ±2°C 안에 60초 머물면 도달로 본다(HEATER_SOAK_*). 그 뒤 대기는 heater_soak</t>
         </is>
       </c>
     </row>
@@ -4633,12 +4633,12 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>도달 후 SOAK 0~480분 — 목표 ±2°C(HEATER_SOAK_TOLERANCE) 안에 이만큼 연속으로 머물면 공정 시작. 공란 = 기본값(HEATER_SOAK_TIME_SEC, 60초)</t>
+          <t>도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>±2°C 를 벗어나면 처음부터 다시 셈. 행마다 따로 적용(공란 행은 기본값). 대기 한도(E831) = 예상 RAMP + SOAK + 30분</t>
+          <t>SOAK 중에도 히터 이상·꺼짐·출력 무응답/끊김이면 공정 중단. ±2°C 밖으로 나가면 로그·도달 카드에 기록만. 행마다 따로 적용</t>
         </is>
       </c>
     </row>

--- a/recipes/Recipe_Template.xlsx
+++ b/recipes/Recipe_Template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -46,11 +46,6 @@
       <family val="3"/>
       <sz val="8"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -98,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -121,9 +116,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -317,146 +309,169 @@
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
+        <t>단위: nm/s
+증착률(&gt;0). thickness 를 쓰면 필수 — Thickness 모드 예상시간·안전 상한·시간 대체 계산용, Time 모드는 process_time 이 비었을 때 thickness÷dep_rate 로 시간을 계산</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>단위: nm
+목표 두께(&gt;0). CH2 두께 모니터가 켜져 있으면 Thickness 모드 — 목표 두께에 닿으면 메인 공정 종료(process_time 이 비었으면 thickness÷dep_rate 를 예상시간으로 자동 계산). 건 1개만, chuck×건 Factor 필요. CH1·모니터 없음은 지금처럼 thickness÷dep_rate 시간 종료</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
         <t>단위: T/F
 T=G1 사용</t>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=G2 사용</t>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=G3 사용</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>G1 타겟 이름(재고 DB 이름과 동일하게)</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>G2 타겟 이름</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>G3 타겟 이름</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=DC1 연속 파워 사용</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 DC1 설정 파워(&gt;0)</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AB1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 DC2 폐지 — 비워 두세요</t>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=RF 연속 파워 사용</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 RF 설정 파워(&gt;0)</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AF1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)</t>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>단위: kHz
 정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AI1" authorId="0" shapeId="0">
       <text>
         <t>단위: us
 Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지</t>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨</t>
       </text>
     </comment>
-    <comment ref="AI1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 RF Pulse 설정 파워 1~1000</t>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0" shapeId="0">
+    <comment ref="AL1" authorId="0" shapeId="0">
       <text>
         <t>단위: kHz
 0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지</t>
       </text>
     </comment>
-    <comment ref="AK1" authorId="0" shapeId="0">
+    <comment ref="AM1" authorId="0" shapeId="0">
       <text>
         <t>단위: %
 정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)</t>
       </text>
     </comment>
-    <comment ref="AL1" authorId="0" shapeId="0">
+    <comment ref="AN1" authorId="0" shapeId="0">
+      <text>
+        <t>중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)</t>
+      </text>
+    </comment>
+    <comment ref="AO1" authorId="0" shapeId="0">
+      <text>
+        <t>단위: W
+그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용</t>
+      </text>
+    </comment>
+    <comment ref="AP1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
       </text>
     </comment>
-    <comment ref="AM1" authorId="0" shapeId="0">
+    <comment ref="AQ1" authorId="0" shapeId="0">
       <text>
         <t>단위: °C
 목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수</t>
       </text>
     </comment>
-    <comment ref="AN1" authorId="0" shapeId="0">
+    <comment ref="AR1" authorId="0" shapeId="0">
       <text>
         <t>단위: °C/min
 RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)</t>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0">
+    <comment ref="AS1" authorId="0" shapeId="0">
       <text>
         <t>단위: min
 도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)</t>
@@ -755,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO61"/>
+  <dimension ref="A1:AS60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="9" min="1" max="1"/>
@@ -764,29 +779,45 @@
     <col width="17" customWidth="1" style="9" min="4" max="4"/>
     <col width="15" customWidth="1" style="9" min="5" max="5"/>
     <col width="19" customWidth="1" style="9" min="6" max="6"/>
-    <col width="9" customWidth="1" style="9" min="7" max="9"/>
-    <col width="10" customWidth="1" style="9" min="10" max="12"/>
+    <col width="9" customWidth="1" style="9" min="7" max="7"/>
+    <col width="9" customWidth="1" style="9" min="8" max="8"/>
+    <col width="9" customWidth="1" style="9" min="9" max="9"/>
+    <col width="10" customWidth="1" style="9" min="10" max="10"/>
+    <col width="10" customWidth="1" style="9" min="11" max="11"/>
+    <col width="10" customWidth="1" style="9" min="12" max="12"/>
     <col width="16" customWidth="1" style="9" min="13" max="13"/>
     <col width="19" customWidth="1" style="9" min="14" max="14"/>
     <col width="16" customWidth="1" style="9" min="15" max="15"/>
     <col width="15" customWidth="1" style="9" min="16" max="16"/>
-    <col width="9" customWidth="1" style="9" min="17" max="19"/>
-    <col width="12" customWidth="1" style="9" min="20" max="22"/>
-    <col width="15" customWidth="1" style="9" min="23" max="24"/>
-    <col width="11" customWidth="1" style="9" min="25" max="25"/>
-    <col width="16" customWidth="1" style="9" min="26" max="26"/>
-    <col width="12" customWidth="1" style="9" min="27" max="27"/>
-    <col width="15" customWidth="1" style="9" min="28" max="28"/>
-    <col width="11" customWidth="1" style="9" min="29" max="29"/>
+    <col width="15" customWidth="1" style="9" min="17" max="17"/>
+    <col width="15" customWidth="1" style="9" min="18" max="18"/>
+    <col width="9" customWidth="1" style="9" min="19" max="19"/>
+    <col width="9" customWidth="1" style="9" min="20" max="20"/>
+    <col width="9" customWidth="1" style="9" min="21" max="21"/>
+    <col width="12" customWidth="1" style="9" min="22" max="22"/>
+    <col width="12" customWidth="1" style="9" min="23" max="23"/>
+    <col width="12" customWidth="1" style="9" min="24" max="24"/>
+    <col width="15" customWidth="1" style="9" min="25" max="25"/>
+    <col width="15" customWidth="1" style="9" min="26" max="26"/>
+    <col width="11" customWidth="1" style="9" min="27" max="27"/>
+    <col width="16" customWidth="1" style="9" min="28" max="28"/>
+    <col width="12" customWidth="1" style="9" min="29" max="29"/>
     <col width="15" customWidth="1" style="9" min="30" max="30"/>
-    <col width="17" customWidth="1" style="9" min="31" max="31"/>
-    <col width="16" customWidth="1" style="9" min="32" max="32"/>
-    <col width="20" customWidth="1" style="9" min="33" max="33"/>
-    <col width="15" customWidth="1" style="9" min="34" max="34"/>
-    <col width="17" customWidth="1" style="9" min="35" max="35"/>
-    <col width="16" customWidth="1" style="9" min="36" max="36"/>
-    <col width="22" customWidth="1" style="9" min="37" max="37"/>
-    <col width="13" customWidth="1" style="9" min="38" max="41"/>
+    <col width="11" customWidth="1" style="9" min="31" max="31"/>
+    <col width="15" customWidth="1" style="9" min="32" max="32"/>
+    <col width="17" customWidth="1" style="9" min="33" max="33"/>
+    <col width="16" customWidth="1" style="9" min="34" max="34"/>
+    <col width="20" customWidth="1" style="9" min="35" max="35"/>
+    <col width="15" customWidth="1" style="9" min="36" max="36"/>
+    <col width="17" customWidth="1" style="9" min="37" max="37"/>
+    <col width="16" customWidth="1" style="9" min="38" max="38"/>
+    <col width="22" customWidth="1" style="9" min="39" max="39"/>
+    <col width="22" customWidth="1" style="9" min="40" max="40"/>
+    <col width="22" customWidth="1" style="9" min="41" max="41"/>
+    <col width="13" customWidth="1" style="9" min="42" max="42"/>
+    <col width="13" customWidth="1" style="9" min="43" max="43"/>
+    <col width="13" customWidth="1" style="9" min="44" max="44"/>
+    <col width="13" customWidth="1" style="9" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" s="9">
@@ -872,307 +903,337 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>dep_rate</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>thickness</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>gun1</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>gun2</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>gun3</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>G1 Target</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>G2 Target</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>G3 Target</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>power_select</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>use_dc_power</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dc_power</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>use_dc_power2</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dc_power2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>use_rf_power</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>rf_power</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>use_dc_pulse</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dc_pulse_power</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dc_pulse_freq</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dc_pulse_off_time</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>use_rf_pulse</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_power</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_freq</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_duty_cycle</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>power_change_time</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>change_power_value</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>use_heater</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>heater_temp</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>heater_ramp</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>heater_soak</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>delay</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>20m</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>예시_공정명</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>7e-06</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>350</v>
+      </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="n"/>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="V2" s="2" t="n"/>
       <c r="W2" s="2" t="n"/>
       <c r="X2" s="2" t="n"/>
-      <c r="Y2" s="2" t="n"/>
-      <c r="Z2" s="2" t="n"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AA2" s="2" t="n"/>
-      <c r="AB2" s="2" t="n"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="n"/>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AE2" s="2" t="n"/>
-      <c r="AF2" s="4" t="n"/>
-      <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="2" t="n"/>
-      <c r="AI2" s="2" t="n"/>
-      <c r="AJ2" s="4" t="n"/>
-      <c r="AK2" s="4" t="n"/>
-      <c r="AL2" s="2" t="n"/>
-      <c r="AM2" s="2" t="n"/>
-      <c r="AN2" s="2" t="n"/>
-      <c r="AO2" s="2" t="n"/>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH2" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="n"/>
+      <c r="AL2" s="4" t="n"/>
+      <c r="AM2" s="4" t="n"/>
+      <c r="AN2" s="4" t="n"/>
+      <c r="AO2" s="4" t="n"/>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AR2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS2" s="2" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>예시_공정명</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>down</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>7e-06</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
       <c r="T3" s="2" t="n"/>
       <c r="U3" s="2" t="n"/>
       <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="W3" s="2" t="n"/>
+      <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="n"/>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="Z3" s="2" t="n"/>
       <c r="AA3" s="2" t="n"/>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="AB3" s="2" t="n"/>
       <c r="AC3" s="2" t="n"/>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF3" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="AI3" s="2" t="n"/>
-      <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="4" t="n"/>
-      <c r="AL3" s="2" t="n"/>
-      <c r="AM3" s="2" t="n"/>
-      <c r="AN3" s="2" t="n"/>
-      <c r="AO3" s="2" t="n"/>
+      <c r="AD3" s="2" t="n"/>
+      <c r="AE3" s="2" t="n"/>
+      <c r="AF3" s="2" t="n"/>
+      <c r="AG3" s="2" t="n"/>
+      <c r="AH3" s="4" t="n"/>
+      <c r="AI3" s="4" t="n"/>
+      <c r="AJ3" s="2" t="n"/>
+      <c r="AK3" s="2" t="n"/>
+      <c r="AL3" s="4" t="n"/>
+      <c r="AM3" s="4" t="n"/>
+      <c r="AN3" s="4" t="n"/>
+      <c r="AO3" s="4" t="n"/>
+      <c r="AP3" s="2" t="n"/>
+      <c r="AQ3" s="2" t="n"/>
+      <c r="AR3" s="2" t="n"/>
+      <c r="AS3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -1206,16 +1267,20 @@
       <c r="AC4" s="2" t="n"/>
       <c r="AD4" s="2" t="n"/>
       <c r="AE4" s="2" t="n"/>
-      <c r="AF4" s="4" t="n"/>
-      <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="2" t="n"/>
-      <c r="AI4" s="2" t="n"/>
-      <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="4" t="n"/>
-      <c r="AL4" s="2" t="n"/>
-      <c r="AM4" s="2" t="n"/>
-      <c r="AN4" s="2" t="n"/>
-      <c r="AO4" s="2" t="n"/>
+      <c r="AF4" s="2" t="n"/>
+      <c r="AG4" s="2" t="n"/>
+      <c r="AH4" s="4" t="n"/>
+      <c r="AI4" s="4" t="n"/>
+      <c r="AJ4" s="2" t="n"/>
+      <c r="AK4" s="2" t="n"/>
+      <c r="AL4" s="4" t="n"/>
+      <c r="AM4" s="4" t="n"/>
+      <c r="AN4" s="4" t="n"/>
+      <c r="AO4" s="4" t="n"/>
+      <c r="AP4" s="2" t="n"/>
+      <c r="AQ4" s="2" t="n"/>
+      <c r="AR4" s="2" t="n"/>
+      <c r="AS4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -1249,16 +1314,20 @@
       <c r="AC5" s="2" t="n"/>
       <c r="AD5" s="2" t="n"/>
       <c r="AE5" s="2" t="n"/>
-      <c r="AF5" s="4" t="n"/>
-      <c r="AG5" s="4" t="n"/>
-      <c r="AH5" s="2" t="n"/>
-      <c r="AI5" s="2" t="n"/>
-      <c r="AJ5" s="4" t="n"/>
-      <c r="AK5" s="4" t="n"/>
-      <c r="AL5" s="2" t="n"/>
-      <c r="AM5" s="2" t="n"/>
-      <c r="AN5" s="2" t="n"/>
-      <c r="AO5" s="2" t="n"/>
+      <c r="AF5" s="2" t="n"/>
+      <c r="AG5" s="2" t="n"/>
+      <c r="AH5" s="4" t="n"/>
+      <c r="AI5" s="4" t="n"/>
+      <c r="AJ5" s="2" t="n"/>
+      <c r="AK5" s="2" t="n"/>
+      <c r="AL5" s="4" t="n"/>
+      <c r="AM5" s="4" t="n"/>
+      <c r="AN5" s="4" t="n"/>
+      <c r="AO5" s="4" t="n"/>
+      <c r="AP5" s="2" t="n"/>
+      <c r="AQ5" s="2" t="n"/>
+      <c r="AR5" s="2" t="n"/>
+      <c r="AS5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -1292,16 +1361,20 @@
       <c r="AC6" s="2" t="n"/>
       <c r="AD6" s="2" t="n"/>
       <c r="AE6" s="2" t="n"/>
-      <c r="AF6" s="4" t="n"/>
-      <c r="AG6" s="4" t="n"/>
-      <c r="AH6" s="2" t="n"/>
-      <c r="AI6" s="2" t="n"/>
-      <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="4" t="n"/>
-      <c r="AL6" s="2" t="n"/>
-      <c r="AM6" s="2" t="n"/>
-      <c r="AN6" s="2" t="n"/>
-      <c r="AO6" s="2" t="n"/>
+      <c r="AF6" s="2" t="n"/>
+      <c r="AG6" s="2" t="n"/>
+      <c r="AH6" s="4" t="n"/>
+      <c r="AI6" s="4" t="n"/>
+      <c r="AJ6" s="2" t="n"/>
+      <c r="AK6" s="2" t="n"/>
+      <c r="AL6" s="4" t="n"/>
+      <c r="AM6" s="4" t="n"/>
+      <c r="AN6" s="4" t="n"/>
+      <c r="AO6" s="4" t="n"/>
+      <c r="AP6" s="2" t="n"/>
+      <c r="AQ6" s="2" t="n"/>
+      <c r="AR6" s="2" t="n"/>
+      <c r="AS6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1335,16 +1408,20 @@
       <c r="AC7" s="2" t="n"/>
       <c r="AD7" s="2" t="n"/>
       <c r="AE7" s="2" t="n"/>
-      <c r="AF7" s="4" t="n"/>
-      <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="2" t="n"/>
-      <c r="AI7" s="2" t="n"/>
-      <c r="AJ7" s="4" t="n"/>
-      <c r="AK7" s="4" t="n"/>
-      <c r="AL7" s="2" t="n"/>
-      <c r="AM7" s="2" t="n"/>
-      <c r="AN7" s="2" t="n"/>
-      <c r="AO7" s="2" t="n"/>
+      <c r="AF7" s="2" t="n"/>
+      <c r="AG7" s="2" t="n"/>
+      <c r="AH7" s="4" t="n"/>
+      <c r="AI7" s="4" t="n"/>
+      <c r="AJ7" s="2" t="n"/>
+      <c r="AK7" s="2" t="n"/>
+      <c r="AL7" s="4" t="n"/>
+      <c r="AM7" s="4" t="n"/>
+      <c r="AN7" s="4" t="n"/>
+      <c r="AO7" s="4" t="n"/>
+      <c r="AP7" s="2" t="n"/>
+      <c r="AQ7" s="2" t="n"/>
+      <c r="AR7" s="2" t="n"/>
+      <c r="AS7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1378,16 +1455,20 @@
       <c r="AC8" s="2" t="n"/>
       <c r="AD8" s="2" t="n"/>
       <c r="AE8" s="2" t="n"/>
-      <c r="AF8" s="4" t="n"/>
-      <c r="AG8" s="4" t="n"/>
-      <c r="AH8" s="2" t="n"/>
-      <c r="AI8" s="2" t="n"/>
-      <c r="AJ8" s="4" t="n"/>
-      <c r="AK8" s="4" t="n"/>
-      <c r="AL8" s="2" t="n"/>
-      <c r="AM8" s="2" t="n"/>
-      <c r="AN8" s="2" t="n"/>
-      <c r="AO8" s="2" t="n"/>
+      <c r="AF8" s="2" t="n"/>
+      <c r="AG8" s="2" t="n"/>
+      <c r="AH8" s="4" t="n"/>
+      <c r="AI8" s="4" t="n"/>
+      <c r="AJ8" s="2" t="n"/>
+      <c r="AK8" s="2" t="n"/>
+      <c r="AL8" s="4" t="n"/>
+      <c r="AM8" s="4" t="n"/>
+      <c r="AN8" s="4" t="n"/>
+      <c r="AO8" s="4" t="n"/>
+      <c r="AP8" s="2" t="n"/>
+      <c r="AQ8" s="2" t="n"/>
+      <c r="AR8" s="2" t="n"/>
+      <c r="AS8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1421,16 +1502,20 @@
       <c r="AC9" s="2" t="n"/>
       <c r="AD9" s="2" t="n"/>
       <c r="AE9" s="2" t="n"/>
-      <c r="AF9" s="4" t="n"/>
-      <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="2" t="n"/>
-      <c r="AI9" s="2" t="n"/>
-      <c r="AJ9" s="4" t="n"/>
-      <c r="AK9" s="4" t="n"/>
-      <c r="AL9" s="2" t="n"/>
-      <c r="AM9" s="2" t="n"/>
-      <c r="AN9" s="2" t="n"/>
-      <c r="AO9" s="2" t="n"/>
+      <c r="AF9" s="2" t="n"/>
+      <c r="AG9" s="2" t="n"/>
+      <c r="AH9" s="4" t="n"/>
+      <c r="AI9" s="4" t="n"/>
+      <c r="AJ9" s="2" t="n"/>
+      <c r="AK9" s="2" t="n"/>
+      <c r="AL9" s="4" t="n"/>
+      <c r="AM9" s="4" t="n"/>
+      <c r="AN9" s="4" t="n"/>
+      <c r="AO9" s="4" t="n"/>
+      <c r="AP9" s="2" t="n"/>
+      <c r="AQ9" s="2" t="n"/>
+      <c r="AR9" s="2" t="n"/>
+      <c r="AS9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1464,16 +1549,20 @@
       <c r="AC10" s="2" t="n"/>
       <c r="AD10" s="2" t="n"/>
       <c r="AE10" s="2" t="n"/>
-      <c r="AF10" s="4" t="n"/>
-      <c r="AG10" s="4" t="n"/>
-      <c r="AH10" s="2" t="n"/>
-      <c r="AI10" s="2" t="n"/>
-      <c r="AJ10" s="4" t="n"/>
-      <c r="AK10" s="4" t="n"/>
-      <c r="AL10" s="2" t="n"/>
-      <c r="AM10" s="2" t="n"/>
-      <c r="AN10" s="2" t="n"/>
-      <c r="AO10" s="2" t="n"/>
+      <c r="AF10" s="2" t="n"/>
+      <c r="AG10" s="2" t="n"/>
+      <c r="AH10" s="4" t="n"/>
+      <c r="AI10" s="4" t="n"/>
+      <c r="AJ10" s="2" t="n"/>
+      <c r="AK10" s="2" t="n"/>
+      <c r="AL10" s="4" t="n"/>
+      <c r="AM10" s="4" t="n"/>
+      <c r="AN10" s="4" t="n"/>
+      <c r="AO10" s="4" t="n"/>
+      <c r="AP10" s="2" t="n"/>
+      <c r="AQ10" s="2" t="n"/>
+      <c r="AR10" s="2" t="n"/>
+      <c r="AS10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1507,16 +1596,20 @@
       <c r="AC11" s="2" t="n"/>
       <c r="AD11" s="2" t="n"/>
       <c r="AE11" s="2" t="n"/>
-      <c r="AF11" s="4" t="n"/>
-      <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="2" t="n"/>
-      <c r="AI11" s="2" t="n"/>
-      <c r="AJ11" s="4" t="n"/>
-      <c r="AK11" s="4" t="n"/>
-      <c r="AL11" s="2" t="n"/>
-      <c r="AM11" s="2" t="n"/>
-      <c r="AN11" s="2" t="n"/>
-      <c r="AO11" s="2" t="n"/>
+      <c r="AF11" s="2" t="n"/>
+      <c r="AG11" s="2" t="n"/>
+      <c r="AH11" s="4" t="n"/>
+      <c r="AI11" s="4" t="n"/>
+      <c r="AJ11" s="2" t="n"/>
+      <c r="AK11" s="2" t="n"/>
+      <c r="AL11" s="4" t="n"/>
+      <c r="AM11" s="4" t="n"/>
+      <c r="AN11" s="4" t="n"/>
+      <c r="AO11" s="4" t="n"/>
+      <c r="AP11" s="2" t="n"/>
+      <c r="AQ11" s="2" t="n"/>
+      <c r="AR11" s="2" t="n"/>
+      <c r="AS11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1550,16 +1643,20 @@
       <c r="AC12" s="2" t="n"/>
       <c r="AD12" s="2" t="n"/>
       <c r="AE12" s="2" t="n"/>
-      <c r="AF12" s="4" t="n"/>
-      <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="2" t="n"/>
-      <c r="AI12" s="2" t="n"/>
-      <c r="AJ12" s="4" t="n"/>
-      <c r="AK12" s="4" t="n"/>
-      <c r="AL12" s="2" t="n"/>
-      <c r="AM12" s="2" t="n"/>
-      <c r="AN12" s="2" t="n"/>
-      <c r="AO12" s="2" t="n"/>
+      <c r="AF12" s="2" t="n"/>
+      <c r="AG12" s="2" t="n"/>
+      <c r="AH12" s="4" t="n"/>
+      <c r="AI12" s="4" t="n"/>
+      <c r="AJ12" s="2" t="n"/>
+      <c r="AK12" s="2" t="n"/>
+      <c r="AL12" s="4" t="n"/>
+      <c r="AM12" s="4" t="n"/>
+      <c r="AN12" s="4" t="n"/>
+      <c r="AO12" s="4" t="n"/>
+      <c r="AP12" s="2" t="n"/>
+      <c r="AQ12" s="2" t="n"/>
+      <c r="AR12" s="2" t="n"/>
+      <c r="AS12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1593,16 +1690,20 @@
       <c r="AC13" s="2" t="n"/>
       <c r="AD13" s="2" t="n"/>
       <c r="AE13" s="2" t="n"/>
-      <c r="AF13" s="4" t="n"/>
-      <c r="AG13" s="4" t="n"/>
-      <c r="AH13" s="2" t="n"/>
-      <c r="AI13" s="2" t="n"/>
-      <c r="AJ13" s="4" t="n"/>
-      <c r="AK13" s="4" t="n"/>
-      <c r="AL13" s="2" t="n"/>
-      <c r="AM13" s="2" t="n"/>
-      <c r="AN13" s="2" t="n"/>
-      <c r="AO13" s="2" t="n"/>
+      <c r="AF13" s="2" t="n"/>
+      <c r="AG13" s="2" t="n"/>
+      <c r="AH13" s="4" t="n"/>
+      <c r="AI13" s="4" t="n"/>
+      <c r="AJ13" s="2" t="n"/>
+      <c r="AK13" s="2" t="n"/>
+      <c r="AL13" s="4" t="n"/>
+      <c r="AM13" s="4" t="n"/>
+      <c r="AN13" s="4" t="n"/>
+      <c r="AO13" s="4" t="n"/>
+      <c r="AP13" s="2" t="n"/>
+      <c r="AQ13" s="2" t="n"/>
+      <c r="AR13" s="2" t="n"/>
+      <c r="AS13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1636,16 +1737,20 @@
       <c r="AC14" s="2" t="n"/>
       <c r="AD14" s="2" t="n"/>
       <c r="AE14" s="2" t="n"/>
-      <c r="AF14" s="4" t="n"/>
-      <c r="AG14" s="4" t="n"/>
-      <c r="AH14" s="2" t="n"/>
-      <c r="AI14" s="2" t="n"/>
-      <c r="AJ14" s="4" t="n"/>
-      <c r="AK14" s="4" t="n"/>
-      <c r="AL14" s="2" t="n"/>
-      <c r="AM14" s="2" t="n"/>
-      <c r="AN14" s="2" t="n"/>
-      <c r="AO14" s="2" t="n"/>
+      <c r="AF14" s="2" t="n"/>
+      <c r="AG14" s="2" t="n"/>
+      <c r="AH14" s="4" t="n"/>
+      <c r="AI14" s="4" t="n"/>
+      <c r="AJ14" s="2" t="n"/>
+      <c r="AK14" s="2" t="n"/>
+      <c r="AL14" s="4" t="n"/>
+      <c r="AM14" s="4" t="n"/>
+      <c r="AN14" s="4" t="n"/>
+      <c r="AO14" s="4" t="n"/>
+      <c r="AP14" s="2" t="n"/>
+      <c r="AQ14" s="2" t="n"/>
+      <c r="AR14" s="2" t="n"/>
+      <c r="AS14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1679,16 +1784,20 @@
       <c r="AC15" s="2" t="n"/>
       <c r="AD15" s="2" t="n"/>
       <c r="AE15" s="2" t="n"/>
-      <c r="AF15" s="4" t="n"/>
-      <c r="AG15" s="4" t="n"/>
-      <c r="AH15" s="2" t="n"/>
-      <c r="AI15" s="2" t="n"/>
-      <c r="AJ15" s="4" t="n"/>
-      <c r="AK15" s="4" t="n"/>
-      <c r="AL15" s="2" t="n"/>
-      <c r="AM15" s="2" t="n"/>
-      <c r="AN15" s="2" t="n"/>
-      <c r="AO15" s="2" t="n"/>
+      <c r="AF15" s="2" t="n"/>
+      <c r="AG15" s="2" t="n"/>
+      <c r="AH15" s="4" t="n"/>
+      <c r="AI15" s="4" t="n"/>
+      <c r="AJ15" s="2" t="n"/>
+      <c r="AK15" s="2" t="n"/>
+      <c r="AL15" s="4" t="n"/>
+      <c r="AM15" s="4" t="n"/>
+      <c r="AN15" s="4" t="n"/>
+      <c r="AO15" s="4" t="n"/>
+      <c r="AP15" s="2" t="n"/>
+      <c r="AQ15" s="2" t="n"/>
+      <c r="AR15" s="2" t="n"/>
+      <c r="AS15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1722,16 +1831,20 @@
       <c r="AC16" s="2" t="n"/>
       <c r="AD16" s="2" t="n"/>
       <c r="AE16" s="2" t="n"/>
-      <c r="AF16" s="4" t="n"/>
-      <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="2" t="n"/>
-      <c r="AI16" s="2" t="n"/>
-      <c r="AJ16" s="4" t="n"/>
-      <c r="AK16" s="4" t="n"/>
-      <c r="AL16" s="2" t="n"/>
-      <c r="AM16" s="2" t="n"/>
-      <c r="AN16" s="2" t="n"/>
-      <c r="AO16" s="2" t="n"/>
+      <c r="AF16" s="2" t="n"/>
+      <c r="AG16" s="2" t="n"/>
+      <c r="AH16" s="4" t="n"/>
+      <c r="AI16" s="4" t="n"/>
+      <c r="AJ16" s="2" t="n"/>
+      <c r="AK16" s="2" t="n"/>
+      <c r="AL16" s="4" t="n"/>
+      <c r="AM16" s="4" t="n"/>
+      <c r="AN16" s="4" t="n"/>
+      <c r="AO16" s="4" t="n"/>
+      <c r="AP16" s="2" t="n"/>
+      <c r="AQ16" s="2" t="n"/>
+      <c r="AR16" s="2" t="n"/>
+      <c r="AS16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1765,16 +1878,20 @@
       <c r="AC17" s="2" t="n"/>
       <c r="AD17" s="2" t="n"/>
       <c r="AE17" s="2" t="n"/>
-      <c r="AF17" s="4" t="n"/>
-      <c r="AG17" s="4" t="n"/>
-      <c r="AH17" s="2" t="n"/>
-      <c r="AI17" s="2" t="n"/>
-      <c r="AJ17" s="4" t="n"/>
-      <c r="AK17" s="4" t="n"/>
-      <c r="AL17" s="2" t="n"/>
-      <c r="AM17" s="2" t="n"/>
-      <c r="AN17" s="2" t="n"/>
-      <c r="AO17" s="2" t="n"/>
+      <c r="AF17" s="2" t="n"/>
+      <c r="AG17" s="2" t="n"/>
+      <c r="AH17" s="4" t="n"/>
+      <c r="AI17" s="4" t="n"/>
+      <c r="AJ17" s="2" t="n"/>
+      <c r="AK17" s="2" t="n"/>
+      <c r="AL17" s="4" t="n"/>
+      <c r="AM17" s="4" t="n"/>
+      <c r="AN17" s="4" t="n"/>
+      <c r="AO17" s="4" t="n"/>
+      <c r="AP17" s="2" t="n"/>
+      <c r="AQ17" s="2" t="n"/>
+      <c r="AR17" s="2" t="n"/>
+      <c r="AS17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1808,16 +1925,20 @@
       <c r="AC18" s="2" t="n"/>
       <c r="AD18" s="2" t="n"/>
       <c r="AE18" s="2" t="n"/>
-      <c r="AF18" s="4" t="n"/>
-      <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="2" t="n"/>
-      <c r="AI18" s="2" t="n"/>
-      <c r="AJ18" s="4" t="n"/>
-      <c r="AK18" s="4" t="n"/>
-      <c r="AL18" s="2" t="n"/>
-      <c r="AM18" s="2" t="n"/>
-      <c r="AN18" s="2" t="n"/>
-      <c r="AO18" s="2" t="n"/>
+      <c r="AF18" s="2" t="n"/>
+      <c r="AG18" s="2" t="n"/>
+      <c r="AH18" s="4" t="n"/>
+      <c r="AI18" s="4" t="n"/>
+      <c r="AJ18" s="2" t="n"/>
+      <c r="AK18" s="2" t="n"/>
+      <c r="AL18" s="4" t="n"/>
+      <c r="AM18" s="4" t="n"/>
+      <c r="AN18" s="4" t="n"/>
+      <c r="AO18" s="4" t="n"/>
+      <c r="AP18" s="2" t="n"/>
+      <c r="AQ18" s="2" t="n"/>
+      <c r="AR18" s="2" t="n"/>
+      <c r="AS18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1851,16 +1972,20 @@
       <c r="AC19" s="2" t="n"/>
       <c r="AD19" s="2" t="n"/>
       <c r="AE19" s="2" t="n"/>
-      <c r="AF19" s="4" t="n"/>
-      <c r="AG19" s="4" t="n"/>
-      <c r="AH19" s="2" t="n"/>
-      <c r="AI19" s="2" t="n"/>
-      <c r="AJ19" s="4" t="n"/>
-      <c r="AK19" s="4" t="n"/>
-      <c r="AL19" s="2" t="n"/>
-      <c r="AM19" s="2" t="n"/>
-      <c r="AN19" s="2" t="n"/>
-      <c r="AO19" s="2" t="n"/>
+      <c r="AF19" s="2" t="n"/>
+      <c r="AG19" s="2" t="n"/>
+      <c r="AH19" s="4" t="n"/>
+      <c r="AI19" s="4" t="n"/>
+      <c r="AJ19" s="2" t="n"/>
+      <c r="AK19" s="2" t="n"/>
+      <c r="AL19" s="4" t="n"/>
+      <c r="AM19" s="4" t="n"/>
+      <c r="AN19" s="4" t="n"/>
+      <c r="AO19" s="4" t="n"/>
+      <c r="AP19" s="2" t="n"/>
+      <c r="AQ19" s="2" t="n"/>
+      <c r="AR19" s="2" t="n"/>
+      <c r="AS19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -1894,16 +2019,20 @@
       <c r="AC20" s="2" t="n"/>
       <c r="AD20" s="2" t="n"/>
       <c r="AE20" s="2" t="n"/>
-      <c r="AF20" s="4" t="n"/>
-      <c r="AG20" s="4" t="n"/>
-      <c r="AH20" s="2" t="n"/>
-      <c r="AI20" s="2" t="n"/>
-      <c r="AJ20" s="4" t="n"/>
-      <c r="AK20" s="4" t="n"/>
-      <c r="AL20" s="2" t="n"/>
-      <c r="AM20" s="2" t="n"/>
-      <c r="AN20" s="2" t="n"/>
-      <c r="AO20" s="2" t="n"/>
+      <c r="AF20" s="2" t="n"/>
+      <c r="AG20" s="2" t="n"/>
+      <c r="AH20" s="4" t="n"/>
+      <c r="AI20" s="4" t="n"/>
+      <c r="AJ20" s="2" t="n"/>
+      <c r="AK20" s="2" t="n"/>
+      <c r="AL20" s="4" t="n"/>
+      <c r="AM20" s="4" t="n"/>
+      <c r="AN20" s="4" t="n"/>
+      <c r="AO20" s="4" t="n"/>
+      <c r="AP20" s="2" t="n"/>
+      <c r="AQ20" s="2" t="n"/>
+      <c r="AR20" s="2" t="n"/>
+      <c r="AS20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -1937,16 +2066,20 @@
       <c r="AC21" s="2" t="n"/>
       <c r="AD21" s="2" t="n"/>
       <c r="AE21" s="2" t="n"/>
-      <c r="AF21" s="4" t="n"/>
-      <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="2" t="n"/>
-      <c r="AI21" s="2" t="n"/>
-      <c r="AJ21" s="4" t="n"/>
-      <c r="AK21" s="4" t="n"/>
-      <c r="AL21" s="2" t="n"/>
-      <c r="AM21" s="2" t="n"/>
-      <c r="AN21" s="2" t="n"/>
-      <c r="AO21" s="2" t="n"/>
+      <c r="AF21" s="2" t="n"/>
+      <c r="AG21" s="2" t="n"/>
+      <c r="AH21" s="4" t="n"/>
+      <c r="AI21" s="4" t="n"/>
+      <c r="AJ21" s="2" t="n"/>
+      <c r="AK21" s="2" t="n"/>
+      <c r="AL21" s="4" t="n"/>
+      <c r="AM21" s="4" t="n"/>
+      <c r="AN21" s="4" t="n"/>
+      <c r="AO21" s="4" t="n"/>
+      <c r="AP21" s="2" t="n"/>
+      <c r="AQ21" s="2" t="n"/>
+      <c r="AR21" s="2" t="n"/>
+      <c r="AS21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -1980,16 +2113,20 @@
       <c r="AC22" s="2" t="n"/>
       <c r="AD22" s="2" t="n"/>
       <c r="AE22" s="2" t="n"/>
-      <c r="AF22" s="4" t="n"/>
-      <c r="AG22" s="4" t="n"/>
-      <c r="AH22" s="2" t="n"/>
-      <c r="AI22" s="2" t="n"/>
-      <c r="AJ22" s="4" t="n"/>
-      <c r="AK22" s="4" t="n"/>
-      <c r="AL22" s="2" t="n"/>
-      <c r="AM22" s="2" t="n"/>
-      <c r="AN22" s="2" t="n"/>
-      <c r="AO22" s="2" t="n"/>
+      <c r="AF22" s="2" t="n"/>
+      <c r="AG22" s="2" t="n"/>
+      <c r="AH22" s="4" t="n"/>
+      <c r="AI22" s="4" t="n"/>
+      <c r="AJ22" s="2" t="n"/>
+      <c r="AK22" s="2" t="n"/>
+      <c r="AL22" s="4" t="n"/>
+      <c r="AM22" s="4" t="n"/>
+      <c r="AN22" s="4" t="n"/>
+      <c r="AO22" s="4" t="n"/>
+      <c r="AP22" s="2" t="n"/>
+      <c r="AQ22" s="2" t="n"/>
+      <c r="AR22" s="2" t="n"/>
+      <c r="AS22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -2023,16 +2160,20 @@
       <c r="AC23" s="2" t="n"/>
       <c r="AD23" s="2" t="n"/>
       <c r="AE23" s="2" t="n"/>
-      <c r="AF23" s="4" t="n"/>
-      <c r="AG23" s="4" t="n"/>
-      <c r="AH23" s="2" t="n"/>
-      <c r="AI23" s="2" t="n"/>
-      <c r="AJ23" s="4" t="n"/>
-      <c r="AK23" s="4" t="n"/>
-      <c r="AL23" s="2" t="n"/>
-      <c r="AM23" s="2" t="n"/>
-      <c r="AN23" s="2" t="n"/>
-      <c r="AO23" s="2" t="n"/>
+      <c r="AF23" s="2" t="n"/>
+      <c r="AG23" s="2" t="n"/>
+      <c r="AH23" s="4" t="n"/>
+      <c r="AI23" s="4" t="n"/>
+      <c r="AJ23" s="2" t="n"/>
+      <c r="AK23" s="2" t="n"/>
+      <c r="AL23" s="4" t="n"/>
+      <c r="AM23" s="4" t="n"/>
+      <c r="AN23" s="4" t="n"/>
+      <c r="AO23" s="4" t="n"/>
+      <c r="AP23" s="2" t="n"/>
+      <c r="AQ23" s="2" t="n"/>
+      <c r="AR23" s="2" t="n"/>
+      <c r="AS23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -2066,16 +2207,20 @@
       <c r="AC24" s="2" t="n"/>
       <c r="AD24" s="2" t="n"/>
       <c r="AE24" s="2" t="n"/>
-      <c r="AF24" s="4" t="n"/>
-      <c r="AG24" s="4" t="n"/>
-      <c r="AH24" s="2" t="n"/>
-      <c r="AI24" s="2" t="n"/>
-      <c r="AJ24" s="4" t="n"/>
-      <c r="AK24" s="4" t="n"/>
-      <c r="AL24" s="2" t="n"/>
-      <c r="AM24" s="2" t="n"/>
-      <c r="AN24" s="2" t="n"/>
-      <c r="AO24" s="2" t="n"/>
+      <c r="AF24" s="2" t="n"/>
+      <c r="AG24" s="2" t="n"/>
+      <c r="AH24" s="4" t="n"/>
+      <c r="AI24" s="4" t="n"/>
+      <c r="AJ24" s="2" t="n"/>
+      <c r="AK24" s="2" t="n"/>
+      <c r="AL24" s="4" t="n"/>
+      <c r="AM24" s="4" t="n"/>
+      <c r="AN24" s="4" t="n"/>
+      <c r="AO24" s="4" t="n"/>
+      <c r="AP24" s="2" t="n"/>
+      <c r="AQ24" s="2" t="n"/>
+      <c r="AR24" s="2" t="n"/>
+      <c r="AS24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -2109,16 +2254,20 @@
       <c r="AC25" s="2" t="n"/>
       <c r="AD25" s="2" t="n"/>
       <c r="AE25" s="2" t="n"/>
-      <c r="AF25" s="4" t="n"/>
-      <c r="AG25" s="4" t="n"/>
-      <c r="AH25" s="2" t="n"/>
-      <c r="AI25" s="2" t="n"/>
-      <c r="AJ25" s="4" t="n"/>
-      <c r="AK25" s="4" t="n"/>
-      <c r="AL25" s="2" t="n"/>
-      <c r="AM25" s="2" t="n"/>
-      <c r="AN25" s="2" t="n"/>
-      <c r="AO25" s="2" t="n"/>
+      <c r="AF25" s="2" t="n"/>
+      <c r="AG25" s="2" t="n"/>
+      <c r="AH25" s="4" t="n"/>
+      <c r="AI25" s="4" t="n"/>
+      <c r="AJ25" s="2" t="n"/>
+      <c r="AK25" s="2" t="n"/>
+      <c r="AL25" s="4" t="n"/>
+      <c r="AM25" s="4" t="n"/>
+      <c r="AN25" s="4" t="n"/>
+      <c r="AO25" s="4" t="n"/>
+      <c r="AP25" s="2" t="n"/>
+      <c r="AQ25" s="2" t="n"/>
+      <c r="AR25" s="2" t="n"/>
+      <c r="AS25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2152,16 +2301,20 @@
       <c r="AC26" s="2" t="n"/>
       <c r="AD26" s="2" t="n"/>
       <c r="AE26" s="2" t="n"/>
-      <c r="AF26" s="4" t="n"/>
-      <c r="AG26" s="4" t="n"/>
-      <c r="AH26" s="2" t="n"/>
-      <c r="AI26" s="2" t="n"/>
-      <c r="AJ26" s="4" t="n"/>
-      <c r="AK26" s="4" t="n"/>
-      <c r="AL26" s="2" t="n"/>
-      <c r="AM26" s="2" t="n"/>
-      <c r="AN26" s="2" t="n"/>
-      <c r="AO26" s="2" t="n"/>
+      <c r="AF26" s="2" t="n"/>
+      <c r="AG26" s="2" t="n"/>
+      <c r="AH26" s="4" t="n"/>
+      <c r="AI26" s="4" t="n"/>
+      <c r="AJ26" s="2" t="n"/>
+      <c r="AK26" s="2" t="n"/>
+      <c r="AL26" s="4" t="n"/>
+      <c r="AM26" s="4" t="n"/>
+      <c r="AN26" s="4" t="n"/>
+      <c r="AO26" s="4" t="n"/>
+      <c r="AP26" s="2" t="n"/>
+      <c r="AQ26" s="2" t="n"/>
+      <c r="AR26" s="2" t="n"/>
+      <c r="AS26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2195,16 +2348,20 @@
       <c r="AC27" s="2" t="n"/>
       <c r="AD27" s="2" t="n"/>
       <c r="AE27" s="2" t="n"/>
-      <c r="AF27" s="4" t="n"/>
-      <c r="AG27" s="4" t="n"/>
-      <c r="AH27" s="2" t="n"/>
-      <c r="AI27" s="2" t="n"/>
-      <c r="AJ27" s="4" t="n"/>
-      <c r="AK27" s="4" t="n"/>
-      <c r="AL27" s="2" t="n"/>
-      <c r="AM27" s="2" t="n"/>
-      <c r="AN27" s="2" t="n"/>
-      <c r="AO27" s="2" t="n"/>
+      <c r="AF27" s="2" t="n"/>
+      <c r="AG27" s="2" t="n"/>
+      <c r="AH27" s="4" t="n"/>
+      <c r="AI27" s="4" t="n"/>
+      <c r="AJ27" s="2" t="n"/>
+      <c r="AK27" s="2" t="n"/>
+      <c r="AL27" s="4" t="n"/>
+      <c r="AM27" s="4" t="n"/>
+      <c r="AN27" s="4" t="n"/>
+      <c r="AO27" s="4" t="n"/>
+      <c r="AP27" s="2" t="n"/>
+      <c r="AQ27" s="2" t="n"/>
+      <c r="AR27" s="2" t="n"/>
+      <c r="AS27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2238,16 +2395,20 @@
       <c r="AC28" s="2" t="n"/>
       <c r="AD28" s="2" t="n"/>
       <c r="AE28" s="2" t="n"/>
-      <c r="AF28" s="4" t="n"/>
-      <c r="AG28" s="4" t="n"/>
-      <c r="AH28" s="2" t="n"/>
-      <c r="AI28" s="2" t="n"/>
-      <c r="AJ28" s="4" t="n"/>
-      <c r="AK28" s="4" t="n"/>
-      <c r="AL28" s="2" t="n"/>
-      <c r="AM28" s="2" t="n"/>
-      <c r="AN28" s="2" t="n"/>
-      <c r="AO28" s="2" t="n"/>
+      <c r="AF28" s="2" t="n"/>
+      <c r="AG28" s="2" t="n"/>
+      <c r="AH28" s="4" t="n"/>
+      <c r="AI28" s="4" t="n"/>
+      <c r="AJ28" s="2" t="n"/>
+      <c r="AK28" s="2" t="n"/>
+      <c r="AL28" s="4" t="n"/>
+      <c r="AM28" s="4" t="n"/>
+      <c r="AN28" s="4" t="n"/>
+      <c r="AO28" s="4" t="n"/>
+      <c r="AP28" s="2" t="n"/>
+      <c r="AQ28" s="2" t="n"/>
+      <c r="AR28" s="2" t="n"/>
+      <c r="AS28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2281,16 +2442,20 @@
       <c r="AC29" s="2" t="n"/>
       <c r="AD29" s="2" t="n"/>
       <c r="AE29" s="2" t="n"/>
-      <c r="AF29" s="4" t="n"/>
-      <c r="AG29" s="4" t="n"/>
-      <c r="AH29" s="2" t="n"/>
-      <c r="AI29" s="2" t="n"/>
-      <c r="AJ29" s="4" t="n"/>
-      <c r="AK29" s="4" t="n"/>
-      <c r="AL29" s="2" t="n"/>
-      <c r="AM29" s="2" t="n"/>
-      <c r="AN29" s="2" t="n"/>
-      <c r="AO29" s="2" t="n"/>
+      <c r="AF29" s="2" t="n"/>
+      <c r="AG29" s="2" t="n"/>
+      <c r="AH29" s="4" t="n"/>
+      <c r="AI29" s="4" t="n"/>
+      <c r="AJ29" s="2" t="n"/>
+      <c r="AK29" s="2" t="n"/>
+      <c r="AL29" s="4" t="n"/>
+      <c r="AM29" s="4" t="n"/>
+      <c r="AN29" s="4" t="n"/>
+      <c r="AO29" s="4" t="n"/>
+      <c r="AP29" s="2" t="n"/>
+      <c r="AQ29" s="2" t="n"/>
+      <c r="AR29" s="2" t="n"/>
+      <c r="AS29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2324,16 +2489,20 @@
       <c r="AC30" s="2" t="n"/>
       <c r="AD30" s="2" t="n"/>
       <c r="AE30" s="2" t="n"/>
-      <c r="AF30" s="4" t="n"/>
-      <c r="AG30" s="4" t="n"/>
-      <c r="AH30" s="2" t="n"/>
-      <c r="AI30" s="2" t="n"/>
-      <c r="AJ30" s="4" t="n"/>
-      <c r="AK30" s="4" t="n"/>
-      <c r="AL30" s="2" t="n"/>
-      <c r="AM30" s="2" t="n"/>
-      <c r="AN30" s="2" t="n"/>
-      <c r="AO30" s="2" t="n"/>
+      <c r="AF30" s="2" t="n"/>
+      <c r="AG30" s="2" t="n"/>
+      <c r="AH30" s="4" t="n"/>
+      <c r="AI30" s="4" t="n"/>
+      <c r="AJ30" s="2" t="n"/>
+      <c r="AK30" s="2" t="n"/>
+      <c r="AL30" s="4" t="n"/>
+      <c r="AM30" s="4" t="n"/>
+      <c r="AN30" s="4" t="n"/>
+      <c r="AO30" s="4" t="n"/>
+      <c r="AP30" s="2" t="n"/>
+      <c r="AQ30" s="2" t="n"/>
+      <c r="AR30" s="2" t="n"/>
+      <c r="AS30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2367,16 +2536,20 @@
       <c r="AC31" s="2" t="n"/>
       <c r="AD31" s="2" t="n"/>
       <c r="AE31" s="2" t="n"/>
-      <c r="AF31" s="4" t="n"/>
-      <c r="AG31" s="4" t="n"/>
-      <c r="AH31" s="2" t="n"/>
-      <c r="AI31" s="2" t="n"/>
-      <c r="AJ31" s="4" t="n"/>
-      <c r="AK31" s="4" t="n"/>
-      <c r="AL31" s="2" t="n"/>
-      <c r="AM31" s="2" t="n"/>
-      <c r="AN31" s="2" t="n"/>
-      <c r="AO31" s="2" t="n"/>
+      <c r="AF31" s="2" t="n"/>
+      <c r="AG31" s="2" t="n"/>
+      <c r="AH31" s="4" t="n"/>
+      <c r="AI31" s="4" t="n"/>
+      <c r="AJ31" s="2" t="n"/>
+      <c r="AK31" s="2" t="n"/>
+      <c r="AL31" s="4" t="n"/>
+      <c r="AM31" s="4" t="n"/>
+      <c r="AN31" s="4" t="n"/>
+      <c r="AO31" s="4" t="n"/>
+      <c r="AP31" s="2" t="n"/>
+      <c r="AQ31" s="2" t="n"/>
+      <c r="AR31" s="2" t="n"/>
+      <c r="AS31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2410,16 +2583,20 @@
       <c r="AC32" s="2" t="n"/>
       <c r="AD32" s="2" t="n"/>
       <c r="AE32" s="2" t="n"/>
-      <c r="AF32" s="4" t="n"/>
-      <c r="AG32" s="4" t="n"/>
-      <c r="AH32" s="2" t="n"/>
-      <c r="AI32" s="2" t="n"/>
-      <c r="AJ32" s="4" t="n"/>
-      <c r="AK32" s="4" t="n"/>
-      <c r="AL32" s="2" t="n"/>
-      <c r="AM32" s="2" t="n"/>
-      <c r="AN32" s="2" t="n"/>
-      <c r="AO32" s="2" t="n"/>
+      <c r="AF32" s="2" t="n"/>
+      <c r="AG32" s="2" t="n"/>
+      <c r="AH32" s="4" t="n"/>
+      <c r="AI32" s="4" t="n"/>
+      <c r="AJ32" s="2" t="n"/>
+      <c r="AK32" s="2" t="n"/>
+      <c r="AL32" s="4" t="n"/>
+      <c r="AM32" s="4" t="n"/>
+      <c r="AN32" s="4" t="n"/>
+      <c r="AO32" s="4" t="n"/>
+      <c r="AP32" s="2" t="n"/>
+      <c r="AQ32" s="2" t="n"/>
+      <c r="AR32" s="2" t="n"/>
+      <c r="AS32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2453,16 +2630,20 @@
       <c r="AC33" s="2" t="n"/>
       <c r="AD33" s="2" t="n"/>
       <c r="AE33" s="2" t="n"/>
-      <c r="AF33" s="4" t="n"/>
-      <c r="AG33" s="4" t="n"/>
-      <c r="AH33" s="2" t="n"/>
-      <c r="AI33" s="2" t="n"/>
-      <c r="AJ33" s="4" t="n"/>
-      <c r="AK33" s="4" t="n"/>
-      <c r="AL33" s="2" t="n"/>
-      <c r="AM33" s="2" t="n"/>
-      <c r="AN33" s="2" t="n"/>
-      <c r="AO33" s="2" t="n"/>
+      <c r="AF33" s="2" t="n"/>
+      <c r="AG33" s="2" t="n"/>
+      <c r="AH33" s="4" t="n"/>
+      <c r="AI33" s="4" t="n"/>
+      <c r="AJ33" s="2" t="n"/>
+      <c r="AK33" s="2" t="n"/>
+      <c r="AL33" s="4" t="n"/>
+      <c r="AM33" s="4" t="n"/>
+      <c r="AN33" s="4" t="n"/>
+      <c r="AO33" s="4" t="n"/>
+      <c r="AP33" s="2" t="n"/>
+      <c r="AQ33" s="2" t="n"/>
+      <c r="AR33" s="2" t="n"/>
+      <c r="AS33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2496,16 +2677,20 @@
       <c r="AC34" s="2" t="n"/>
       <c r="AD34" s="2" t="n"/>
       <c r="AE34" s="2" t="n"/>
-      <c r="AF34" s="4" t="n"/>
-      <c r="AG34" s="4" t="n"/>
-      <c r="AH34" s="2" t="n"/>
-      <c r="AI34" s="2" t="n"/>
-      <c r="AJ34" s="4" t="n"/>
-      <c r="AK34" s="4" t="n"/>
-      <c r="AL34" s="2" t="n"/>
-      <c r="AM34" s="2" t="n"/>
-      <c r="AN34" s="2" t="n"/>
-      <c r="AO34" s="2" t="n"/>
+      <c r="AF34" s="2" t="n"/>
+      <c r="AG34" s="2" t="n"/>
+      <c r="AH34" s="4" t="n"/>
+      <c r="AI34" s="4" t="n"/>
+      <c r="AJ34" s="2" t="n"/>
+      <c r="AK34" s="2" t="n"/>
+      <c r="AL34" s="4" t="n"/>
+      <c r="AM34" s="4" t="n"/>
+      <c r="AN34" s="4" t="n"/>
+      <c r="AO34" s="4" t="n"/>
+      <c r="AP34" s="2" t="n"/>
+      <c r="AQ34" s="2" t="n"/>
+      <c r="AR34" s="2" t="n"/>
+      <c r="AS34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2539,16 +2724,20 @@
       <c r="AC35" s="2" t="n"/>
       <c r="AD35" s="2" t="n"/>
       <c r="AE35" s="2" t="n"/>
-      <c r="AF35" s="4" t="n"/>
-      <c r="AG35" s="4" t="n"/>
-      <c r="AH35" s="2" t="n"/>
-      <c r="AI35" s="2" t="n"/>
-      <c r="AJ35" s="4" t="n"/>
-      <c r="AK35" s="4" t="n"/>
-      <c r="AL35" s="2" t="n"/>
-      <c r="AM35" s="2" t="n"/>
-      <c r="AN35" s="2" t="n"/>
-      <c r="AO35" s="2" t="n"/>
+      <c r="AF35" s="2" t="n"/>
+      <c r="AG35" s="2" t="n"/>
+      <c r="AH35" s="4" t="n"/>
+      <c r="AI35" s="4" t="n"/>
+      <c r="AJ35" s="2" t="n"/>
+      <c r="AK35" s="2" t="n"/>
+      <c r="AL35" s="4" t="n"/>
+      <c r="AM35" s="4" t="n"/>
+      <c r="AN35" s="4" t="n"/>
+      <c r="AO35" s="4" t="n"/>
+      <c r="AP35" s="2" t="n"/>
+      <c r="AQ35" s="2" t="n"/>
+      <c r="AR35" s="2" t="n"/>
+      <c r="AS35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2582,16 +2771,20 @@
       <c r="AC36" s="2" t="n"/>
       <c r="AD36" s="2" t="n"/>
       <c r="AE36" s="2" t="n"/>
-      <c r="AF36" s="4" t="n"/>
-      <c r="AG36" s="4" t="n"/>
-      <c r="AH36" s="2" t="n"/>
-      <c r="AI36" s="2" t="n"/>
-      <c r="AJ36" s="4" t="n"/>
-      <c r="AK36" s="4" t="n"/>
-      <c r="AL36" s="2" t="n"/>
-      <c r="AM36" s="2" t="n"/>
-      <c r="AN36" s="2" t="n"/>
-      <c r="AO36" s="2" t="n"/>
+      <c r="AF36" s="2" t="n"/>
+      <c r="AG36" s="2" t="n"/>
+      <c r="AH36" s="4" t="n"/>
+      <c r="AI36" s="4" t="n"/>
+      <c r="AJ36" s="2" t="n"/>
+      <c r="AK36" s="2" t="n"/>
+      <c r="AL36" s="4" t="n"/>
+      <c r="AM36" s="4" t="n"/>
+      <c r="AN36" s="4" t="n"/>
+      <c r="AO36" s="4" t="n"/>
+      <c r="AP36" s="2" t="n"/>
+      <c r="AQ36" s="2" t="n"/>
+      <c r="AR36" s="2" t="n"/>
+      <c r="AS36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -2625,16 +2818,20 @@
       <c r="AC37" s="2" t="n"/>
       <c r="AD37" s="2" t="n"/>
       <c r="AE37" s="2" t="n"/>
-      <c r="AF37" s="4" t="n"/>
-      <c r="AG37" s="4" t="n"/>
-      <c r="AH37" s="2" t="n"/>
-      <c r="AI37" s="2" t="n"/>
-      <c r="AJ37" s="4" t="n"/>
-      <c r="AK37" s="4" t="n"/>
-      <c r="AL37" s="2" t="n"/>
-      <c r="AM37" s="2" t="n"/>
-      <c r="AN37" s="2" t="n"/>
-      <c r="AO37" s="2" t="n"/>
+      <c r="AF37" s="2" t="n"/>
+      <c r="AG37" s="2" t="n"/>
+      <c r="AH37" s="4" t="n"/>
+      <c r="AI37" s="4" t="n"/>
+      <c r="AJ37" s="2" t="n"/>
+      <c r="AK37" s="2" t="n"/>
+      <c r="AL37" s="4" t="n"/>
+      <c r="AM37" s="4" t="n"/>
+      <c r="AN37" s="4" t="n"/>
+      <c r="AO37" s="4" t="n"/>
+      <c r="AP37" s="2" t="n"/>
+      <c r="AQ37" s="2" t="n"/>
+      <c r="AR37" s="2" t="n"/>
+      <c r="AS37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -2668,16 +2865,20 @@
       <c r="AC38" s="2" t="n"/>
       <c r="AD38" s="2" t="n"/>
       <c r="AE38" s="2" t="n"/>
-      <c r="AF38" s="4" t="n"/>
-      <c r="AG38" s="4" t="n"/>
-      <c r="AH38" s="2" t="n"/>
-      <c r="AI38" s="2" t="n"/>
-      <c r="AJ38" s="4" t="n"/>
-      <c r="AK38" s="4" t="n"/>
-      <c r="AL38" s="2" t="n"/>
-      <c r="AM38" s="2" t="n"/>
-      <c r="AN38" s="2" t="n"/>
-      <c r="AO38" s="2" t="n"/>
+      <c r="AF38" s="2" t="n"/>
+      <c r="AG38" s="2" t="n"/>
+      <c r="AH38" s="4" t="n"/>
+      <c r="AI38" s="4" t="n"/>
+      <c r="AJ38" s="2" t="n"/>
+      <c r="AK38" s="2" t="n"/>
+      <c r="AL38" s="4" t="n"/>
+      <c r="AM38" s="4" t="n"/>
+      <c r="AN38" s="4" t="n"/>
+      <c r="AO38" s="4" t="n"/>
+      <c r="AP38" s="2" t="n"/>
+      <c r="AQ38" s="2" t="n"/>
+      <c r="AR38" s="2" t="n"/>
+      <c r="AS38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -2711,16 +2912,20 @@
       <c r="AC39" s="2" t="n"/>
       <c r="AD39" s="2" t="n"/>
       <c r="AE39" s="2" t="n"/>
-      <c r="AF39" s="4" t="n"/>
-      <c r="AG39" s="4" t="n"/>
-      <c r="AH39" s="2" t="n"/>
-      <c r="AI39" s="2" t="n"/>
-      <c r="AJ39" s="4" t="n"/>
-      <c r="AK39" s="4" t="n"/>
-      <c r="AL39" s="2" t="n"/>
-      <c r="AM39" s="2" t="n"/>
-      <c r="AN39" s="2" t="n"/>
-      <c r="AO39" s="2" t="n"/>
+      <c r="AF39" s="2" t="n"/>
+      <c r="AG39" s="2" t="n"/>
+      <c r="AH39" s="4" t="n"/>
+      <c r="AI39" s="4" t="n"/>
+      <c r="AJ39" s="2" t="n"/>
+      <c r="AK39" s="2" t="n"/>
+      <c r="AL39" s="4" t="n"/>
+      <c r="AM39" s="4" t="n"/>
+      <c r="AN39" s="4" t="n"/>
+      <c r="AO39" s="4" t="n"/>
+      <c r="AP39" s="2" t="n"/>
+      <c r="AQ39" s="2" t="n"/>
+      <c r="AR39" s="2" t="n"/>
+      <c r="AS39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2754,16 +2959,20 @@
       <c r="AC40" s="2" t="n"/>
       <c r="AD40" s="2" t="n"/>
       <c r="AE40" s="2" t="n"/>
-      <c r="AF40" s="4" t="n"/>
-      <c r="AG40" s="4" t="n"/>
-      <c r="AH40" s="2" t="n"/>
-      <c r="AI40" s="2" t="n"/>
-      <c r="AJ40" s="4" t="n"/>
-      <c r="AK40" s="4" t="n"/>
-      <c r="AL40" s="2" t="n"/>
-      <c r="AM40" s="2" t="n"/>
-      <c r="AN40" s="2" t="n"/>
-      <c r="AO40" s="2" t="n"/>
+      <c r="AF40" s="2" t="n"/>
+      <c r="AG40" s="2" t="n"/>
+      <c r="AH40" s="4" t="n"/>
+      <c r="AI40" s="4" t="n"/>
+      <c r="AJ40" s="2" t="n"/>
+      <c r="AK40" s="2" t="n"/>
+      <c r="AL40" s="4" t="n"/>
+      <c r="AM40" s="4" t="n"/>
+      <c r="AN40" s="4" t="n"/>
+      <c r="AO40" s="4" t="n"/>
+      <c r="AP40" s="2" t="n"/>
+      <c r="AQ40" s="2" t="n"/>
+      <c r="AR40" s="2" t="n"/>
+      <c r="AS40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -2797,16 +3006,20 @@
       <c r="AC41" s="2" t="n"/>
       <c r="AD41" s="2" t="n"/>
       <c r="AE41" s="2" t="n"/>
-      <c r="AF41" s="4" t="n"/>
-      <c r="AG41" s="4" t="n"/>
-      <c r="AH41" s="2" t="n"/>
-      <c r="AI41" s="2" t="n"/>
-      <c r="AJ41" s="4" t="n"/>
-      <c r="AK41" s="4" t="n"/>
-      <c r="AL41" s="2" t="n"/>
-      <c r="AM41" s="2" t="n"/>
-      <c r="AN41" s="2" t="n"/>
-      <c r="AO41" s="2" t="n"/>
+      <c r="AF41" s="2" t="n"/>
+      <c r="AG41" s="2" t="n"/>
+      <c r="AH41" s="4" t="n"/>
+      <c r="AI41" s="4" t="n"/>
+      <c r="AJ41" s="2" t="n"/>
+      <c r="AK41" s="2" t="n"/>
+      <c r="AL41" s="4" t="n"/>
+      <c r="AM41" s="4" t="n"/>
+      <c r="AN41" s="4" t="n"/>
+      <c r="AO41" s="4" t="n"/>
+      <c r="AP41" s="2" t="n"/>
+      <c r="AQ41" s="2" t="n"/>
+      <c r="AR41" s="2" t="n"/>
+      <c r="AS41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2840,16 +3053,20 @@
       <c r="AC42" s="2" t="n"/>
       <c r="AD42" s="2" t="n"/>
       <c r="AE42" s="2" t="n"/>
-      <c r="AF42" s="4" t="n"/>
-      <c r="AG42" s="4" t="n"/>
-      <c r="AH42" s="2" t="n"/>
-      <c r="AI42" s="2" t="n"/>
-      <c r="AJ42" s="4" t="n"/>
-      <c r="AK42" s="4" t="n"/>
-      <c r="AL42" s="2" t="n"/>
-      <c r="AM42" s="2" t="n"/>
-      <c r="AN42" s="2" t="n"/>
-      <c r="AO42" s="2" t="n"/>
+      <c r="AF42" s="2" t="n"/>
+      <c r="AG42" s="2" t="n"/>
+      <c r="AH42" s="4" t="n"/>
+      <c r="AI42" s="4" t="n"/>
+      <c r="AJ42" s="2" t="n"/>
+      <c r="AK42" s="2" t="n"/>
+      <c r="AL42" s="4" t="n"/>
+      <c r="AM42" s="4" t="n"/>
+      <c r="AN42" s="4" t="n"/>
+      <c r="AO42" s="4" t="n"/>
+      <c r="AP42" s="2" t="n"/>
+      <c r="AQ42" s="2" t="n"/>
+      <c r="AR42" s="2" t="n"/>
+      <c r="AS42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -2883,16 +3100,20 @@
       <c r="AC43" s="2" t="n"/>
       <c r="AD43" s="2" t="n"/>
       <c r="AE43" s="2" t="n"/>
-      <c r="AF43" s="4" t="n"/>
-      <c r="AG43" s="4" t="n"/>
-      <c r="AH43" s="2" t="n"/>
-      <c r="AI43" s="2" t="n"/>
-      <c r="AJ43" s="4" t="n"/>
-      <c r="AK43" s="4" t="n"/>
-      <c r="AL43" s="2" t="n"/>
-      <c r="AM43" s="2" t="n"/>
-      <c r="AN43" s="2" t="n"/>
-      <c r="AO43" s="2" t="n"/>
+      <c r="AF43" s="2" t="n"/>
+      <c r="AG43" s="2" t="n"/>
+      <c r="AH43" s="4" t="n"/>
+      <c r="AI43" s="4" t="n"/>
+      <c r="AJ43" s="2" t="n"/>
+      <c r="AK43" s="2" t="n"/>
+      <c r="AL43" s="4" t="n"/>
+      <c r="AM43" s="4" t="n"/>
+      <c r="AN43" s="4" t="n"/>
+      <c r="AO43" s="4" t="n"/>
+      <c r="AP43" s="2" t="n"/>
+      <c r="AQ43" s="2" t="n"/>
+      <c r="AR43" s="2" t="n"/>
+      <c r="AS43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2926,16 +3147,20 @@
       <c r="AC44" s="2" t="n"/>
       <c r="AD44" s="2" t="n"/>
       <c r="AE44" s="2" t="n"/>
-      <c r="AF44" s="4" t="n"/>
-      <c r="AG44" s="4" t="n"/>
-      <c r="AH44" s="2" t="n"/>
-      <c r="AI44" s="2" t="n"/>
-      <c r="AJ44" s="4" t="n"/>
-      <c r="AK44" s="4" t="n"/>
-      <c r="AL44" s="2" t="n"/>
-      <c r="AM44" s="2" t="n"/>
-      <c r="AN44" s="2" t="n"/>
-      <c r="AO44" s="2" t="n"/>
+      <c r="AF44" s="2" t="n"/>
+      <c r="AG44" s="2" t="n"/>
+      <c r="AH44" s="4" t="n"/>
+      <c r="AI44" s="4" t="n"/>
+      <c r="AJ44" s="2" t="n"/>
+      <c r="AK44" s="2" t="n"/>
+      <c r="AL44" s="4" t="n"/>
+      <c r="AM44" s="4" t="n"/>
+      <c r="AN44" s="4" t="n"/>
+      <c r="AO44" s="4" t="n"/>
+      <c r="AP44" s="2" t="n"/>
+      <c r="AQ44" s="2" t="n"/>
+      <c r="AR44" s="2" t="n"/>
+      <c r="AS44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -2969,16 +3194,20 @@
       <c r="AC45" s="2" t="n"/>
       <c r="AD45" s="2" t="n"/>
       <c r="AE45" s="2" t="n"/>
-      <c r="AF45" s="4" t="n"/>
-      <c r="AG45" s="4" t="n"/>
-      <c r="AH45" s="2" t="n"/>
-      <c r="AI45" s="2" t="n"/>
-      <c r="AJ45" s="4" t="n"/>
-      <c r="AK45" s="4" t="n"/>
-      <c r="AL45" s="2" t="n"/>
-      <c r="AM45" s="2" t="n"/>
-      <c r="AN45" s="2" t="n"/>
-      <c r="AO45" s="2" t="n"/>
+      <c r="AF45" s="2" t="n"/>
+      <c r="AG45" s="2" t="n"/>
+      <c r="AH45" s="4" t="n"/>
+      <c r="AI45" s="4" t="n"/>
+      <c r="AJ45" s="2" t="n"/>
+      <c r="AK45" s="2" t="n"/>
+      <c r="AL45" s="4" t="n"/>
+      <c r="AM45" s="4" t="n"/>
+      <c r="AN45" s="4" t="n"/>
+      <c r="AO45" s="4" t="n"/>
+      <c r="AP45" s="2" t="n"/>
+      <c r="AQ45" s="2" t="n"/>
+      <c r="AR45" s="2" t="n"/>
+      <c r="AS45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -3012,16 +3241,20 @@
       <c r="AC46" s="2" t="n"/>
       <c r="AD46" s="2" t="n"/>
       <c r="AE46" s="2" t="n"/>
-      <c r="AF46" s="4" t="n"/>
-      <c r="AG46" s="4" t="n"/>
-      <c r="AH46" s="2" t="n"/>
-      <c r="AI46" s="2" t="n"/>
-      <c r="AJ46" s="4" t="n"/>
-      <c r="AK46" s="4" t="n"/>
-      <c r="AL46" s="2" t="n"/>
-      <c r="AM46" s="2" t="n"/>
-      <c r="AN46" s="2" t="n"/>
-      <c r="AO46" s="2" t="n"/>
+      <c r="AF46" s="2" t="n"/>
+      <c r="AG46" s="2" t="n"/>
+      <c r="AH46" s="4" t="n"/>
+      <c r="AI46" s="4" t="n"/>
+      <c r="AJ46" s="2" t="n"/>
+      <c r="AK46" s="2" t="n"/>
+      <c r="AL46" s="4" t="n"/>
+      <c r="AM46" s="4" t="n"/>
+      <c r="AN46" s="4" t="n"/>
+      <c r="AO46" s="4" t="n"/>
+      <c r="AP46" s="2" t="n"/>
+      <c r="AQ46" s="2" t="n"/>
+      <c r="AR46" s="2" t="n"/>
+      <c r="AS46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -3055,16 +3288,20 @@
       <c r="AC47" s="2" t="n"/>
       <c r="AD47" s="2" t="n"/>
       <c r="AE47" s="2" t="n"/>
-      <c r="AF47" s="4" t="n"/>
-      <c r="AG47" s="4" t="n"/>
-      <c r="AH47" s="2" t="n"/>
-      <c r="AI47" s="2" t="n"/>
-      <c r="AJ47" s="4" t="n"/>
-      <c r="AK47" s="4" t="n"/>
-      <c r="AL47" s="2" t="n"/>
-      <c r="AM47" s="2" t="n"/>
-      <c r="AN47" s="2" t="n"/>
-      <c r="AO47" s="2" t="n"/>
+      <c r="AF47" s="2" t="n"/>
+      <c r="AG47" s="2" t="n"/>
+      <c r="AH47" s="4" t="n"/>
+      <c r="AI47" s="4" t="n"/>
+      <c r="AJ47" s="2" t="n"/>
+      <c r="AK47" s="2" t="n"/>
+      <c r="AL47" s="4" t="n"/>
+      <c r="AM47" s="4" t="n"/>
+      <c r="AN47" s="4" t="n"/>
+      <c r="AO47" s="4" t="n"/>
+      <c r="AP47" s="2" t="n"/>
+      <c r="AQ47" s="2" t="n"/>
+      <c r="AR47" s="2" t="n"/>
+      <c r="AS47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -3098,16 +3335,20 @@
       <c r="AC48" s="2" t="n"/>
       <c r="AD48" s="2" t="n"/>
       <c r="AE48" s="2" t="n"/>
-      <c r="AF48" s="4" t="n"/>
-      <c r="AG48" s="4" t="n"/>
-      <c r="AH48" s="2" t="n"/>
-      <c r="AI48" s="2" t="n"/>
-      <c r="AJ48" s="4" t="n"/>
-      <c r="AK48" s="4" t="n"/>
-      <c r="AL48" s="2" t="n"/>
-      <c r="AM48" s="2" t="n"/>
-      <c r="AN48" s="2" t="n"/>
-      <c r="AO48" s="2" t="n"/>
+      <c r="AF48" s="2" t="n"/>
+      <c r="AG48" s="2" t="n"/>
+      <c r="AH48" s="4" t="n"/>
+      <c r="AI48" s="4" t="n"/>
+      <c r="AJ48" s="2" t="n"/>
+      <c r="AK48" s="2" t="n"/>
+      <c r="AL48" s="4" t="n"/>
+      <c r="AM48" s="4" t="n"/>
+      <c r="AN48" s="4" t="n"/>
+      <c r="AO48" s="4" t="n"/>
+      <c r="AP48" s="2" t="n"/>
+      <c r="AQ48" s="2" t="n"/>
+      <c r="AR48" s="2" t="n"/>
+      <c r="AS48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -3141,16 +3382,20 @@
       <c r="AC49" s="2" t="n"/>
       <c r="AD49" s="2" t="n"/>
       <c r="AE49" s="2" t="n"/>
-      <c r="AF49" s="4" t="n"/>
-      <c r="AG49" s="4" t="n"/>
-      <c r="AH49" s="2" t="n"/>
-      <c r="AI49" s="2" t="n"/>
-      <c r="AJ49" s="4" t="n"/>
-      <c r="AK49" s="4" t="n"/>
-      <c r="AL49" s="2" t="n"/>
-      <c r="AM49" s="2" t="n"/>
-      <c r="AN49" s="2" t="n"/>
-      <c r="AO49" s="2" t="n"/>
+      <c r="AF49" s="2" t="n"/>
+      <c r="AG49" s="2" t="n"/>
+      <c r="AH49" s="4" t="n"/>
+      <c r="AI49" s="4" t="n"/>
+      <c r="AJ49" s="2" t="n"/>
+      <c r="AK49" s="2" t="n"/>
+      <c r="AL49" s="4" t="n"/>
+      <c r="AM49" s="4" t="n"/>
+      <c r="AN49" s="4" t="n"/>
+      <c r="AO49" s="4" t="n"/>
+      <c r="AP49" s="2" t="n"/>
+      <c r="AQ49" s="2" t="n"/>
+      <c r="AR49" s="2" t="n"/>
+      <c r="AS49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -3184,16 +3429,20 @@
       <c r="AC50" s="2" t="n"/>
       <c r="AD50" s="2" t="n"/>
       <c r="AE50" s="2" t="n"/>
-      <c r="AF50" s="4" t="n"/>
-      <c r="AG50" s="4" t="n"/>
-      <c r="AH50" s="2" t="n"/>
-      <c r="AI50" s="2" t="n"/>
-      <c r="AJ50" s="4" t="n"/>
-      <c r="AK50" s="4" t="n"/>
-      <c r="AL50" s="2" t="n"/>
-      <c r="AM50" s="2" t="n"/>
-      <c r="AN50" s="2" t="n"/>
-      <c r="AO50" s="2" t="n"/>
+      <c r="AF50" s="2" t="n"/>
+      <c r="AG50" s="2" t="n"/>
+      <c r="AH50" s="4" t="n"/>
+      <c r="AI50" s="4" t="n"/>
+      <c r="AJ50" s="2" t="n"/>
+      <c r="AK50" s="2" t="n"/>
+      <c r="AL50" s="4" t="n"/>
+      <c r="AM50" s="4" t="n"/>
+      <c r="AN50" s="4" t="n"/>
+      <c r="AO50" s="4" t="n"/>
+      <c r="AP50" s="2" t="n"/>
+      <c r="AQ50" s="2" t="n"/>
+      <c r="AR50" s="2" t="n"/>
+      <c r="AS50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -3227,16 +3476,20 @@
       <c r="AC51" s="2" t="n"/>
       <c r="AD51" s="2" t="n"/>
       <c r="AE51" s="2" t="n"/>
-      <c r="AF51" s="4" t="n"/>
-      <c r="AG51" s="4" t="n"/>
-      <c r="AH51" s="2" t="n"/>
-      <c r="AI51" s="2" t="n"/>
-      <c r="AJ51" s="4" t="n"/>
-      <c r="AK51" s="4" t="n"/>
-      <c r="AL51" s="2" t="n"/>
-      <c r="AM51" s="2" t="n"/>
-      <c r="AN51" s="2" t="n"/>
-      <c r="AO51" s="2" t="n"/>
+      <c r="AF51" s="2" t="n"/>
+      <c r="AG51" s="2" t="n"/>
+      <c r="AH51" s="4" t="n"/>
+      <c r="AI51" s="4" t="n"/>
+      <c r="AJ51" s="2" t="n"/>
+      <c r="AK51" s="2" t="n"/>
+      <c r="AL51" s="4" t="n"/>
+      <c r="AM51" s="4" t="n"/>
+      <c r="AN51" s="4" t="n"/>
+      <c r="AO51" s="4" t="n"/>
+      <c r="AP51" s="2" t="n"/>
+      <c r="AQ51" s="2" t="n"/>
+      <c r="AR51" s="2" t="n"/>
+      <c r="AS51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -3270,16 +3523,20 @@
       <c r="AC52" s="2" t="n"/>
       <c r="AD52" s="2" t="n"/>
       <c r="AE52" s="2" t="n"/>
-      <c r="AF52" s="4" t="n"/>
-      <c r="AG52" s="4" t="n"/>
-      <c r="AH52" s="2" t="n"/>
-      <c r="AI52" s="2" t="n"/>
-      <c r="AJ52" s="4" t="n"/>
-      <c r="AK52" s="4" t="n"/>
-      <c r="AL52" s="2" t="n"/>
-      <c r="AM52" s="2" t="n"/>
-      <c r="AN52" s="2" t="n"/>
-      <c r="AO52" s="2" t="n"/>
+      <c r="AF52" s="2" t="n"/>
+      <c r="AG52" s="2" t="n"/>
+      <c r="AH52" s="4" t="n"/>
+      <c r="AI52" s="4" t="n"/>
+      <c r="AJ52" s="2" t="n"/>
+      <c r="AK52" s="2" t="n"/>
+      <c r="AL52" s="4" t="n"/>
+      <c r="AM52" s="4" t="n"/>
+      <c r="AN52" s="4" t="n"/>
+      <c r="AO52" s="4" t="n"/>
+      <c r="AP52" s="2" t="n"/>
+      <c r="AQ52" s="2" t="n"/>
+      <c r="AR52" s="2" t="n"/>
+      <c r="AS52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -3313,16 +3570,20 @@
       <c r="AC53" s="2" t="n"/>
       <c r="AD53" s="2" t="n"/>
       <c r="AE53" s="2" t="n"/>
-      <c r="AF53" s="4" t="n"/>
-      <c r="AG53" s="4" t="n"/>
-      <c r="AH53" s="2" t="n"/>
-      <c r="AI53" s="2" t="n"/>
-      <c r="AJ53" s="4" t="n"/>
-      <c r="AK53" s="4" t="n"/>
-      <c r="AL53" s="2" t="n"/>
-      <c r="AM53" s="2" t="n"/>
-      <c r="AN53" s="2" t="n"/>
-      <c r="AO53" s="2" t="n"/>
+      <c r="AF53" s="2" t="n"/>
+      <c r="AG53" s="2" t="n"/>
+      <c r="AH53" s="4" t="n"/>
+      <c r="AI53" s="4" t="n"/>
+      <c r="AJ53" s="2" t="n"/>
+      <c r="AK53" s="2" t="n"/>
+      <c r="AL53" s="4" t="n"/>
+      <c r="AM53" s="4" t="n"/>
+      <c r="AN53" s="4" t="n"/>
+      <c r="AO53" s="4" t="n"/>
+      <c r="AP53" s="2" t="n"/>
+      <c r="AQ53" s="2" t="n"/>
+      <c r="AR53" s="2" t="n"/>
+      <c r="AS53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -3356,16 +3617,20 @@
       <c r="AC54" s="2" t="n"/>
       <c r="AD54" s="2" t="n"/>
       <c r="AE54" s="2" t="n"/>
-      <c r="AF54" s="4" t="n"/>
-      <c r="AG54" s="4" t="n"/>
-      <c r="AH54" s="2" t="n"/>
-      <c r="AI54" s="2" t="n"/>
-      <c r="AJ54" s="4" t="n"/>
-      <c r="AK54" s="4" t="n"/>
-      <c r="AL54" s="2" t="n"/>
-      <c r="AM54" s="2" t="n"/>
-      <c r="AN54" s="2" t="n"/>
-      <c r="AO54" s="2" t="n"/>
+      <c r="AF54" s="2" t="n"/>
+      <c r="AG54" s="2" t="n"/>
+      <c r="AH54" s="4" t="n"/>
+      <c r="AI54" s="4" t="n"/>
+      <c r="AJ54" s="2" t="n"/>
+      <c r="AK54" s="2" t="n"/>
+      <c r="AL54" s="4" t="n"/>
+      <c r="AM54" s="4" t="n"/>
+      <c r="AN54" s="4" t="n"/>
+      <c r="AO54" s="4" t="n"/>
+      <c r="AP54" s="2" t="n"/>
+      <c r="AQ54" s="2" t="n"/>
+      <c r="AR54" s="2" t="n"/>
+      <c r="AS54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -3399,16 +3664,20 @@
       <c r="AC55" s="2" t="n"/>
       <c r="AD55" s="2" t="n"/>
       <c r="AE55" s="2" t="n"/>
-      <c r="AF55" s="4" t="n"/>
-      <c r="AG55" s="4" t="n"/>
-      <c r="AH55" s="2" t="n"/>
-      <c r="AI55" s="2" t="n"/>
-      <c r="AJ55" s="4" t="n"/>
-      <c r="AK55" s="4" t="n"/>
-      <c r="AL55" s="2" t="n"/>
-      <c r="AM55" s="2" t="n"/>
-      <c r="AN55" s="2" t="n"/>
-      <c r="AO55" s="2" t="n"/>
+      <c r="AF55" s="2" t="n"/>
+      <c r="AG55" s="2" t="n"/>
+      <c r="AH55" s="4" t="n"/>
+      <c r="AI55" s="4" t="n"/>
+      <c r="AJ55" s="2" t="n"/>
+      <c r="AK55" s="2" t="n"/>
+      <c r="AL55" s="4" t="n"/>
+      <c r="AM55" s="4" t="n"/>
+      <c r="AN55" s="4" t="n"/>
+      <c r="AO55" s="4" t="n"/>
+      <c r="AP55" s="2" t="n"/>
+      <c r="AQ55" s="2" t="n"/>
+      <c r="AR55" s="2" t="n"/>
+      <c r="AS55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -3442,16 +3711,20 @@
       <c r="AC56" s="2" t="n"/>
       <c r="AD56" s="2" t="n"/>
       <c r="AE56" s="2" t="n"/>
-      <c r="AF56" s="4" t="n"/>
-      <c r="AG56" s="4" t="n"/>
-      <c r="AH56" s="2" t="n"/>
-      <c r="AI56" s="2" t="n"/>
-      <c r="AJ56" s="4" t="n"/>
-      <c r="AK56" s="4" t="n"/>
-      <c r="AL56" s="2" t="n"/>
-      <c r="AM56" s="2" t="n"/>
-      <c r="AN56" s="2" t="n"/>
-      <c r="AO56" s="2" t="n"/>
+      <c r="AF56" s="2" t="n"/>
+      <c r="AG56" s="2" t="n"/>
+      <c r="AH56" s="4" t="n"/>
+      <c r="AI56" s="4" t="n"/>
+      <c r="AJ56" s="2" t="n"/>
+      <c r="AK56" s="2" t="n"/>
+      <c r="AL56" s="4" t="n"/>
+      <c r="AM56" s="4" t="n"/>
+      <c r="AN56" s="4" t="n"/>
+      <c r="AO56" s="4" t="n"/>
+      <c r="AP56" s="2" t="n"/>
+      <c r="AQ56" s="2" t="n"/>
+      <c r="AR56" s="2" t="n"/>
+      <c r="AS56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -3485,16 +3758,20 @@
       <c r="AC57" s="2" t="n"/>
       <c r="AD57" s="2" t="n"/>
       <c r="AE57" s="2" t="n"/>
-      <c r="AF57" s="4" t="n"/>
-      <c r="AG57" s="4" t="n"/>
-      <c r="AH57" s="2" t="n"/>
-      <c r="AI57" s="2" t="n"/>
-      <c r="AJ57" s="4" t="n"/>
-      <c r="AK57" s="4" t="n"/>
-      <c r="AL57" s="2" t="n"/>
-      <c r="AM57" s="2" t="n"/>
-      <c r="AN57" s="2" t="n"/>
-      <c r="AO57" s="2" t="n"/>
+      <c r="AF57" s="2" t="n"/>
+      <c r="AG57" s="2" t="n"/>
+      <c r="AH57" s="4" t="n"/>
+      <c r="AI57" s="4" t="n"/>
+      <c r="AJ57" s="2" t="n"/>
+      <c r="AK57" s="2" t="n"/>
+      <c r="AL57" s="4" t="n"/>
+      <c r="AM57" s="4" t="n"/>
+      <c r="AN57" s="4" t="n"/>
+      <c r="AO57" s="4" t="n"/>
+      <c r="AP57" s="2" t="n"/>
+      <c r="AQ57" s="2" t="n"/>
+      <c r="AR57" s="2" t="n"/>
+      <c r="AS57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -3528,16 +3805,20 @@
       <c r="AC58" s="2" t="n"/>
       <c r="AD58" s="2" t="n"/>
       <c r="AE58" s="2" t="n"/>
-      <c r="AF58" s="4" t="n"/>
-      <c r="AG58" s="4" t="n"/>
-      <c r="AH58" s="2" t="n"/>
-      <c r="AI58" s="2" t="n"/>
-      <c r="AJ58" s="4" t="n"/>
-      <c r="AK58" s="4" t="n"/>
-      <c r="AL58" s="2" t="n"/>
-      <c r="AM58" s="2" t="n"/>
-      <c r="AN58" s="2" t="n"/>
-      <c r="AO58" s="2" t="n"/>
+      <c r="AF58" s="2" t="n"/>
+      <c r="AG58" s="2" t="n"/>
+      <c r="AH58" s="4" t="n"/>
+      <c r="AI58" s="4" t="n"/>
+      <c r="AJ58" s="2" t="n"/>
+      <c r="AK58" s="2" t="n"/>
+      <c r="AL58" s="4" t="n"/>
+      <c r="AM58" s="4" t="n"/>
+      <c r="AN58" s="4" t="n"/>
+      <c r="AO58" s="4" t="n"/>
+      <c r="AP58" s="2" t="n"/>
+      <c r="AQ58" s="2" t="n"/>
+      <c r="AR58" s="2" t="n"/>
+      <c r="AS58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -3571,16 +3852,20 @@
       <c r="AC59" s="2" t="n"/>
       <c r="AD59" s="2" t="n"/>
       <c r="AE59" s="2" t="n"/>
-      <c r="AF59" s="4" t="n"/>
-      <c r="AG59" s="4" t="n"/>
-      <c r="AH59" s="2" t="n"/>
-      <c r="AI59" s="2" t="n"/>
-      <c r="AJ59" s="4" t="n"/>
-      <c r="AK59" s="4" t="n"/>
-      <c r="AL59" s="2" t="n"/>
-      <c r="AM59" s="2" t="n"/>
-      <c r="AN59" s="2" t="n"/>
-      <c r="AO59" s="2" t="n"/>
+      <c r="AF59" s="2" t="n"/>
+      <c r="AG59" s="2" t="n"/>
+      <c r="AH59" s="4" t="n"/>
+      <c r="AI59" s="4" t="n"/>
+      <c r="AJ59" s="2" t="n"/>
+      <c r="AK59" s="2" t="n"/>
+      <c r="AL59" s="4" t="n"/>
+      <c r="AM59" s="4" t="n"/>
+      <c r="AN59" s="4" t="n"/>
+      <c r="AO59" s="4" t="n"/>
+      <c r="AP59" s="2" t="n"/>
+      <c r="AQ59" s="2" t="n"/>
+      <c r="AR59" s="2" t="n"/>
+      <c r="AS59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -3614,221 +3899,198 @@
       <c r="AC60" s="2" t="n"/>
       <c r="AD60" s="2" t="n"/>
       <c r="AE60" s="2" t="n"/>
-      <c r="AF60" s="4" t="n"/>
-      <c r="AG60" s="4" t="n"/>
-      <c r="AH60" s="2" t="n"/>
-      <c r="AI60" s="2" t="n"/>
-      <c r="AJ60" s="4" t="n"/>
-      <c r="AK60" s="4" t="n"/>
-      <c r="AL60" s="2" t="n"/>
-      <c r="AM60" s="2" t="n"/>
-      <c r="AN60" s="2" t="n"/>
-      <c r="AO60" s="2" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="n"/>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="n"/>
-      <c r="M61" s="3" t="n"/>
-      <c r="N61" s="2" t="n"/>
-      <c r="O61" s="2" t="n"/>
-      <c r="P61" s="2" t="n"/>
-      <c r="Q61" s="2" t="n"/>
-      <c r="R61" s="2" t="n"/>
-      <c r="S61" s="2" t="n"/>
-      <c r="T61" s="2" t="n"/>
-      <c r="U61" s="2" t="n"/>
-      <c r="V61" s="2" t="n"/>
-      <c r="W61" s="2" t="n"/>
-      <c r="X61" s="2" t="n"/>
-      <c r="Y61" s="2" t="n"/>
-      <c r="Z61" s="2" t="n"/>
-      <c r="AA61" s="2" t="n"/>
-      <c r="AB61" s="2" t="n"/>
-      <c r="AC61" s="2" t="n"/>
-      <c r="AD61" s="2" t="n"/>
-      <c r="AE61" s="2" t="n"/>
-      <c r="AF61" s="4" t="n"/>
-      <c r="AG61" s="4" t="n"/>
-      <c r="AH61" s="2" t="n"/>
-      <c r="AI61" s="2" t="n"/>
-      <c r="AJ61" s="4" t="n"/>
-      <c r="AK61" s="4" t="n"/>
-      <c r="AL61" s="2" t="n"/>
-      <c r="AM61" s="2" t="n"/>
-      <c r="AN61" s="2" t="n"/>
-      <c r="AO61" s="2" t="n"/>
+      <c r="AF60" s="2" t="n"/>
+      <c r="AG60" s="2" t="n"/>
+      <c r="AH60" s="4" t="n"/>
+      <c r="AI60" s="4" t="n"/>
+      <c r="AJ60" s="2" t="n"/>
+      <c r="AK60" s="2" t="n"/>
+      <c r="AL60" s="4" t="n"/>
+      <c r="AM60" s="4" t="n"/>
+      <c r="AN60" s="4" t="n"/>
+      <c r="AO60" s="4" t="n"/>
+      <c r="AP60" s="2" t="n"/>
+      <c r="AQ60" s="2" t="n"/>
+      <c r="AR60" s="2" t="n"/>
+      <c r="AS60" s="2" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AG2:AG61">
+  <conditionalFormatting sqref="AI2:AI60">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND(AG2&lt;&gt;"",NOT(OR(UPPER(AG2)="DC",AND(ISNUMBER(AG2),AG2&gt;=1,AG2&lt;=IF(AF2="",10,MIN(10,400/AF2))))))</formula>
+      <formula>AND(AI2&lt;&gt;"",NOT(OR(UPPER(AI2)="DC",AND(ISNUMBER(AI2),AI2&gt;=1,AI2&lt;=IF(AH2="",10,MIN(10,400/AH2))))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK2:AK61">
+  <conditionalFormatting sqref="AM2:AM60">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>AND(ISNUMBER(AK2),ISNUMBER(AJ2),OR(AK2&lt;1.6*AJ2,AK2&gt;100-1.6*AJ2))</formula>
+      <formula>AND(ISNUMBER(AM2),ISNUMBER(AL2),OR(AM2&lt;1.6*AL2,AM2&gt;100-1.6*AL2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="41">
-    <dataValidation sqref="A2:A61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행" promptTitle="#" prompt="단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행" type="custom">
+  <dataValidations count="45">
+    <dataValidation sqref="A2:A60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행" promptTitle="#" prompt="단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행" type="custom">
       <formula1>IF(ISNUMBER(A2),AND(A2&gt;=1,A2&lt;=999,A2=INT(A2)),LOWER(A2)="test")</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:B61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="공정 이름(로그·챗·CSV에 표시). 대기 행은 'delay' 등 자유" promptTitle="Process_name" prompt="공정 이름(로그·챗·CSV에 표시). 대기 행은 'delay' 등 자유" type="textLength" errorStyle="information">
+    <dataValidation sqref="B2:B60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="공정 이름(로그·챗·CSV에 표시). 대기 행은 'delay' 등 자유" promptTitle="Process_name" prompt="공정 이름(로그·챗·CSV에 표시). 대기 행은 'delay' 등 자유" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="C2:C61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="대기 행 전용. 숫자=분(20), 또는 90s / 10m / 1h30m. 공정 행은 비움" promptTitle="delay [분]" prompt="대기 행 전용. 숫자=분(20), 또는 90s / 10m / 1h30m. 공정 행은 비움" type="textLength" errorStyle="information">
+    <dataValidation sqref="C2:C60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="대기 행 전용. 숫자=분(20), 또는 90s / 10m / 1h30m. 공정 행은 비움" promptTitle="delay [분]" prompt="대기 행 전용. 숫자=분(20), 또는 90s / 10m / 1h30m. 공정 행은 비움" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="D2:D61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="up / mid / down. 공란=이동 안 함" promptTitle="chuck_position" prompt="up / mid / down. 공란=이동 안 함" type="list">
+    <dataValidation sqref="D2:D60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="up / mid / down. 공란=이동 안 함" promptTitle="chuck_position" prompt="up / mid / down. 공란=이동 안 함" type="list">
       <formula1>"up,mid,down"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=메인 셔터 사용" promptTitle="main_shutter [T/F]" prompt="T=메인 셔터 사용" type="list">
+    <dataValidation sqref="E2:E60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=메인 셔터 사용" promptTitle="main_shutter [T/F]" prompt="T=메인 셔터 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="OES 적분시간(정수, ≥1)" promptTitle="integration_time [ms]" prompt="OES 적분시간(정수, ≥1)" type="whole">
+    <dataValidation sqref="F2:F60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="OES 적분시간(정수, ≥1)" promptTitle="integration_time [ms]" prompt="OES 적분시간(정수, ≥1)" type="whole">
       <formula1>1</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="G2:G61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=Ar 사용" promptTitle="Ar [T/F]" prompt="T=Ar 사용" type="list">
+    <dataValidation sqref="G2:G60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=Ar 사용" promptTitle="Ar [T/F]" prompt="T=Ar 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=O2 사용" promptTitle="O2 [T/F]" prompt="T=O2 사용" type="list">
+    <dataValidation sqref="H2:H60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=O2 사용" promptTitle="O2 [T/F]" prompt="T=O2 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=N2 사용" promptTitle="N2 [T/F]" prompt="T=N2 사용" type="list">
+    <dataValidation sqref="I2:I60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=N2 사용" promptTitle="N2 [T/F]" prompt="T=N2 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="Ar 유량(≥0)" promptTitle="Ar_flow [sccm]" prompt="Ar 유량(≥0)" type="decimal">
+    <dataValidation sqref="J2:J60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="Ar 유량(≥0)" promptTitle="Ar_flow [sccm]" prompt="Ar 유량(≥0)" type="decimal">
       <formula1>0</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="K2:K61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="O2 유량(≥0)" promptTitle="O2_flow [sccm]" prompt="O2 유량(≥0)" type="decimal">
+    <dataValidation sqref="K2:K60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="O2 유량(≥0)" promptTitle="O2_flow [sccm]" prompt="O2 유량(≥0)" type="decimal">
       <formula1>0</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="N2 유량(≥0)" promptTitle="N2_flow [sccm]" prompt="N2 유량(≥0)" type="decimal">
+    <dataValidation sqref="L2:L60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="N2 유량(≥0)" promptTitle="N2_flow [sccm]" prompt="N2 유량(≥0)" type="decimal">
       <formula1>0</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="M2:M61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="베이스 압력 도달 기준(예 7.00E-06)" promptTitle="base_pressure [Torr]" prompt="베이스 압력 도달 기준(예 7.00E-06)" type="decimal">
+    <dataValidation sqref="M2:M60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="베이스 압력 도달 기준(예 7.00E-06)" promptTitle="base_pressure [Torr]" prompt="베이스 압력 도달 기준(예 7.00E-06)" type="decimal">
       <formula1>0.000000001</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation sqref="N2:N61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="공정 압력(&gt;0)" promptTitle="working_pressure [mTorr]" prompt="공정 압력(&gt;0)" type="decimal">
+    <dataValidation sqref="N2:N60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="공정 압력(&gt;0)" promptTitle="working_pressure [mTorr]" prompt="공정 압력(&gt;0)" type="decimal">
       <formula1>0.001</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="O2:O61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="프리스퍼터(셔터 닫힌 채 방전) 시간, 분" promptTitle="shutter_delay [min]" prompt="프리스퍼터(셔터 닫힌 채 방전) 시간, 분" type="decimal">
+    <dataValidation sqref="O2:O60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="프리스퍼터(셔터 닫힌 채 방전) 시간, 분" promptTitle="shutter_delay [min]" prompt="프리스퍼터(셔터 닫힌 채 방전) 시간, 분" type="decimal">
       <formula1>0</formula1>
       <formula2>10000</formula2>
     </dataValidation>
-    <dataValidation sqref="P2:P61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="메인 공정(셔터 열림) 시간, 분" promptTitle="process_time [min]" prompt="메인 공정(셔터 열림) 시간, 분" type="decimal">
+    <dataValidation sqref="P2:P60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="메인 공정(셔터 열림) 시간, 분" promptTitle="process_time [min]" prompt="메인 공정(셔터 열림) 시간, 분" type="decimal">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="Q2:Q61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G1 사용" promptTitle="gun1 [T/F]" prompt="T=G1 사용" type="list">
+    <dataValidation sqref="S2:S60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G1 사용" promptTitle="gun1 [T/F]" prompt="T=G1 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G2 사용" promptTitle="gun2 [T/F]" prompt="T=G2 사용" type="list">
+    <dataValidation sqref="T2:T60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G2 사용" promptTitle="gun2 [T/F]" prompt="T=G2 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G3 사용" promptTitle="gun3 [T/F]" prompt="T=G3 사용" type="list">
+    <dataValidation sqref="U2:U60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G3 사용" promptTitle="gun3 [T/F]" prompt="T=G3 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G1 타겟 이름(재고 DB 이름과 동일하게)" promptTitle="G1 Target" prompt="G1 타겟 이름(재고 DB 이름과 동일하게)" type="textLength" errorStyle="information">
+    <dataValidation sqref="V2:V60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G1 타겟 이름(재고 DB 이름과 동일하게)" promptTitle="G1 Target" prompt="G1 타겟 이름(재고 DB 이름과 동일하게)" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="U2:U61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G2 타겟 이름" promptTitle="G2 Target" prompt="G2 타겟 이름" type="textLength" errorStyle="information">
+    <dataValidation sqref="W2:W60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G2 타겟 이름" promptTitle="G2 Target" prompt="G2 타겟 이름" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="V2:V61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G3 타겟 이름" promptTitle="G3 Target" prompt="G3 타겟 이름" type="textLength" errorStyle="information">
+    <dataValidation sqref="X2:X60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G3 타겟 이름" promptTitle="G3 Target" prompt="G3 타겟 이름" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="W2:W61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])" promptTitle="power_select [T/F]" prompt="RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])" type="list">
+    <dataValidation sqref="Y2:Y60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])" promptTitle="power_select [T/F]" prompt="RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="X2:X61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=DC1 연속 파워 사용" promptTitle="use_dc_power [T/F]" prompt="T=DC1 연속 파워 사용" type="list">
+    <dataValidation sqref="Z2:Z60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=DC1 연속 파워 사용" promptTitle="use_dc_power [T/F]" prompt="T=DC1 연속 파워 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="Y2:Y61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC1 설정 파워(&gt;0)" promptTitle="dc_power [W]" prompt="DC1 설정 파워(&gt;0)" type="decimal">
+    <dataValidation sqref="AA2:AA60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC1 설정 파워(&gt;0)" promptTitle="dc_power [W]" prompt="DC1 설정 파워(&gt;0)" type="decimal">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="Z2:Z61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" promptTitle="use_dc_power2 [T/F]" prompt="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" type="list">
+    <dataValidation sqref="AB2:AB60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" promptTitle="use_dc_power2 [T/F]" prompt="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" type="list">
       <formula1>"F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA2:AA61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 비워 두세요" promptTitle="dc_power2 [W]" prompt="DC2 폐지 — 비워 두세요" type="decimal">
+    <dataValidation sqref="AC2:AC60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 비워 두세요" promptTitle="dc_power2 [W]" prompt="DC2 폐지 — 비워 두세요" type="decimal">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="AB2:AB61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=RF 연속 파워 사용" promptTitle="use_rf_power [T/F]" prompt="T=RF 연속 파워 사용" type="list">
+    <dataValidation sqref="AD2:AD60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=RF 연속 파워 사용" promptTitle="use_rf_power [T/F]" prompt="T=RF 연속 파워 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF 설정 파워(&gt;0)" promptTitle="rf_power [W]" prompt="RF 설정 파워(&gt;0)" type="decimal">
+    <dataValidation sqref="AE2:AE60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF 설정 파워(&gt;0)" promptTitle="rf_power [W]" prompt="RF 설정 파워(&gt;0)" type="decimal">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="AD2:AD61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨" promptTitle="use_dc_pulse [T/F]" prompt="T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨" type="list">
+    <dataValidation sqref="AF2:AF60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨" promptTitle="use_dc_pulse [T/F]" prompt="T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AE2:AE61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)" promptTitle="dc_pulse_power [W]" prompt="DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)" type="decimal">
+    <dataValidation sqref="AG2:AG60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)" promptTitle="dc_pulse_power [W]" prompt="DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)" type="decimal">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="AF2:AF61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지" promptTitle="dc_pulse_freq [kHz]" prompt="정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지" type="whole">
+    <dataValidation sqref="AH2:AH60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지" promptTitle="dc_pulse_freq [kHz]" prompt="정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지" type="whole">
       <formula1>20</formula1>
       <formula2>150</formula2>
     </dataValidation>
-    <dataValidation sqref="AG2:AG61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지" promptTitle="dc_pulse_off_time [us]" prompt="Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지" type="custom">
-      <formula1>OR(UPPER(AG2)="DC",AND(ISNUMBER(AG2),AG2&gt;=1,AG2&lt;=IF(AF2="",10,MIN(10,400/AF2))))</formula1>
+    <dataValidation sqref="AI2:AI60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지" promptTitle="dc_pulse_off_time [us]" prompt="Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지" type="custom">
+      <formula1>OR(UPPER(AI2)="DC",AND(ISNUMBER(AI2),AI2&gt;=1,AI2&lt;=IF(AH2="",10,MIN(10,400/AH2))))</formula1>
     </dataValidation>
-    <dataValidation sqref="AH2:AH61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨" promptTitle="use_rf_pulse [T/F]" prompt="T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨" type="list">
+    <dataValidation sqref="AJ2:AJ60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨" promptTitle="use_rf_pulse [T/F]" prompt="T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AI2:AI61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF Pulse 설정 파워 1~1000" promptTitle="rf_pulse_power [W]" prompt="RF Pulse 설정 파워 1~1000" type="decimal">
+    <dataValidation sqref="AK2:AK60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF Pulse 설정 파워 1~1000" promptTitle="rf_pulse_power [W]" prompt="RF Pulse 설정 파워 1~1000" type="decimal">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="AJ2:AJ61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지" promptTitle="rf_pulse_freq [kHz]" prompt="0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지" type="decimal">
+    <dataValidation sqref="AL2:AL60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지" promptTitle="rf_pulse_freq [kHz]" prompt="0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지" type="decimal">
       <formula1>0.001</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="AK2:AK61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)" promptTitle="rf_pulse_duty_cycle [%]" prompt="정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)" type="whole">
+    <dataValidation sqref="AM2:AM60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)" promptTitle="rf_pulse_duty_cycle [%]" prompt="정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)" type="whole">
       <formula1>1</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation sqref="AL2:AL61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" promptTitle="use_heater [T/F]" prompt="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" type="list">
+    <dataValidation sqref="AP2:AP60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" promptTitle="use_heater [T/F]" prompt="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AM2:AM61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" promptTitle="heater_temp [°C]" prompt="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" type="decimal">
+    <dataValidation sqref="AQ2:AQ60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" promptTitle="heater_temp [°C]" prompt="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" type="decimal">
       <formula1>1</formula1>
       <formula2>900</formula2>
     </dataValidation>
-    <dataValidation sqref="AN2:AN61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)" promptTitle="heater_ramp [°C/min]" prompt="RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)" type="decimal">
+    <dataValidation sqref="AR2:AR60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)" promptTitle="heater_ramp [°C/min]" prompt="RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)" type="decimal">
       <formula1>0.1</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation sqref="AO2:AO61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" promptTitle="heater_soak [min]" prompt="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" type="decimal">
+    <dataValidation sqref="AS2:AS60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" promptTitle="heater_soak [min]" prompt="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" type="decimal">
       <formula1>0</formula1>
       <formula2>480</formula2>
     </dataValidation>
+    <dataValidation sqref="Q2:Q60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="증착률(&gt;0). thickness 를 쓰면 필수 — Thickness 모드 예상시간·안전 상한·시간 대체 계산용, Time 모드는 process_time 이 비었을 때 thickness÷dep_rate 로 시간을 계산" promptTitle="dep_rate [nm/s]" prompt="증착률(&gt;0). thickness 를 쓰면 필수 — Thickness 모드 예상시간·안전 상한·시간 대체 계산용, Time 모드는 process_time 이 비었을 때 thickness÷dep_rate 로 시간을 계산" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+    <dataValidation sqref="R2:R60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="목표 두께(&gt;0). CH2 두께 모니터가 켜져 있으면 Thickness 모드 — 목표 두께에 닿으면 메인 공정 종료(process_time 이 비었으면 thickness÷dep_rate 를 예상시간으로 자동 계산). 건 1개만, chuck×건 Factor 필요. CH1·모니터 없음은 지금처럼 thickness÷dep_rate 시간 종료" promptTitle="thickness [nm]" prompt="목표 두께(&gt;0). CH2 두께 모니터가 켜져 있으면 Thickness 모드 — 목표 두께에 닿으면 메인 공정 종료(process_time 이 비었으면 thickness÷dep_rate 를 예상시간으로 자동 계산). 건 1개만, chuck×건 Factor 필요. CH1·모니터 없음은 지금처럼 thickness÷dep_rate 시간 종료" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>100000</formula2>
+    </dataValidation>
+    <dataValidation sqref="AN2:AN60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)" promptTitle="power_change_time" prompt="중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)" type="textLength" operator="between">
+      <formula1>0</formula1>
+      <formula2>200</formula2>
+    </dataValidation>
+    <dataValidation sqref="AO2:AO60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용" promptTitle="change_power_value [W]" prompt="그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용" type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -3839,7 +4101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" style="9" min="1" max="1"/>
@@ -3916,7 +4178,7 @@
       </c>
       <c r="D6" s="7" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="25.5" customHeight="1" s="9">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>delay</t>
@@ -4168,46 +4430,54 @@
       </c>
       <c r="D20" s="7" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="25.5" customHeight="1" s="9">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>gun1</t>
+          <t>dep_rate</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>T/F</t>
+          <t>nm/s</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>T=G1 사용</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="n"/>
-    </row>
-    <row r="22">
+          <t>증착률(&gt;0). thickness 를 쓰면 필수 — Thickness 모드 예상시간·안전 상한·시간 대체 계산용, Time 모드는 process_time 이 비었을 때 thickness÷dep_rate 로 시간을 계산</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>0 보다 커야 함. Thickness 모드는 예상시간 = thickness÷dep_rate, 안전 상한 = max(예상×2, 예상+5분)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25.5" customHeight="1" s="9">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>gun2</t>
+          <t>thickness</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>T/F</t>
+          <t>nm</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>T=G2 사용</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n"/>
+          <t>목표 두께(&gt;0). CH2 두께 모니터가 켜져 있으면 Thickness 모드 — 목표 두께에 닿으면 메인 공정 종료(process_time 이 비었으면 thickness÷dep_rate 를 예상시간으로 자동 계산). 건 1개만, chuck×건 Factor 필요. CH1·모니터 없음은 지금처럼 thickness÷dep_rate 시간 종료</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Thickness 모드 거부(E840~E846): 모니터 응답 없음·XTAL FAIL·건 2개 이상·Factor 없음 등. 통신 이상이면 멈추지 않고 시간으로 대체</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>gun3</t>
+          <t>gun1</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -4217,7 +4487,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>T=G3 사용</t>
+          <t>T=G1 사용</t>
         </is>
       </c>
       <c r="D23" s="7" t="n"/>
@@ -4225,13 +4495,17 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>G1 Target</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n"/>
+          <t>gun2</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>G1 타겟 이름(재고 DB 이름과 동일하게)</t>
+          <t>T=G2 사용</t>
         </is>
       </c>
       <c r="D24" s="7" t="n"/>
@@ -4239,13 +4513,17 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>G2 Target</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
+          <t>gun3</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>G2 타겟 이름</t>
+          <t>T=G3 사용</t>
         </is>
       </c>
       <c r="D25" s="7" t="n"/>
@@ -4253,13 +4531,13 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>G3 Target</t>
+          <t>G1 Target</t>
         </is>
       </c>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>G3 타겟 이름</t>
+          <t>G1 타겟 이름(재고 DB 이름과 동일하게)</t>
         </is>
       </c>
       <c r="D26" s="7" t="n"/>
@@ -4267,39 +4545,27 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>power_select</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>T/F</t>
-        </is>
-      </c>
+          <t>G2 Target</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>DC Pulse와 함께 T이면 과전류(8/25 사고)</t>
-        </is>
-      </c>
+          <t>G2 타겟 이름</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>use_dc_power</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>T/F</t>
-        </is>
-      </c>
+          <t>G3 Target</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>T=DC1 연속 파워 사용</t>
+          <t>G3 타겟 이름</t>
         </is>
       </c>
       <c r="D28" s="7" t="n"/>
@@ -4307,25 +4573,29 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>dc_power</t>
+          <t>power_select</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>T/F</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>DC1 설정 파워(&gt;0)</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n"/>
+          <t>RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>DC Pulse와 함께 T이면 과전류(8/25 사고)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>use_dc_power2</t>
+          <t>use_dc_power</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -4335,19 +4605,15 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>2026-10 CH2 히터 추가로 D/A CH3 를 히터가 씀</t>
-        </is>
-      </c>
+          <t>T=DC1 연속 파워 사용</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>dc_power2</t>
+          <t>dc_power</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -4357,7 +4623,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>DC2 폐지 — 비워 두세요</t>
+          <t>DC1 설정 파워(&gt;0)</t>
         </is>
       </c>
       <c r="D31" s="7" t="n"/>
@@ -4365,7 +4631,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>use_rf_power</t>
+          <t>use_dc_power2</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -4375,15 +4641,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>T=RF 연속 파워 사용</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n"/>
+          <t>DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10 CH2 히터 추가로 D/A CH3 를 히터가 씀</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>rf_power</t>
+          <t>dc_power2</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -4393,7 +4663,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>RF 설정 파워(&gt;0)</t>
+          <t>DC2 폐지 — 비워 두세요</t>
         </is>
       </c>
       <c r="D33" s="7" t="n"/>
@@ -4401,7 +4671,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>use_dc_pulse</t>
+          <t>use_rf_power</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -4411,7 +4681,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨</t>
+          <t>T=RF 연속 파워 사용</t>
         </is>
       </c>
       <c r="D34" s="7" t="n"/>
@@ -4419,7 +4689,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>dc_pulse_power</t>
+          <t>rf_power</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -4429,7 +4699,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)</t>
+          <t>RF 설정 파워(&gt;0)</t>
         </is>
       </c>
       <c r="D35" s="7" t="n"/>
@@ -4437,97 +4707,97 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>dc_pulse_freq</t>
+          <t>use_dc_pulse</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>kHz</t>
+          <t>T/F</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>20 kHz → Off 최대 10.0 / 50 kHz → 8.0 / 100 kHz → 4.0 µs</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25.5" customHeight="1" s="9">
+          <t>T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n"/>
+    </row>
+    <row r="37" s="9">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>dc_pulse_off_time</t>
+          <t>dc_pulse_power</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>EnerPulse는 듀티가 아니라 Off Time(µs)을 설정값으로 씀. 듀티 = 1 − Off×kHz/1000</t>
-        </is>
-      </c>
+          <t>DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>use_rf_pulse</t>
+          <t>dc_pulse_freq</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>T/F</t>
+          <t>kHz</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="n"/>
-    </row>
-    <row r="39">
+          <t>정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>20 kHz → Off 최대 10.0 / 50 kHz → 8.0 / 100 kHz → 4.0 µs</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="25.5" customHeight="1" s="9">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>rf_pulse_power</t>
+          <t>dc_pulse_off_time</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>us</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>RF Pulse 설정 파워 1~1000</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n"/>
+          <t>Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>EnerPulse는 듀티가 아니라 Off Time(µs)을 설정값으로 씀. 듀티 = 1 − Off×kHz/1000</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>rf_pulse_freq</t>
+          <t>use_rf_pulse</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>kHz</t>
+          <t>T/F</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지</t>
+          <t>T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨</t>
         </is>
       </c>
       <c r="D40" s="7" t="n"/>
@@ -4535,108 +4805,184 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
+          <t>rf_pulse_power</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>RF Pulse 설정 파워 1~1000</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n"/>
+    </row>
+    <row r="42" s="9">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>rf_pulse_freq</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>kHz</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n"/>
+    </row>
+    <row r="43" s="9">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
           <t>rf_pulse_duty_cycle</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>범위 밖이면 장비가 CSR 51로 거부함</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="25.5" customHeight="1" s="9">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>use_heater</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>T/F</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>다음 공정 행도 use_heater=T 면 히터를 켠 채 넘어가고, 아니면 공정이 끝날 때 끈다</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="25.5" customHeight="1" s="9">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>heater_temp</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>목표 ±2°C 안에 60초 머물면 도달로 본다(HEATER_SOAK_*). 그 뒤 대기는 heater_soak</t>
         </is>
       </c>
     </row>
     <row r="44" ht="25.5" customHeight="1" s="9">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>heater_ramp</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>°C/min</t>
-        </is>
-      </c>
+          <t>power_change_time</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n"/>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)</t>
+          <t>중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>목표 20°C 앞부터 감속해 1°C/min 로 도착(HEATER_APPROACH_*)</t>
+          <t>Shutter Delay 안 변경은 Thickness 모드에서도 가능. 메인 구간 안이면 E844 로 시작 거부</t>
         </is>
       </c>
     </row>
     <row r="45" ht="25.5" customHeight="1" s="9">
       <c r="A45" s="7" t="inlineStr">
         <is>
+          <t>change_power_value</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>DC/RF Pulse 를 동시에 쓰면 DC 우선</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25.5" customHeight="1" s="9">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>use_heater</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>다음 공정 행도 use_heater=T 면 히터를 켠 채 넘어가고, 아니면 공정이 끝날 때 끈다</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25.5" customHeight="1" s="9">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>heater_temp</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>목표 ±2°C 안에 60초 머물면 도달로 본다(HEATER_SOAK_*). 그 뒤 대기는 heater_soak</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="25.5" customHeight="1" s="9">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>heater_ramp</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>°C/min</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>목표 20°C 앞부터 감속해 1°C/min 로 도착(HEATER_APPROACH_*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="25.5" customHeight="1" s="9">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
           <t>heater_soak</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>SOAK 중에도 히터 이상·꺼짐·출력 무응답/끊김이면 공정 중단. ±2°C 밖으로 나가면 로그·도달 카드에 기록만. 행마다 따로 적용</t>
         </is>

--- a/recipes/Recipe_Template.xlsx
+++ b/recipes/Recipe_Template.xlsx
@@ -321,157 +321,174 @@
     </comment>
     <comment ref="S1" authorId="0" shapeId="0">
       <text>
+        <t>단위: %
+Thickness 모드에서만 사용. 두께 모니터 tooling(10.0~399). 값이 있으면 레시피 값, 비우면 Factor 팝업의 chuck×건 tooling. Time 모드(thickness 비움)는 무시</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>단위: g/cm3
+Thickness 모드에서만 사용. 재료 밀도(0.500~99.99). 값이 있으면 레시피 값, 비우면 Factor 팝업에서 고른 건 재료의 density. Time 모드는 무시</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Thickness 모드에서만 사용. 재료 Z-factor(0.100~9.999). 값이 있으면 레시피 값, 비우면 Factor 팝업에서 고른 건 재료의 Z. Time 모드는 무시</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
         <t>단위: T/F
 T=G1 사용</t>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=G2 사용</t>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=G3 사용</t>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>G1 타겟 이름(재고 DB 이름과 동일하게)</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>G2 타겟 이름</t>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0">
+    <comment ref="AA1" authorId="0" shapeId="0">
       <text>
         <t>G3 타겟 이름</t>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0">
+    <comment ref="AB1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])</t>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0">
+    <comment ref="AC1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=DC1 연속 파워 사용</t>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0">
+    <comment ref="AD1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 DC1 설정 파워(&gt;0)</t>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0">
+    <comment ref="AE1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력</t>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0">
+    <comment ref="AF1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 DC2 폐지 — 비워 두세요</t>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0">
+    <comment ref="AG1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=RF 연속 파워 사용</t>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0" shapeId="0">
+    <comment ref="AH1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 RF 설정 파워(&gt;0)</t>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0" shapeId="0">
+    <comment ref="AI1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨</t>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)</t>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
         <t>단위: kHz
 정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지</t>
       </text>
     </comment>
-    <comment ref="AI1" authorId="0" shapeId="0">
+    <comment ref="AL1" authorId="0" shapeId="0">
       <text>
         <t>단위: us
 Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지</t>
       </text>
     </comment>
-    <comment ref="AJ1" authorId="0" shapeId="0">
+    <comment ref="AM1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨</t>
       </text>
     </comment>
-    <comment ref="AK1" authorId="0" shapeId="0">
+    <comment ref="AN1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 RF Pulse 설정 파워 1~1000</t>
       </text>
     </comment>
-    <comment ref="AL1" authorId="0" shapeId="0">
+    <comment ref="AO1" authorId="0" shapeId="0">
       <text>
         <t>단위: kHz
 0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지</t>
       </text>
     </comment>
-    <comment ref="AM1" authorId="0" shapeId="0">
+    <comment ref="AP1" authorId="0" shapeId="0">
       <text>
         <t>단위: %
 정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)</t>
       </text>
     </comment>
-    <comment ref="AN1" authorId="0" shapeId="0">
+    <comment ref="AQ1" authorId="0" shapeId="0">
       <text>
         <t>중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)</t>
       </text>
     </comment>
-    <comment ref="AO1" authorId="0" shapeId="0">
+    <comment ref="AR1" authorId="0" shapeId="0">
       <text>
         <t>단위: W
 그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용</t>
       </text>
     </comment>
-    <comment ref="AP1" authorId="0" shapeId="0">
+    <comment ref="AS1" authorId="0" shapeId="0">
       <text>
         <t>단위: T/F
 T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
       </text>
     </comment>
-    <comment ref="AQ1" authorId="0" shapeId="0">
+    <comment ref="AT1" authorId="0" shapeId="0">
       <text>
         <t>단위: °C
 목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수</t>
       </text>
     </comment>
-    <comment ref="AR1" authorId="0" shapeId="0">
+    <comment ref="AU1" authorId="0" shapeId="0">
       <text>
         <t>단위: °C/min
 RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)</t>
       </text>
     </comment>
-    <comment ref="AS1" authorId="0" shapeId="0">
+    <comment ref="AV1" authorId="0" shapeId="0">
       <text>
         <t>단위: min
 도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)</t>
@@ -770,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS60"/>
+  <dimension ref="A1:AV60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="9" min="1" max="1"/>
@@ -791,33 +808,36 @@
     <col width="15" customWidth="1" style="9" min="16" max="16"/>
     <col width="15" customWidth="1" style="9" min="17" max="17"/>
     <col width="15" customWidth="1" style="9" min="18" max="18"/>
-    <col width="9" customWidth="1" style="9" min="19" max="19"/>
-    <col width="9" customWidth="1" style="9" min="20" max="20"/>
-    <col width="9" customWidth="1" style="9" min="21" max="21"/>
-    <col width="12" customWidth="1" style="9" min="22" max="22"/>
-    <col width="12" customWidth="1" style="9" min="23" max="23"/>
-    <col width="12" customWidth="1" style="9" min="24" max="24"/>
-    <col width="15" customWidth="1" style="9" min="25" max="25"/>
-    <col width="15" customWidth="1" style="9" min="26" max="26"/>
-    <col width="11" customWidth="1" style="9" min="27" max="27"/>
-    <col width="16" customWidth="1" style="9" min="28" max="28"/>
-    <col width="12" customWidth="1" style="9" min="29" max="29"/>
-    <col width="15" customWidth="1" style="9" min="30" max="30"/>
-    <col width="11" customWidth="1" style="9" min="31" max="31"/>
-    <col width="15" customWidth="1" style="9" min="32" max="32"/>
-    <col width="17" customWidth="1" style="9" min="33" max="33"/>
-    <col width="16" customWidth="1" style="9" min="34" max="34"/>
-    <col width="20" customWidth="1" style="9" min="35" max="35"/>
-    <col width="15" customWidth="1" style="9" min="36" max="36"/>
-    <col width="17" customWidth="1" style="9" min="37" max="37"/>
-    <col width="16" customWidth="1" style="9" min="38" max="38"/>
-    <col width="22" customWidth="1" style="9" min="39" max="39"/>
-    <col width="22" customWidth="1" style="9" min="40" max="40"/>
-    <col width="22" customWidth="1" style="9" min="41" max="41"/>
-    <col width="13" customWidth="1" style="9" min="42" max="42"/>
-    <col width="13" customWidth="1" style="9" min="43" max="43"/>
-    <col width="13" customWidth="1" style="9" min="44" max="44"/>
+    <col width="15" customWidth="1" style="9" min="19" max="19"/>
+    <col width="15" customWidth="1" style="9" min="20" max="20"/>
+    <col width="15" customWidth="1" style="9" min="21" max="21"/>
+    <col width="9" customWidth="1" style="9" min="22" max="22"/>
+    <col width="9" customWidth="1" style="9" min="23" max="23"/>
+    <col width="9" customWidth="1" style="9" min="24" max="24"/>
+    <col width="12" customWidth="1" style="9" min="25" max="25"/>
+    <col width="12" customWidth="1" style="9" min="26" max="26"/>
+    <col width="12" customWidth="1" style="9" min="27" max="27"/>
+    <col width="15" customWidth="1" style="9" min="28" max="28"/>
+    <col width="15" customWidth="1" style="9" min="29" max="29"/>
+    <col width="11" customWidth="1" style="9" min="30" max="30"/>
+    <col width="16" customWidth="1" style="9" min="31" max="31"/>
+    <col width="12" customWidth="1" style="9" min="32" max="32"/>
+    <col width="15" customWidth="1" style="9" min="33" max="33"/>
+    <col width="11" customWidth="1" style="9" min="34" max="34"/>
+    <col width="15" customWidth="1" style="9" min="35" max="35"/>
+    <col width="17" customWidth="1" style="9" min="36" max="36"/>
+    <col width="16" customWidth="1" style="9" min="37" max="37"/>
+    <col width="20" customWidth="1" style="9" min="38" max="38"/>
+    <col width="15" customWidth="1" style="9" min="39" max="39"/>
+    <col width="17" customWidth="1" style="9" min="40" max="40"/>
+    <col width="16" customWidth="1" style="9" min="41" max="41"/>
+    <col width="22" customWidth="1" style="9" min="42" max="42"/>
+    <col width="22" customWidth="1" style="9" min="43" max="43"/>
+    <col width="22" customWidth="1" style="9" min="44" max="44"/>
     <col width="13" customWidth="1" style="9" min="45" max="45"/>
+    <col width="13" customWidth="1" style="9" min="46" max="46"/>
+    <col width="13" customWidth="1" style="9" min="47" max="47"/>
+    <col width="13" customWidth="1" style="9" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.95" customHeight="1" s="9">
@@ -913,135 +933,150 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>tooling</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>density</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>z_factor</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>gun1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>gun2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>gun3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>G1 Target</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>G2 Target</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>G3 Target</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>power_select</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>use_dc_power</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dc_power</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>use_dc_power2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dc_power2</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>use_rf_power</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>rf_power</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>use_dc_pulse</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dc_pulse_power</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dc_pulse_freq</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>dc_pulse_off_time</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>use_rf_pulse</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_power</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_freq</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>rf_pulse_duty_cycle</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>power_change_time</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>change_power_value</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>use_heater</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>heater_temp</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>heater_ramp</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>heater_soak</t>
         </is>
@@ -1108,83 +1143,86 @@
       </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="n"/>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="n"/>
-      <c r="X2" s="2" t="n"/>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="Y2" s="2" t="n"/>
+      <c r="Z2" s="2" t="n"/>
       <c r="AA2" s="2" t="n"/>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="n"/>
-      <c r="AF2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="n"/>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="n"/>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="n"/>
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AG2" s="2" t="n">
+      <c r="AJ2" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="AH2" s="4" t="n">
+      <c r="AK2" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AI2" s="4" t="n">
+      <c r="AL2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AJ2" s="2" t="inlineStr">
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="AK2" s="2" t="n"/>
-      <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n"/>
+      <c r="AN2" s="2" t="n"/>
       <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="2" t="inlineStr">
+      <c r="AP2" s="4" t="n"/>
+      <c r="AQ2" s="4" t="n"/>
+      <c r="AR2" s="4" t="n"/>
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AQ2" s="2" t="n">
+      <c r="AT2" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="AR2" s="2" t="n">
+      <c r="AU2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AS2" s="2" t="n">
+      <c r="AV2" s="2" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1222,18 +1260,21 @@
       <c r="AE3" s="2" t="n"/>
       <c r="AF3" s="2" t="n"/>
       <c r="AG3" s="2" t="n"/>
-      <c r="AH3" s="4" t="n"/>
-      <c r="AI3" s="4" t="n"/>
+      <c r="AH3" s="2" t="n"/>
+      <c r="AI3" s="2" t="n"/>
       <c r="AJ3" s="2" t="n"/>
-      <c r="AK3" s="2" t="n"/>
+      <c r="AK3" s="4" t="n"/>
       <c r="AL3" s="4" t="n"/>
-      <c r="AM3" s="4" t="n"/>
-      <c r="AN3" s="4" t="n"/>
+      <c r="AM3" s="2" t="n"/>
+      <c r="AN3" s="2" t="n"/>
       <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="2" t="n"/>
-      <c r="AQ3" s="2" t="n"/>
-      <c r="AR3" s="2" t="n"/>
+      <c r="AP3" s="4" t="n"/>
+      <c r="AQ3" s="4" t="n"/>
+      <c r="AR3" s="4" t="n"/>
       <c r="AS3" s="2" t="n"/>
+      <c r="AT3" s="2" t="n"/>
+      <c r="AU3" s="2" t="n"/>
+      <c r="AV3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -1269,18 +1310,21 @@
       <c r="AE4" s="2" t="n"/>
       <c r="AF4" s="2" t="n"/>
       <c r="AG4" s="2" t="n"/>
-      <c r="AH4" s="4" t="n"/>
-      <c r="AI4" s="4" t="n"/>
+      <c r="AH4" s="2" t="n"/>
+      <c r="AI4" s="2" t="n"/>
       <c r="AJ4" s="2" t="n"/>
-      <c r="AK4" s="2" t="n"/>
+      <c r="AK4" s="4" t="n"/>
       <c r="AL4" s="4" t="n"/>
-      <c r="AM4" s="4" t="n"/>
-      <c r="AN4" s="4" t="n"/>
+      <c r="AM4" s="2" t="n"/>
+      <c r="AN4" s="2" t="n"/>
       <c r="AO4" s="4" t="n"/>
-      <c r="AP4" s="2" t="n"/>
-      <c r="AQ4" s="2" t="n"/>
-      <c r="AR4" s="2" t="n"/>
+      <c r="AP4" s="4" t="n"/>
+      <c r="AQ4" s="4" t="n"/>
+      <c r="AR4" s="4" t="n"/>
       <c r="AS4" s="2" t="n"/>
+      <c r="AT4" s="2" t="n"/>
+      <c r="AU4" s="2" t="n"/>
+      <c r="AV4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -1316,18 +1360,21 @@
       <c r="AE5" s="2" t="n"/>
       <c r="AF5" s="2" t="n"/>
       <c r="AG5" s="2" t="n"/>
-      <c r="AH5" s="4" t="n"/>
-      <c r="AI5" s="4" t="n"/>
+      <c r="AH5" s="2" t="n"/>
+      <c r="AI5" s="2" t="n"/>
       <c r="AJ5" s="2" t="n"/>
-      <c r="AK5" s="2" t="n"/>
+      <c r="AK5" s="4" t="n"/>
       <c r="AL5" s="4" t="n"/>
-      <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="n"/>
+      <c r="AM5" s="2" t="n"/>
+      <c r="AN5" s="2" t="n"/>
       <c r="AO5" s="4" t="n"/>
-      <c r="AP5" s="2" t="n"/>
-      <c r="AQ5" s="2" t="n"/>
-      <c r="AR5" s="2" t="n"/>
+      <c r="AP5" s="4" t="n"/>
+      <c r="AQ5" s="4" t="n"/>
+      <c r="AR5" s="4" t="n"/>
       <c r="AS5" s="2" t="n"/>
+      <c r="AT5" s="2" t="n"/>
+      <c r="AU5" s="2" t="n"/>
+      <c r="AV5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -1363,18 +1410,21 @@
       <c r="AE6" s="2" t="n"/>
       <c r="AF6" s="2" t="n"/>
       <c r="AG6" s="2" t="n"/>
-      <c r="AH6" s="4" t="n"/>
-      <c r="AI6" s="4" t="n"/>
+      <c r="AH6" s="2" t="n"/>
+      <c r="AI6" s="2" t="n"/>
       <c r="AJ6" s="2" t="n"/>
-      <c r="AK6" s="2" t="n"/>
+      <c r="AK6" s="4" t="n"/>
       <c r="AL6" s="4" t="n"/>
-      <c r="AM6" s="4" t="n"/>
-      <c r="AN6" s="4" t="n"/>
+      <c r="AM6" s="2" t="n"/>
+      <c r="AN6" s="2" t="n"/>
       <c r="AO6" s="4" t="n"/>
-      <c r="AP6" s="2" t="n"/>
-      <c r="AQ6" s="2" t="n"/>
-      <c r="AR6" s="2" t="n"/>
+      <c r="AP6" s="4" t="n"/>
+      <c r="AQ6" s="4" t="n"/>
+      <c r="AR6" s="4" t="n"/>
       <c r="AS6" s="2" t="n"/>
+      <c r="AT6" s="2" t="n"/>
+      <c r="AU6" s="2" t="n"/>
+      <c r="AV6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1410,18 +1460,21 @@
       <c r="AE7" s="2" t="n"/>
       <c r="AF7" s="2" t="n"/>
       <c r="AG7" s="2" t="n"/>
-      <c r="AH7" s="4" t="n"/>
-      <c r="AI7" s="4" t="n"/>
+      <c r="AH7" s="2" t="n"/>
+      <c r="AI7" s="2" t="n"/>
       <c r="AJ7" s="2" t="n"/>
-      <c r="AK7" s="2" t="n"/>
+      <c r="AK7" s="4" t="n"/>
       <c r="AL7" s="4" t="n"/>
-      <c r="AM7" s="4" t="n"/>
-      <c r="AN7" s="4" t="n"/>
+      <c r="AM7" s="2" t="n"/>
+      <c r="AN7" s="2" t="n"/>
       <c r="AO7" s="4" t="n"/>
-      <c r="AP7" s="2" t="n"/>
-      <c r="AQ7" s="2" t="n"/>
-      <c r="AR7" s="2" t="n"/>
+      <c r="AP7" s="4" t="n"/>
+      <c r="AQ7" s="4" t="n"/>
+      <c r="AR7" s="4" t="n"/>
       <c r="AS7" s="2" t="n"/>
+      <c r="AT7" s="2" t="n"/>
+      <c r="AU7" s="2" t="n"/>
+      <c r="AV7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1457,18 +1510,21 @@
       <c r="AE8" s="2" t="n"/>
       <c r="AF8" s="2" t="n"/>
       <c r="AG8" s="2" t="n"/>
-      <c r="AH8" s="4" t="n"/>
-      <c r="AI8" s="4" t="n"/>
+      <c r="AH8" s="2" t="n"/>
+      <c r="AI8" s="2" t="n"/>
       <c r="AJ8" s="2" t="n"/>
-      <c r="AK8" s="2" t="n"/>
+      <c r="AK8" s="4" t="n"/>
       <c r="AL8" s="4" t="n"/>
-      <c r="AM8" s="4" t="n"/>
-      <c r="AN8" s="4" t="n"/>
+      <c r="AM8" s="2" t="n"/>
+      <c r="AN8" s="2" t="n"/>
       <c r="AO8" s="4" t="n"/>
-      <c r="AP8" s="2" t="n"/>
-      <c r="AQ8" s="2" t="n"/>
-      <c r="AR8" s="2" t="n"/>
+      <c r="AP8" s="4" t="n"/>
+      <c r="AQ8" s="4" t="n"/>
+      <c r="AR8" s="4" t="n"/>
       <c r="AS8" s="2" t="n"/>
+      <c r="AT8" s="2" t="n"/>
+      <c r="AU8" s="2" t="n"/>
+      <c r="AV8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1504,18 +1560,21 @@
       <c r="AE9" s="2" t="n"/>
       <c r="AF9" s="2" t="n"/>
       <c r="AG9" s="2" t="n"/>
-      <c r="AH9" s="4" t="n"/>
-      <c r="AI9" s="4" t="n"/>
+      <c r="AH9" s="2" t="n"/>
+      <c r="AI9" s="2" t="n"/>
       <c r="AJ9" s="2" t="n"/>
-      <c r="AK9" s="2" t="n"/>
+      <c r="AK9" s="4" t="n"/>
       <c r="AL9" s="4" t="n"/>
-      <c r="AM9" s="4" t="n"/>
-      <c r="AN9" s="4" t="n"/>
+      <c r="AM9" s="2" t="n"/>
+      <c r="AN9" s="2" t="n"/>
       <c r="AO9" s="4" t="n"/>
-      <c r="AP9" s="2" t="n"/>
-      <c r="AQ9" s="2" t="n"/>
-      <c r="AR9" s="2" t="n"/>
+      <c r="AP9" s="4" t="n"/>
+      <c r="AQ9" s="4" t="n"/>
+      <c r="AR9" s="4" t="n"/>
       <c r="AS9" s="2" t="n"/>
+      <c r="AT9" s="2" t="n"/>
+      <c r="AU9" s="2" t="n"/>
+      <c r="AV9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1551,18 +1610,21 @@
       <c r="AE10" s="2" t="n"/>
       <c r="AF10" s="2" t="n"/>
       <c r="AG10" s="2" t="n"/>
-      <c r="AH10" s="4" t="n"/>
-      <c r="AI10" s="4" t="n"/>
+      <c r="AH10" s="2" t="n"/>
+      <c r="AI10" s="2" t="n"/>
       <c r="AJ10" s="2" t="n"/>
-      <c r="AK10" s="2" t="n"/>
+      <c r="AK10" s="4" t="n"/>
       <c r="AL10" s="4" t="n"/>
-      <c r="AM10" s="4" t="n"/>
-      <c r="AN10" s="4" t="n"/>
+      <c r="AM10" s="2" t="n"/>
+      <c r="AN10" s="2" t="n"/>
       <c r="AO10" s="4" t="n"/>
-      <c r="AP10" s="2" t="n"/>
-      <c r="AQ10" s="2" t="n"/>
-      <c r="AR10" s="2" t="n"/>
+      <c r="AP10" s="4" t="n"/>
+      <c r="AQ10" s="4" t="n"/>
+      <c r="AR10" s="4" t="n"/>
       <c r="AS10" s="2" t="n"/>
+      <c r="AT10" s="2" t="n"/>
+      <c r="AU10" s="2" t="n"/>
+      <c r="AV10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1598,18 +1660,21 @@
       <c r="AE11" s="2" t="n"/>
       <c r="AF11" s="2" t="n"/>
       <c r="AG11" s="2" t="n"/>
-      <c r="AH11" s="4" t="n"/>
-      <c r="AI11" s="4" t="n"/>
+      <c r="AH11" s="2" t="n"/>
+      <c r="AI11" s="2" t="n"/>
       <c r="AJ11" s="2" t="n"/>
-      <c r="AK11" s="2" t="n"/>
+      <c r="AK11" s="4" t="n"/>
       <c r="AL11" s="4" t="n"/>
-      <c r="AM11" s="4" t="n"/>
-      <c r="AN11" s="4" t="n"/>
+      <c r="AM11" s="2" t="n"/>
+      <c r="AN11" s="2" t="n"/>
       <c r="AO11" s="4" t="n"/>
-      <c r="AP11" s="2" t="n"/>
-      <c r="AQ11" s="2" t="n"/>
-      <c r="AR11" s="2" t="n"/>
+      <c r="AP11" s="4" t="n"/>
+      <c r="AQ11" s="4" t="n"/>
+      <c r="AR11" s="4" t="n"/>
       <c r="AS11" s="2" t="n"/>
+      <c r="AT11" s="2" t="n"/>
+      <c r="AU11" s="2" t="n"/>
+      <c r="AV11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1645,18 +1710,21 @@
       <c r="AE12" s="2" t="n"/>
       <c r="AF12" s="2" t="n"/>
       <c r="AG12" s="2" t="n"/>
-      <c r="AH12" s="4" t="n"/>
-      <c r="AI12" s="4" t="n"/>
+      <c r="AH12" s="2" t="n"/>
+      <c r="AI12" s="2" t="n"/>
       <c r="AJ12" s="2" t="n"/>
-      <c r="AK12" s="2" t="n"/>
+      <c r="AK12" s="4" t="n"/>
       <c r="AL12" s="4" t="n"/>
-      <c r="AM12" s="4" t="n"/>
-      <c r="AN12" s="4" t="n"/>
+      <c r="AM12" s="2" t="n"/>
+      <c r="AN12" s="2" t="n"/>
       <c r="AO12" s="4" t="n"/>
-      <c r="AP12" s="2" t="n"/>
-      <c r="AQ12" s="2" t="n"/>
-      <c r="AR12" s="2" t="n"/>
+      <c r="AP12" s="4" t="n"/>
+      <c r="AQ12" s="4" t="n"/>
+      <c r="AR12" s="4" t="n"/>
       <c r="AS12" s="2" t="n"/>
+      <c r="AT12" s="2" t="n"/>
+      <c r="AU12" s="2" t="n"/>
+      <c r="AV12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1692,18 +1760,21 @@
       <c r="AE13" s="2" t="n"/>
       <c r="AF13" s="2" t="n"/>
       <c r="AG13" s="2" t="n"/>
-      <c r="AH13" s="4" t="n"/>
-      <c r="AI13" s="4" t="n"/>
+      <c r="AH13" s="2" t="n"/>
+      <c r="AI13" s="2" t="n"/>
       <c r="AJ13" s="2" t="n"/>
-      <c r="AK13" s="2" t="n"/>
+      <c r="AK13" s="4" t="n"/>
       <c r="AL13" s="4" t="n"/>
-      <c r="AM13" s="4" t="n"/>
-      <c r="AN13" s="4" t="n"/>
+      <c r="AM13" s="2" t="n"/>
+      <c r="AN13" s="2" t="n"/>
       <c r="AO13" s="4" t="n"/>
-      <c r="AP13" s="2" t="n"/>
-      <c r="AQ13" s="2" t="n"/>
-      <c r="AR13" s="2" t="n"/>
+      <c r="AP13" s="4" t="n"/>
+      <c r="AQ13" s="4" t="n"/>
+      <c r="AR13" s="4" t="n"/>
       <c r="AS13" s="2" t="n"/>
+      <c r="AT13" s="2" t="n"/>
+      <c r="AU13" s="2" t="n"/>
+      <c r="AV13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1739,18 +1810,21 @@
       <c r="AE14" s="2" t="n"/>
       <c r="AF14" s="2" t="n"/>
       <c r="AG14" s="2" t="n"/>
-      <c r="AH14" s="4" t="n"/>
-      <c r="AI14" s="4" t="n"/>
+      <c r="AH14" s="2" t="n"/>
+      <c r="AI14" s="2" t="n"/>
       <c r="AJ14" s="2" t="n"/>
-      <c r="AK14" s="2" t="n"/>
+      <c r="AK14" s="4" t="n"/>
       <c r="AL14" s="4" t="n"/>
-      <c r="AM14" s="4" t="n"/>
-      <c r="AN14" s="4" t="n"/>
+      <c r="AM14" s="2" t="n"/>
+      <c r="AN14" s="2" t="n"/>
       <c r="AO14" s="4" t="n"/>
-      <c r="AP14" s="2" t="n"/>
-      <c r="AQ14" s="2" t="n"/>
-      <c r="AR14" s="2" t="n"/>
+      <c r="AP14" s="4" t="n"/>
+      <c r="AQ14" s="4" t="n"/>
+      <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="2" t="n"/>
+      <c r="AT14" s="2" t="n"/>
+      <c r="AU14" s="2" t="n"/>
+      <c r="AV14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1786,18 +1860,21 @@
       <c r="AE15" s="2" t="n"/>
       <c r="AF15" s="2" t="n"/>
       <c r="AG15" s="2" t="n"/>
-      <c r="AH15" s="4" t="n"/>
-      <c r="AI15" s="4" t="n"/>
+      <c r="AH15" s="2" t="n"/>
+      <c r="AI15" s="2" t="n"/>
       <c r="AJ15" s="2" t="n"/>
-      <c r="AK15" s="2" t="n"/>
+      <c r="AK15" s="4" t="n"/>
       <c r="AL15" s="4" t="n"/>
-      <c r="AM15" s="4" t="n"/>
-      <c r="AN15" s="4" t="n"/>
+      <c r="AM15" s="2" t="n"/>
+      <c r="AN15" s="2" t="n"/>
       <c r="AO15" s="4" t="n"/>
-      <c r="AP15" s="2" t="n"/>
-      <c r="AQ15" s="2" t="n"/>
-      <c r="AR15" s="2" t="n"/>
+      <c r="AP15" s="4" t="n"/>
+      <c r="AQ15" s="4" t="n"/>
+      <c r="AR15" s="4" t="n"/>
       <c r="AS15" s="2" t="n"/>
+      <c r="AT15" s="2" t="n"/>
+      <c r="AU15" s="2" t="n"/>
+      <c r="AV15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1833,18 +1910,21 @@
       <c r="AE16" s="2" t="n"/>
       <c r="AF16" s="2" t="n"/>
       <c r="AG16" s="2" t="n"/>
-      <c r="AH16" s="4" t="n"/>
-      <c r="AI16" s="4" t="n"/>
+      <c r="AH16" s="2" t="n"/>
+      <c r="AI16" s="2" t="n"/>
       <c r="AJ16" s="2" t="n"/>
-      <c r="AK16" s="2" t="n"/>
+      <c r="AK16" s="4" t="n"/>
       <c r="AL16" s="4" t="n"/>
-      <c r="AM16" s="4" t="n"/>
-      <c r="AN16" s="4" t="n"/>
+      <c r="AM16" s="2" t="n"/>
+      <c r="AN16" s="2" t="n"/>
       <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="2" t="n"/>
-      <c r="AQ16" s="2" t="n"/>
-      <c r="AR16" s="2" t="n"/>
+      <c r="AP16" s="4" t="n"/>
+      <c r="AQ16" s="4" t="n"/>
+      <c r="AR16" s="4" t="n"/>
       <c r="AS16" s="2" t="n"/>
+      <c r="AT16" s="2" t="n"/>
+      <c r="AU16" s="2" t="n"/>
+      <c r="AV16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1880,18 +1960,21 @@
       <c r="AE17" s="2" t="n"/>
       <c r="AF17" s="2" t="n"/>
       <c r="AG17" s="2" t="n"/>
-      <c r="AH17" s="4" t="n"/>
-      <c r="AI17" s="4" t="n"/>
+      <c r="AH17" s="2" t="n"/>
+      <c r="AI17" s="2" t="n"/>
       <c r="AJ17" s="2" t="n"/>
-      <c r="AK17" s="2" t="n"/>
+      <c r="AK17" s="4" t="n"/>
       <c r="AL17" s="4" t="n"/>
-      <c r="AM17" s="4" t="n"/>
-      <c r="AN17" s="4" t="n"/>
+      <c r="AM17" s="2" t="n"/>
+      <c r="AN17" s="2" t="n"/>
       <c r="AO17" s="4" t="n"/>
-      <c r="AP17" s="2" t="n"/>
-      <c r="AQ17" s="2" t="n"/>
-      <c r="AR17" s="2" t="n"/>
+      <c r="AP17" s="4" t="n"/>
+      <c r="AQ17" s="4" t="n"/>
+      <c r="AR17" s="4" t="n"/>
       <c r="AS17" s="2" t="n"/>
+      <c r="AT17" s="2" t="n"/>
+      <c r="AU17" s="2" t="n"/>
+      <c r="AV17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1927,18 +2010,21 @@
       <c r="AE18" s="2" t="n"/>
       <c r="AF18" s="2" t="n"/>
       <c r="AG18" s="2" t="n"/>
-      <c r="AH18" s="4" t="n"/>
-      <c r="AI18" s="4" t="n"/>
+      <c r="AH18" s="2" t="n"/>
+      <c r="AI18" s="2" t="n"/>
       <c r="AJ18" s="2" t="n"/>
-      <c r="AK18" s="2" t="n"/>
+      <c r="AK18" s="4" t="n"/>
       <c r="AL18" s="4" t="n"/>
-      <c r="AM18" s="4" t="n"/>
-      <c r="AN18" s="4" t="n"/>
+      <c r="AM18" s="2" t="n"/>
+      <c r="AN18" s="2" t="n"/>
       <c r="AO18" s="4" t="n"/>
-      <c r="AP18" s="2" t="n"/>
-      <c r="AQ18" s="2" t="n"/>
-      <c r="AR18" s="2" t="n"/>
+      <c r="AP18" s="4" t="n"/>
+      <c r="AQ18" s="4" t="n"/>
+      <c r="AR18" s="4" t="n"/>
       <c r="AS18" s="2" t="n"/>
+      <c r="AT18" s="2" t="n"/>
+      <c r="AU18" s="2" t="n"/>
+      <c r="AV18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1974,18 +2060,21 @@
       <c r="AE19" s="2" t="n"/>
       <c r="AF19" s="2" t="n"/>
       <c r="AG19" s="2" t="n"/>
-      <c r="AH19" s="4" t="n"/>
-      <c r="AI19" s="4" t="n"/>
+      <c r="AH19" s="2" t="n"/>
+      <c r="AI19" s="2" t="n"/>
       <c r="AJ19" s="2" t="n"/>
-      <c r="AK19" s="2" t="n"/>
+      <c r="AK19" s="4" t="n"/>
       <c r="AL19" s="4" t="n"/>
-      <c r="AM19" s="4" t="n"/>
-      <c r="AN19" s="4" t="n"/>
+      <c r="AM19" s="2" t="n"/>
+      <c r="AN19" s="2" t="n"/>
       <c r="AO19" s="4" t="n"/>
-      <c r="AP19" s="2" t="n"/>
-      <c r="AQ19" s="2" t="n"/>
-      <c r="AR19" s="2" t="n"/>
+      <c r="AP19" s="4" t="n"/>
+      <c r="AQ19" s="4" t="n"/>
+      <c r="AR19" s="4" t="n"/>
       <c r="AS19" s="2" t="n"/>
+      <c r="AT19" s="2" t="n"/>
+      <c r="AU19" s="2" t="n"/>
+      <c r="AV19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -2021,18 +2110,21 @@
       <c r="AE20" s="2" t="n"/>
       <c r="AF20" s="2" t="n"/>
       <c r="AG20" s="2" t="n"/>
-      <c r="AH20" s="4" t="n"/>
-      <c r="AI20" s="4" t="n"/>
+      <c r="AH20" s="2" t="n"/>
+      <c r="AI20" s="2" t="n"/>
       <c r="AJ20" s="2" t="n"/>
-      <c r="AK20" s="2" t="n"/>
+      <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
-      <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="n"/>
+      <c r="AM20" s="2" t="n"/>
+      <c r="AN20" s="2" t="n"/>
       <c r="AO20" s="4" t="n"/>
-      <c r="AP20" s="2" t="n"/>
-      <c r="AQ20" s="2" t="n"/>
-      <c r="AR20" s="2" t="n"/>
+      <c r="AP20" s="4" t="n"/>
+      <c r="AQ20" s="4" t="n"/>
+      <c r="AR20" s="4" t="n"/>
       <c r="AS20" s="2" t="n"/>
+      <c r="AT20" s="2" t="n"/>
+      <c r="AU20" s="2" t="n"/>
+      <c r="AV20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -2068,18 +2160,21 @@
       <c r="AE21" s="2" t="n"/>
       <c r="AF21" s="2" t="n"/>
       <c r="AG21" s="2" t="n"/>
-      <c r="AH21" s="4" t="n"/>
-      <c r="AI21" s="4" t="n"/>
+      <c r="AH21" s="2" t="n"/>
+      <c r="AI21" s="2" t="n"/>
       <c r="AJ21" s="2" t="n"/>
-      <c r="AK21" s="2" t="n"/>
+      <c r="AK21" s="4" t="n"/>
       <c r="AL21" s="4" t="n"/>
-      <c r="AM21" s="4" t="n"/>
-      <c r="AN21" s="4" t="n"/>
+      <c r="AM21" s="2" t="n"/>
+      <c r="AN21" s="2" t="n"/>
       <c r="AO21" s="4" t="n"/>
-      <c r="AP21" s="2" t="n"/>
-      <c r="AQ21" s="2" t="n"/>
-      <c r="AR21" s="2" t="n"/>
+      <c r="AP21" s="4" t="n"/>
+      <c r="AQ21" s="4" t="n"/>
+      <c r="AR21" s="4" t="n"/>
       <c r="AS21" s="2" t="n"/>
+      <c r="AT21" s="2" t="n"/>
+      <c r="AU21" s="2" t="n"/>
+      <c r="AV21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -2115,18 +2210,21 @@
       <c r="AE22" s="2" t="n"/>
       <c r="AF22" s="2" t="n"/>
       <c r="AG22" s="2" t="n"/>
-      <c r="AH22" s="4" t="n"/>
-      <c r="AI22" s="4" t="n"/>
+      <c r="AH22" s="2" t="n"/>
+      <c r="AI22" s="2" t="n"/>
       <c r="AJ22" s="2" t="n"/>
-      <c r="AK22" s="2" t="n"/>
+      <c r="AK22" s="4" t="n"/>
       <c r="AL22" s="4" t="n"/>
-      <c r="AM22" s="4" t="n"/>
-      <c r="AN22" s="4" t="n"/>
+      <c r="AM22" s="2" t="n"/>
+      <c r="AN22" s="2" t="n"/>
       <c r="AO22" s="4" t="n"/>
-      <c r="AP22" s="2" t="n"/>
-      <c r="AQ22" s="2" t="n"/>
-      <c r="AR22" s="2" t="n"/>
+      <c r="AP22" s="4" t="n"/>
+      <c r="AQ22" s="4" t="n"/>
+      <c r="AR22" s="4" t="n"/>
       <c r="AS22" s="2" t="n"/>
+      <c r="AT22" s="2" t="n"/>
+      <c r="AU22" s="2" t="n"/>
+      <c r="AV22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -2162,18 +2260,21 @@
       <c r="AE23" s="2" t="n"/>
       <c r="AF23" s="2" t="n"/>
       <c r="AG23" s="2" t="n"/>
-      <c r="AH23" s="4" t="n"/>
-      <c r="AI23" s="4" t="n"/>
+      <c r="AH23" s="2" t="n"/>
+      <c r="AI23" s="2" t="n"/>
       <c r="AJ23" s="2" t="n"/>
-      <c r="AK23" s="2" t="n"/>
+      <c r="AK23" s="4" t="n"/>
       <c r="AL23" s="4" t="n"/>
-      <c r="AM23" s="4" t="n"/>
-      <c r="AN23" s="4" t="n"/>
+      <c r="AM23" s="2" t="n"/>
+      <c r="AN23" s="2" t="n"/>
       <c r="AO23" s="4" t="n"/>
-      <c r="AP23" s="2" t="n"/>
-      <c r="AQ23" s="2" t="n"/>
-      <c r="AR23" s="2" t="n"/>
+      <c r="AP23" s="4" t="n"/>
+      <c r="AQ23" s="4" t="n"/>
+      <c r="AR23" s="4" t="n"/>
       <c r="AS23" s="2" t="n"/>
+      <c r="AT23" s="2" t="n"/>
+      <c r="AU23" s="2" t="n"/>
+      <c r="AV23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -2209,18 +2310,21 @@
       <c r="AE24" s="2" t="n"/>
       <c r="AF24" s="2" t="n"/>
       <c r="AG24" s="2" t="n"/>
-      <c r="AH24" s="4" t="n"/>
-      <c r="AI24" s="4" t="n"/>
+      <c r="AH24" s="2" t="n"/>
+      <c r="AI24" s="2" t="n"/>
       <c r="AJ24" s="2" t="n"/>
-      <c r="AK24" s="2" t="n"/>
+      <c r="AK24" s="4" t="n"/>
       <c r="AL24" s="4" t="n"/>
-      <c r="AM24" s="4" t="n"/>
-      <c r="AN24" s="4" t="n"/>
+      <c r="AM24" s="2" t="n"/>
+      <c r="AN24" s="2" t="n"/>
       <c r="AO24" s="4" t="n"/>
-      <c r="AP24" s="2" t="n"/>
-      <c r="AQ24" s="2" t="n"/>
-      <c r="AR24" s="2" t="n"/>
+      <c r="AP24" s="4" t="n"/>
+      <c r="AQ24" s="4" t="n"/>
+      <c r="AR24" s="4" t="n"/>
       <c r="AS24" s="2" t="n"/>
+      <c r="AT24" s="2" t="n"/>
+      <c r="AU24" s="2" t="n"/>
+      <c r="AV24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -2256,18 +2360,21 @@
       <c r="AE25" s="2" t="n"/>
       <c r="AF25" s="2" t="n"/>
       <c r="AG25" s="2" t="n"/>
-      <c r="AH25" s="4" t="n"/>
-      <c r="AI25" s="4" t="n"/>
+      <c r="AH25" s="2" t="n"/>
+      <c r="AI25" s="2" t="n"/>
       <c r="AJ25" s="2" t="n"/>
-      <c r="AK25" s="2" t="n"/>
+      <c r="AK25" s="4" t="n"/>
       <c r="AL25" s="4" t="n"/>
-      <c r="AM25" s="4" t="n"/>
-      <c r="AN25" s="4" t="n"/>
+      <c r="AM25" s="2" t="n"/>
+      <c r="AN25" s="2" t="n"/>
       <c r="AO25" s="4" t="n"/>
-      <c r="AP25" s="2" t="n"/>
-      <c r="AQ25" s="2" t="n"/>
-      <c r="AR25" s="2" t="n"/>
+      <c r="AP25" s="4" t="n"/>
+      <c r="AQ25" s="4" t="n"/>
+      <c r="AR25" s="4" t="n"/>
       <c r="AS25" s="2" t="n"/>
+      <c r="AT25" s="2" t="n"/>
+      <c r="AU25" s="2" t="n"/>
+      <c r="AV25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2303,18 +2410,21 @@
       <c r="AE26" s="2" t="n"/>
       <c r="AF26" s="2" t="n"/>
       <c r="AG26" s="2" t="n"/>
-      <c r="AH26" s="4" t="n"/>
-      <c r="AI26" s="4" t="n"/>
+      <c r="AH26" s="2" t="n"/>
+      <c r="AI26" s="2" t="n"/>
       <c r="AJ26" s="2" t="n"/>
-      <c r="AK26" s="2" t="n"/>
+      <c r="AK26" s="4" t="n"/>
       <c r="AL26" s="4" t="n"/>
-      <c r="AM26" s="4" t="n"/>
-      <c r="AN26" s="4" t="n"/>
+      <c r="AM26" s="2" t="n"/>
+      <c r="AN26" s="2" t="n"/>
       <c r="AO26" s="4" t="n"/>
-      <c r="AP26" s="2" t="n"/>
-      <c r="AQ26" s="2" t="n"/>
-      <c r="AR26" s="2" t="n"/>
+      <c r="AP26" s="4" t="n"/>
+      <c r="AQ26" s="4" t="n"/>
+      <c r="AR26" s="4" t="n"/>
       <c r="AS26" s="2" t="n"/>
+      <c r="AT26" s="2" t="n"/>
+      <c r="AU26" s="2" t="n"/>
+      <c r="AV26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2350,18 +2460,21 @@
       <c r="AE27" s="2" t="n"/>
       <c r="AF27" s="2" t="n"/>
       <c r="AG27" s="2" t="n"/>
-      <c r="AH27" s="4" t="n"/>
-      <c r="AI27" s="4" t="n"/>
+      <c r="AH27" s="2" t="n"/>
+      <c r="AI27" s="2" t="n"/>
       <c r="AJ27" s="2" t="n"/>
-      <c r="AK27" s="2" t="n"/>
+      <c r="AK27" s="4" t="n"/>
       <c r="AL27" s="4" t="n"/>
-      <c r="AM27" s="4" t="n"/>
-      <c r="AN27" s="4" t="n"/>
+      <c r="AM27" s="2" t="n"/>
+      <c r="AN27" s="2" t="n"/>
       <c r="AO27" s="4" t="n"/>
-      <c r="AP27" s="2" t="n"/>
-      <c r="AQ27" s="2" t="n"/>
-      <c r="AR27" s="2" t="n"/>
+      <c r="AP27" s="4" t="n"/>
+      <c r="AQ27" s="4" t="n"/>
+      <c r="AR27" s="4" t="n"/>
       <c r="AS27" s="2" t="n"/>
+      <c r="AT27" s="2" t="n"/>
+      <c r="AU27" s="2" t="n"/>
+      <c r="AV27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2397,18 +2510,21 @@
       <c r="AE28" s="2" t="n"/>
       <c r="AF28" s="2" t="n"/>
       <c r="AG28" s="2" t="n"/>
-      <c r="AH28" s="4" t="n"/>
-      <c r="AI28" s="4" t="n"/>
+      <c r="AH28" s="2" t="n"/>
+      <c r="AI28" s="2" t="n"/>
       <c r="AJ28" s="2" t="n"/>
-      <c r="AK28" s="2" t="n"/>
+      <c r="AK28" s="4" t="n"/>
       <c r="AL28" s="4" t="n"/>
-      <c r="AM28" s="4" t="n"/>
-      <c r="AN28" s="4" t="n"/>
+      <c r="AM28" s="2" t="n"/>
+      <c r="AN28" s="2" t="n"/>
       <c r="AO28" s="4" t="n"/>
-      <c r="AP28" s="2" t="n"/>
-      <c r="AQ28" s="2" t="n"/>
-      <c r="AR28" s="2" t="n"/>
+      <c r="AP28" s="4" t="n"/>
+      <c r="AQ28" s="4" t="n"/>
+      <c r="AR28" s="4" t="n"/>
       <c r="AS28" s="2" t="n"/>
+      <c r="AT28" s="2" t="n"/>
+      <c r="AU28" s="2" t="n"/>
+      <c r="AV28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2444,18 +2560,21 @@
       <c r="AE29" s="2" t="n"/>
       <c r="AF29" s="2" t="n"/>
       <c r="AG29" s="2" t="n"/>
-      <c r="AH29" s="4" t="n"/>
-      <c r="AI29" s="4" t="n"/>
+      <c r="AH29" s="2" t="n"/>
+      <c r="AI29" s="2" t="n"/>
       <c r="AJ29" s="2" t="n"/>
-      <c r="AK29" s="2" t="n"/>
+      <c r="AK29" s="4" t="n"/>
       <c r="AL29" s="4" t="n"/>
-      <c r="AM29" s="4" t="n"/>
-      <c r="AN29" s="4" t="n"/>
+      <c r="AM29" s="2" t="n"/>
+      <c r="AN29" s="2" t="n"/>
       <c r="AO29" s="4" t="n"/>
-      <c r="AP29" s="2" t="n"/>
-      <c r="AQ29" s="2" t="n"/>
-      <c r="AR29" s="2" t="n"/>
+      <c r="AP29" s="4" t="n"/>
+      <c r="AQ29" s="4" t="n"/>
+      <c r="AR29" s="4" t="n"/>
       <c r="AS29" s="2" t="n"/>
+      <c r="AT29" s="2" t="n"/>
+      <c r="AU29" s="2" t="n"/>
+      <c r="AV29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2491,18 +2610,21 @@
       <c r="AE30" s="2" t="n"/>
       <c r="AF30" s="2" t="n"/>
       <c r="AG30" s="2" t="n"/>
-      <c r="AH30" s="4" t="n"/>
-      <c r="AI30" s="4" t="n"/>
+      <c r="AH30" s="2" t="n"/>
+      <c r="AI30" s="2" t="n"/>
       <c r="AJ30" s="2" t="n"/>
-      <c r="AK30" s="2" t="n"/>
+      <c r="AK30" s="4" t="n"/>
       <c r="AL30" s="4" t="n"/>
-      <c r="AM30" s="4" t="n"/>
-      <c r="AN30" s="4" t="n"/>
+      <c r="AM30" s="2" t="n"/>
+      <c r="AN30" s="2" t="n"/>
       <c r="AO30" s="4" t="n"/>
-      <c r="AP30" s="2" t="n"/>
-      <c r="AQ30" s="2" t="n"/>
-      <c r="AR30" s="2" t="n"/>
+      <c r="AP30" s="4" t="n"/>
+      <c r="AQ30" s="4" t="n"/>
+      <c r="AR30" s="4" t="n"/>
       <c r="AS30" s="2" t="n"/>
+      <c r="AT30" s="2" t="n"/>
+      <c r="AU30" s="2" t="n"/>
+      <c r="AV30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2538,18 +2660,21 @@
       <c r="AE31" s="2" t="n"/>
       <c r="AF31" s="2" t="n"/>
       <c r="AG31" s="2" t="n"/>
-      <c r="AH31" s="4" t="n"/>
-      <c r="AI31" s="4" t="n"/>
+      <c r="AH31" s="2" t="n"/>
+      <c r="AI31" s="2" t="n"/>
       <c r="AJ31" s="2" t="n"/>
-      <c r="AK31" s="2" t="n"/>
+      <c r="AK31" s="4" t="n"/>
       <c r="AL31" s="4" t="n"/>
-      <c r="AM31" s="4" t="n"/>
-      <c r="AN31" s="4" t="n"/>
+      <c r="AM31" s="2" t="n"/>
+      <c r="AN31" s="2" t="n"/>
       <c r="AO31" s="4" t="n"/>
-      <c r="AP31" s="2" t="n"/>
-      <c r="AQ31" s="2" t="n"/>
-      <c r="AR31" s="2" t="n"/>
+      <c r="AP31" s="4" t="n"/>
+      <c r="AQ31" s="4" t="n"/>
+      <c r="AR31" s="4" t="n"/>
       <c r="AS31" s="2" t="n"/>
+      <c r="AT31" s="2" t="n"/>
+      <c r="AU31" s="2" t="n"/>
+      <c r="AV31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2585,18 +2710,21 @@
       <c r="AE32" s="2" t="n"/>
       <c r="AF32" s="2" t="n"/>
       <c r="AG32" s="2" t="n"/>
-      <c r="AH32" s="4" t="n"/>
-      <c r="AI32" s="4" t="n"/>
+      <c r="AH32" s="2" t="n"/>
+      <c r="AI32" s="2" t="n"/>
       <c r="AJ32" s="2" t="n"/>
-      <c r="AK32" s="2" t="n"/>
+      <c r="AK32" s="4" t="n"/>
       <c r="AL32" s="4" t="n"/>
-      <c r="AM32" s="4" t="n"/>
-      <c r="AN32" s="4" t="n"/>
+      <c r="AM32" s="2" t="n"/>
+      <c r="AN32" s="2" t="n"/>
       <c r="AO32" s="4" t="n"/>
-      <c r="AP32" s="2" t="n"/>
-      <c r="AQ32" s="2" t="n"/>
-      <c r="AR32" s="2" t="n"/>
+      <c r="AP32" s="4" t="n"/>
+      <c r="AQ32" s="4" t="n"/>
+      <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="2" t="n"/>
+      <c r="AT32" s="2" t="n"/>
+      <c r="AU32" s="2" t="n"/>
+      <c r="AV32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2632,18 +2760,21 @@
       <c r="AE33" s="2" t="n"/>
       <c r="AF33" s="2" t="n"/>
       <c r="AG33" s="2" t="n"/>
-      <c r="AH33" s="4" t="n"/>
-      <c r="AI33" s="4" t="n"/>
+      <c r="AH33" s="2" t="n"/>
+      <c r="AI33" s="2" t="n"/>
       <c r="AJ33" s="2" t="n"/>
-      <c r="AK33" s="2" t="n"/>
+      <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
-      <c r="AM33" s="4" t="n"/>
-      <c r="AN33" s="4" t="n"/>
+      <c r="AM33" s="2" t="n"/>
+      <c r="AN33" s="2" t="n"/>
       <c r="AO33" s="4" t="n"/>
-      <c r="AP33" s="2" t="n"/>
-      <c r="AQ33" s="2" t="n"/>
-      <c r="AR33" s="2" t="n"/>
+      <c r="AP33" s="4" t="n"/>
+      <c r="AQ33" s="4" t="n"/>
+      <c r="AR33" s="4" t="n"/>
       <c r="AS33" s="2" t="n"/>
+      <c r="AT33" s="2" t="n"/>
+      <c r="AU33" s="2" t="n"/>
+      <c r="AV33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -2679,18 +2810,21 @@
       <c r="AE34" s="2" t="n"/>
       <c r="AF34" s="2" t="n"/>
       <c r="AG34" s="2" t="n"/>
-      <c r="AH34" s="4" t="n"/>
-      <c r="AI34" s="4" t="n"/>
+      <c r="AH34" s="2" t="n"/>
+      <c r="AI34" s="2" t="n"/>
       <c r="AJ34" s="2" t="n"/>
-      <c r="AK34" s="2" t="n"/>
+      <c r="AK34" s="4" t="n"/>
       <c r="AL34" s="4" t="n"/>
-      <c r="AM34" s="4" t="n"/>
-      <c r="AN34" s="4" t="n"/>
+      <c r="AM34" s="2" t="n"/>
+      <c r="AN34" s="2" t="n"/>
       <c r="AO34" s="4" t="n"/>
-      <c r="AP34" s="2" t="n"/>
-      <c r="AQ34" s="2" t="n"/>
-      <c r="AR34" s="2" t="n"/>
+      <c r="AP34" s="4" t="n"/>
+      <c r="AQ34" s="4" t="n"/>
+      <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="2" t="n"/>
+      <c r="AT34" s="2" t="n"/>
+      <c r="AU34" s="2" t="n"/>
+      <c r="AV34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -2726,18 +2860,21 @@
       <c r="AE35" s="2" t="n"/>
       <c r="AF35" s="2" t="n"/>
       <c r="AG35" s="2" t="n"/>
-      <c r="AH35" s="4" t="n"/>
-      <c r="AI35" s="4" t="n"/>
+      <c r="AH35" s="2" t="n"/>
+      <c r="AI35" s="2" t="n"/>
       <c r="AJ35" s="2" t="n"/>
-      <c r="AK35" s="2" t="n"/>
+      <c r="AK35" s="4" t="n"/>
       <c r="AL35" s="4" t="n"/>
-      <c r="AM35" s="4" t="n"/>
-      <c r="AN35" s="4" t="n"/>
+      <c r="AM35" s="2" t="n"/>
+      <c r="AN35" s="2" t="n"/>
       <c r="AO35" s="4" t="n"/>
-      <c r="AP35" s="2" t="n"/>
-      <c r="AQ35" s="2" t="n"/>
-      <c r="AR35" s="2" t="n"/>
+      <c r="AP35" s="4" t="n"/>
+      <c r="AQ35" s="4" t="n"/>
+      <c r="AR35" s="4" t="n"/>
       <c r="AS35" s="2" t="n"/>
+      <c r="AT35" s="2" t="n"/>
+      <c r="AU35" s="2" t="n"/>
+      <c r="AV35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -2773,18 +2910,21 @@
       <c r="AE36" s="2" t="n"/>
       <c r="AF36" s="2" t="n"/>
       <c r="AG36" s="2" t="n"/>
-      <c r="AH36" s="4" t="n"/>
-      <c r="AI36" s="4" t="n"/>
+      <c r="AH36" s="2" t="n"/>
+      <c r="AI36" s="2" t="n"/>
       <c r="AJ36" s="2" t="n"/>
-      <c r="AK36" s="2" t="n"/>
+      <c r="AK36" s="4" t="n"/>
       <c r="AL36" s="4" t="n"/>
-      <c r="AM36" s="4" t="n"/>
-      <c r="AN36" s="4" t="n"/>
+      <c r="AM36" s="2" t="n"/>
+      <c r="AN36" s="2" t="n"/>
       <c r="AO36" s="4" t="n"/>
-      <c r="AP36" s="2" t="n"/>
-      <c r="AQ36" s="2" t="n"/>
-      <c r="AR36" s="2" t="n"/>
+      <c r="AP36" s="4" t="n"/>
+      <c r="AQ36" s="4" t="n"/>
+      <c r="AR36" s="4" t="n"/>
       <c r="AS36" s="2" t="n"/>
+      <c r="AT36" s="2" t="n"/>
+      <c r="AU36" s="2" t="n"/>
+      <c r="AV36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -2820,18 +2960,21 @@
       <c r="AE37" s="2" t="n"/>
       <c r="AF37" s="2" t="n"/>
       <c r="AG37" s="2" t="n"/>
-      <c r="AH37" s="4" t="n"/>
-      <c r="AI37" s="4" t="n"/>
+      <c r="AH37" s="2" t="n"/>
+      <c r="AI37" s="2" t="n"/>
       <c r="AJ37" s="2" t="n"/>
-      <c r="AK37" s="2" t="n"/>
+      <c r="AK37" s="4" t="n"/>
       <c r="AL37" s="4" t="n"/>
-      <c r="AM37" s="4" t="n"/>
-      <c r="AN37" s="4" t="n"/>
+      <c r="AM37" s="2" t="n"/>
+      <c r="AN37" s="2" t="n"/>
       <c r="AO37" s="4" t="n"/>
-      <c r="AP37" s="2" t="n"/>
-      <c r="AQ37" s="2" t="n"/>
-      <c r="AR37" s="2" t="n"/>
+      <c r="AP37" s="4" t="n"/>
+      <c r="AQ37" s="4" t="n"/>
+      <c r="AR37" s="4" t="n"/>
       <c r="AS37" s="2" t="n"/>
+      <c r="AT37" s="2" t="n"/>
+      <c r="AU37" s="2" t="n"/>
+      <c r="AV37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -2867,18 +3010,21 @@
       <c r="AE38" s="2" t="n"/>
       <c r="AF38" s="2" t="n"/>
       <c r="AG38" s="2" t="n"/>
-      <c r="AH38" s="4" t="n"/>
-      <c r="AI38" s="4" t="n"/>
+      <c r="AH38" s="2" t="n"/>
+      <c r="AI38" s="2" t="n"/>
       <c r="AJ38" s="2" t="n"/>
-      <c r="AK38" s="2" t="n"/>
+      <c r="AK38" s="4" t="n"/>
       <c r="AL38" s="4" t="n"/>
-      <c r="AM38" s="4" t="n"/>
-      <c r="AN38" s="4" t="n"/>
+      <c r="AM38" s="2" t="n"/>
+      <c r="AN38" s="2" t="n"/>
       <c r="AO38" s="4" t="n"/>
-      <c r="AP38" s="2" t="n"/>
-      <c r="AQ38" s="2" t="n"/>
-      <c r="AR38" s="2" t="n"/>
+      <c r="AP38" s="4" t="n"/>
+      <c r="AQ38" s="4" t="n"/>
+      <c r="AR38" s="4" t="n"/>
       <c r="AS38" s="2" t="n"/>
+      <c r="AT38" s="2" t="n"/>
+      <c r="AU38" s="2" t="n"/>
+      <c r="AV38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -2914,18 +3060,21 @@
       <c r="AE39" s="2" t="n"/>
       <c r="AF39" s="2" t="n"/>
       <c r="AG39" s="2" t="n"/>
-      <c r="AH39" s="4" t="n"/>
-      <c r="AI39" s="4" t="n"/>
+      <c r="AH39" s="2" t="n"/>
+      <c r="AI39" s="2" t="n"/>
       <c r="AJ39" s="2" t="n"/>
-      <c r="AK39" s="2" t="n"/>
+      <c r="AK39" s="4" t="n"/>
       <c r="AL39" s="4" t="n"/>
-      <c r="AM39" s="4" t="n"/>
-      <c r="AN39" s="4" t="n"/>
+      <c r="AM39" s="2" t="n"/>
+      <c r="AN39" s="2" t="n"/>
       <c r="AO39" s="4" t="n"/>
-      <c r="AP39" s="2" t="n"/>
-      <c r="AQ39" s="2" t="n"/>
-      <c r="AR39" s="2" t="n"/>
+      <c r="AP39" s="4" t="n"/>
+      <c r="AQ39" s="4" t="n"/>
+      <c r="AR39" s="4" t="n"/>
       <c r="AS39" s="2" t="n"/>
+      <c r="AT39" s="2" t="n"/>
+      <c r="AU39" s="2" t="n"/>
+      <c r="AV39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2961,18 +3110,21 @@
       <c r="AE40" s="2" t="n"/>
       <c r="AF40" s="2" t="n"/>
       <c r="AG40" s="2" t="n"/>
-      <c r="AH40" s="4" t="n"/>
-      <c r="AI40" s="4" t="n"/>
+      <c r="AH40" s="2" t="n"/>
+      <c r="AI40" s="2" t="n"/>
       <c r="AJ40" s="2" t="n"/>
-      <c r="AK40" s="2" t="n"/>
+      <c r="AK40" s="4" t="n"/>
       <c r="AL40" s="4" t="n"/>
-      <c r="AM40" s="4" t="n"/>
-      <c r="AN40" s="4" t="n"/>
+      <c r="AM40" s="2" t="n"/>
+      <c r="AN40" s="2" t="n"/>
       <c r="AO40" s="4" t="n"/>
-      <c r="AP40" s="2" t="n"/>
-      <c r="AQ40" s="2" t="n"/>
-      <c r="AR40" s="2" t="n"/>
+      <c r="AP40" s="4" t="n"/>
+      <c r="AQ40" s="4" t="n"/>
+      <c r="AR40" s="4" t="n"/>
       <c r="AS40" s="2" t="n"/>
+      <c r="AT40" s="2" t="n"/>
+      <c r="AU40" s="2" t="n"/>
+      <c r="AV40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -3008,18 +3160,21 @@
       <c r="AE41" s="2" t="n"/>
       <c r="AF41" s="2" t="n"/>
       <c r="AG41" s="2" t="n"/>
-      <c r="AH41" s="4" t="n"/>
-      <c r="AI41" s="4" t="n"/>
+      <c r="AH41" s="2" t="n"/>
+      <c r="AI41" s="2" t="n"/>
       <c r="AJ41" s="2" t="n"/>
-      <c r="AK41" s="2" t="n"/>
+      <c r="AK41" s="4" t="n"/>
       <c r="AL41" s="4" t="n"/>
-      <c r="AM41" s="4" t="n"/>
-      <c r="AN41" s="4" t="n"/>
+      <c r="AM41" s="2" t="n"/>
+      <c r="AN41" s="2" t="n"/>
       <c r="AO41" s="4" t="n"/>
-      <c r="AP41" s="2" t="n"/>
-      <c r="AQ41" s="2" t="n"/>
-      <c r="AR41" s="2" t="n"/>
+      <c r="AP41" s="4" t="n"/>
+      <c r="AQ41" s="4" t="n"/>
+      <c r="AR41" s="4" t="n"/>
       <c r="AS41" s="2" t="n"/>
+      <c r="AT41" s="2" t="n"/>
+      <c r="AU41" s="2" t="n"/>
+      <c r="AV41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -3055,18 +3210,21 @@
       <c r="AE42" s="2" t="n"/>
       <c r="AF42" s="2" t="n"/>
       <c r="AG42" s="2" t="n"/>
-      <c r="AH42" s="4" t="n"/>
-      <c r="AI42" s="4" t="n"/>
+      <c r="AH42" s="2" t="n"/>
+      <c r="AI42" s="2" t="n"/>
       <c r="AJ42" s="2" t="n"/>
-      <c r="AK42" s="2" t="n"/>
+      <c r="AK42" s="4" t="n"/>
       <c r="AL42" s="4" t="n"/>
-      <c r="AM42" s="4" t="n"/>
-      <c r="AN42" s="4" t="n"/>
+      <c r="AM42" s="2" t="n"/>
+      <c r="AN42" s="2" t="n"/>
       <c r="AO42" s="4" t="n"/>
-      <c r="AP42" s="2" t="n"/>
-      <c r="AQ42" s="2" t="n"/>
-      <c r="AR42" s="2" t="n"/>
+      <c r="AP42" s="4" t="n"/>
+      <c r="AQ42" s="4" t="n"/>
+      <c r="AR42" s="4" t="n"/>
       <c r="AS42" s="2" t="n"/>
+      <c r="AT42" s="2" t="n"/>
+      <c r="AU42" s="2" t="n"/>
+      <c r="AV42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -3102,18 +3260,21 @@
       <c r="AE43" s="2" t="n"/>
       <c r="AF43" s="2" t="n"/>
       <c r="AG43" s="2" t="n"/>
-      <c r="AH43" s="4" t="n"/>
-      <c r="AI43" s="4" t="n"/>
+      <c r="AH43" s="2" t="n"/>
+      <c r="AI43" s="2" t="n"/>
       <c r="AJ43" s="2" t="n"/>
-      <c r="AK43" s="2" t="n"/>
+      <c r="AK43" s="4" t="n"/>
       <c r="AL43" s="4" t="n"/>
-      <c r="AM43" s="4" t="n"/>
-      <c r="AN43" s="4" t="n"/>
+      <c r="AM43" s="2" t="n"/>
+      <c r="AN43" s="2" t="n"/>
       <c r="AO43" s="4" t="n"/>
-      <c r="AP43" s="2" t="n"/>
-      <c r="AQ43" s="2" t="n"/>
-      <c r="AR43" s="2" t="n"/>
+      <c r="AP43" s="4" t="n"/>
+      <c r="AQ43" s="4" t="n"/>
+      <c r="AR43" s="4" t="n"/>
       <c r="AS43" s="2" t="n"/>
+      <c r="AT43" s="2" t="n"/>
+      <c r="AU43" s="2" t="n"/>
+      <c r="AV43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -3149,18 +3310,21 @@
       <c r="AE44" s="2" t="n"/>
       <c r="AF44" s="2" t="n"/>
       <c r="AG44" s="2" t="n"/>
-      <c r="AH44" s="4" t="n"/>
-      <c r="AI44" s="4" t="n"/>
+      <c r="AH44" s="2" t="n"/>
+      <c r="AI44" s="2" t="n"/>
       <c r="AJ44" s="2" t="n"/>
-      <c r="AK44" s="2" t="n"/>
+      <c r="AK44" s="4" t="n"/>
       <c r="AL44" s="4" t="n"/>
-      <c r="AM44" s="4" t="n"/>
-      <c r="AN44" s="4" t="n"/>
+      <c r="AM44" s="2" t="n"/>
+      <c r="AN44" s="2" t="n"/>
       <c r="AO44" s="4" t="n"/>
-      <c r="AP44" s="2" t="n"/>
-      <c r="AQ44" s="2" t="n"/>
-      <c r="AR44" s="2" t="n"/>
+      <c r="AP44" s="4" t="n"/>
+      <c r="AQ44" s="4" t="n"/>
+      <c r="AR44" s="4" t="n"/>
       <c r="AS44" s="2" t="n"/>
+      <c r="AT44" s="2" t="n"/>
+      <c r="AU44" s="2" t="n"/>
+      <c r="AV44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -3196,18 +3360,21 @@
       <c r="AE45" s="2" t="n"/>
       <c r="AF45" s="2" t="n"/>
       <c r="AG45" s="2" t="n"/>
-      <c r="AH45" s="4" t="n"/>
-      <c r="AI45" s="4" t="n"/>
+      <c r="AH45" s="2" t="n"/>
+      <c r="AI45" s="2" t="n"/>
       <c r="AJ45" s="2" t="n"/>
-      <c r="AK45" s="2" t="n"/>
+      <c r="AK45" s="4" t="n"/>
       <c r="AL45" s="4" t="n"/>
-      <c r="AM45" s="4" t="n"/>
-      <c r="AN45" s="4" t="n"/>
+      <c r="AM45" s="2" t="n"/>
+      <c r="AN45" s="2" t="n"/>
       <c r="AO45" s="4" t="n"/>
-      <c r="AP45" s="2" t="n"/>
-      <c r="AQ45" s="2" t="n"/>
-      <c r="AR45" s="2" t="n"/>
+      <c r="AP45" s="4" t="n"/>
+      <c r="AQ45" s="4" t="n"/>
+      <c r="AR45" s="4" t="n"/>
       <c r="AS45" s="2" t="n"/>
+      <c r="AT45" s="2" t="n"/>
+      <c r="AU45" s="2" t="n"/>
+      <c r="AV45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -3243,18 +3410,21 @@
       <c r="AE46" s="2" t="n"/>
       <c r="AF46" s="2" t="n"/>
       <c r="AG46" s="2" t="n"/>
-      <c r="AH46" s="4" t="n"/>
-      <c r="AI46" s="4" t="n"/>
+      <c r="AH46" s="2" t="n"/>
+      <c r="AI46" s="2" t="n"/>
       <c r="AJ46" s="2" t="n"/>
-      <c r="AK46" s="2" t="n"/>
+      <c r="AK46" s="4" t="n"/>
       <c r="AL46" s="4" t="n"/>
-      <c r="AM46" s="4" t="n"/>
-      <c r="AN46" s="4" t="n"/>
+      <c r="AM46" s="2" t="n"/>
+      <c r="AN46" s="2" t="n"/>
       <c r="AO46" s="4" t="n"/>
-      <c r="AP46" s="2" t="n"/>
-      <c r="AQ46" s="2" t="n"/>
-      <c r="AR46" s="2" t="n"/>
+      <c r="AP46" s="4" t="n"/>
+      <c r="AQ46" s="4" t="n"/>
+      <c r="AR46" s="4" t="n"/>
       <c r="AS46" s="2" t="n"/>
+      <c r="AT46" s="2" t="n"/>
+      <c r="AU46" s="2" t="n"/>
+      <c r="AV46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -3290,18 +3460,21 @@
       <c r="AE47" s="2" t="n"/>
       <c r="AF47" s="2" t="n"/>
       <c r="AG47" s="2" t="n"/>
-      <c r="AH47" s="4" t="n"/>
-      <c r="AI47" s="4" t="n"/>
+      <c r="AH47" s="2" t="n"/>
+      <c r="AI47" s="2" t="n"/>
       <c r="AJ47" s="2" t="n"/>
-      <c r="AK47" s="2" t="n"/>
+      <c r="AK47" s="4" t="n"/>
       <c r="AL47" s="4" t="n"/>
-      <c r="AM47" s="4" t="n"/>
-      <c r="AN47" s="4" t="n"/>
+      <c r="AM47" s="2" t="n"/>
+      <c r="AN47" s="2" t="n"/>
       <c r="AO47" s="4" t="n"/>
-      <c r="AP47" s="2" t="n"/>
-      <c r="AQ47" s="2" t="n"/>
-      <c r="AR47" s="2" t="n"/>
+      <c r="AP47" s="4" t="n"/>
+      <c r="AQ47" s="4" t="n"/>
+      <c r="AR47" s="4" t="n"/>
       <c r="AS47" s="2" t="n"/>
+      <c r="AT47" s="2" t="n"/>
+      <c r="AU47" s="2" t="n"/>
+      <c r="AV47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -3337,18 +3510,21 @@
       <c r="AE48" s="2" t="n"/>
       <c r="AF48" s="2" t="n"/>
       <c r="AG48" s="2" t="n"/>
-      <c r="AH48" s="4" t="n"/>
-      <c r="AI48" s="4" t="n"/>
+      <c r="AH48" s="2" t="n"/>
+      <c r="AI48" s="2" t="n"/>
       <c r="AJ48" s="2" t="n"/>
-      <c r="AK48" s="2" t="n"/>
+      <c r="AK48" s="4" t="n"/>
       <c r="AL48" s="4" t="n"/>
-      <c r="AM48" s="4" t="n"/>
-      <c r="AN48" s="4" t="n"/>
+      <c r="AM48" s="2" t="n"/>
+      <c r="AN48" s="2" t="n"/>
       <c r="AO48" s="4" t="n"/>
-      <c r="AP48" s="2" t="n"/>
-      <c r="AQ48" s="2" t="n"/>
-      <c r="AR48" s="2" t="n"/>
+      <c r="AP48" s="4" t="n"/>
+      <c r="AQ48" s="4" t="n"/>
+      <c r="AR48" s="4" t="n"/>
       <c r="AS48" s="2" t="n"/>
+      <c r="AT48" s="2" t="n"/>
+      <c r="AU48" s="2" t="n"/>
+      <c r="AV48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -3384,18 +3560,21 @@
       <c r="AE49" s="2" t="n"/>
       <c r="AF49" s="2" t="n"/>
       <c r="AG49" s="2" t="n"/>
-      <c r="AH49" s="4" t="n"/>
-      <c r="AI49" s="4" t="n"/>
+      <c r="AH49" s="2" t="n"/>
+      <c r="AI49" s="2" t="n"/>
       <c r="AJ49" s="2" t="n"/>
-      <c r="AK49" s="2" t="n"/>
+      <c r="AK49" s="4" t="n"/>
       <c r="AL49" s="4" t="n"/>
-      <c r="AM49" s="4" t="n"/>
-      <c r="AN49" s="4" t="n"/>
+      <c r="AM49" s="2" t="n"/>
+      <c r="AN49" s="2" t="n"/>
       <c r="AO49" s="4" t="n"/>
-      <c r="AP49" s="2" t="n"/>
-      <c r="AQ49" s="2" t="n"/>
-      <c r="AR49" s="2" t="n"/>
+      <c r="AP49" s="4" t="n"/>
+      <c r="AQ49" s="4" t="n"/>
+      <c r="AR49" s="4" t="n"/>
       <c r="AS49" s="2" t="n"/>
+      <c r="AT49" s="2" t="n"/>
+      <c r="AU49" s="2" t="n"/>
+      <c r="AV49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -3431,18 +3610,21 @@
       <c r="AE50" s="2" t="n"/>
       <c r="AF50" s="2" t="n"/>
       <c r="AG50" s="2" t="n"/>
-      <c r="AH50" s="4" t="n"/>
-      <c r="AI50" s="4" t="n"/>
+      <c r="AH50" s="2" t="n"/>
+      <c r="AI50" s="2" t="n"/>
       <c r="AJ50" s="2" t="n"/>
-      <c r="AK50" s="2" t="n"/>
+      <c r="AK50" s="4" t="n"/>
       <c r="AL50" s="4" t="n"/>
-      <c r="AM50" s="4" t="n"/>
-      <c r="AN50" s="4" t="n"/>
+      <c r="AM50" s="2" t="n"/>
+      <c r="AN50" s="2" t="n"/>
       <c r="AO50" s="4" t="n"/>
-      <c r="AP50" s="2" t="n"/>
-      <c r="AQ50" s="2" t="n"/>
-      <c r="AR50" s="2" t="n"/>
+      <c r="AP50" s="4" t="n"/>
+      <c r="AQ50" s="4" t="n"/>
+      <c r="AR50" s="4" t="n"/>
       <c r="AS50" s="2" t="n"/>
+      <c r="AT50" s="2" t="n"/>
+      <c r="AU50" s="2" t="n"/>
+      <c r="AV50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -3478,18 +3660,21 @@
       <c r="AE51" s="2" t="n"/>
       <c r="AF51" s="2" t="n"/>
       <c r="AG51" s="2" t="n"/>
-      <c r="AH51" s="4" t="n"/>
-      <c r="AI51" s="4" t="n"/>
+      <c r="AH51" s="2" t="n"/>
+      <c r="AI51" s="2" t="n"/>
       <c r="AJ51" s="2" t="n"/>
-      <c r="AK51" s="2" t="n"/>
+      <c r="AK51" s="4" t="n"/>
       <c r="AL51" s="4" t="n"/>
-      <c r="AM51" s="4" t="n"/>
-      <c r="AN51" s="4" t="n"/>
+      <c r="AM51" s="2" t="n"/>
+      <c r="AN51" s="2" t="n"/>
       <c r="AO51" s="4" t="n"/>
-      <c r="AP51" s="2" t="n"/>
-      <c r="AQ51" s="2" t="n"/>
-      <c r="AR51" s="2" t="n"/>
+      <c r="AP51" s="4" t="n"/>
+      <c r="AQ51" s="4" t="n"/>
+      <c r="AR51" s="4" t="n"/>
       <c r="AS51" s="2" t="n"/>
+      <c r="AT51" s="2" t="n"/>
+      <c r="AU51" s="2" t="n"/>
+      <c r="AV51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -3525,18 +3710,21 @@
       <c r="AE52" s="2" t="n"/>
       <c r="AF52" s="2" t="n"/>
       <c r="AG52" s="2" t="n"/>
-      <c r="AH52" s="4" t="n"/>
-      <c r="AI52" s="4" t="n"/>
+      <c r="AH52" s="2" t="n"/>
+      <c r="AI52" s="2" t="n"/>
       <c r="AJ52" s="2" t="n"/>
-      <c r="AK52" s="2" t="n"/>
+      <c r="AK52" s="4" t="n"/>
       <c r="AL52" s="4" t="n"/>
-      <c r="AM52" s="4" t="n"/>
-      <c r="AN52" s="4" t="n"/>
+      <c r="AM52" s="2" t="n"/>
+      <c r="AN52" s="2" t="n"/>
       <c r="AO52" s="4" t="n"/>
-      <c r="AP52" s="2" t="n"/>
-      <c r="AQ52" s="2" t="n"/>
-      <c r="AR52" s="2" t="n"/>
+      <c r="AP52" s="4" t="n"/>
+      <c r="AQ52" s="4" t="n"/>
+      <c r="AR52" s="4" t="n"/>
       <c r="AS52" s="2" t="n"/>
+      <c r="AT52" s="2" t="n"/>
+      <c r="AU52" s="2" t="n"/>
+      <c r="AV52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -3572,18 +3760,21 @@
       <c r="AE53" s="2" t="n"/>
       <c r="AF53" s="2" t="n"/>
       <c r="AG53" s="2" t="n"/>
-      <c r="AH53" s="4" t="n"/>
-      <c r="AI53" s="4" t="n"/>
+      <c r="AH53" s="2" t="n"/>
+      <c r="AI53" s="2" t="n"/>
       <c r="AJ53" s="2" t="n"/>
-      <c r="AK53" s="2" t="n"/>
+      <c r="AK53" s="4" t="n"/>
       <c r="AL53" s="4" t="n"/>
-      <c r="AM53" s="4" t="n"/>
-      <c r="AN53" s="4" t="n"/>
+      <c r="AM53" s="2" t="n"/>
+      <c r="AN53" s="2" t="n"/>
       <c r="AO53" s="4" t="n"/>
-      <c r="AP53" s="2" t="n"/>
-      <c r="AQ53" s="2" t="n"/>
-      <c r="AR53" s="2" t="n"/>
+      <c r="AP53" s="4" t="n"/>
+      <c r="AQ53" s="4" t="n"/>
+      <c r="AR53" s="4" t="n"/>
       <c r="AS53" s="2" t="n"/>
+      <c r="AT53" s="2" t="n"/>
+      <c r="AU53" s="2" t="n"/>
+      <c r="AV53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -3619,18 +3810,21 @@
       <c r="AE54" s="2" t="n"/>
       <c r="AF54" s="2" t="n"/>
       <c r="AG54" s="2" t="n"/>
-      <c r="AH54" s="4" t="n"/>
-      <c r="AI54" s="4" t="n"/>
+      <c r="AH54" s="2" t="n"/>
+      <c r="AI54" s="2" t="n"/>
       <c r="AJ54" s="2" t="n"/>
-      <c r="AK54" s="2" t="n"/>
+      <c r="AK54" s="4" t="n"/>
       <c r="AL54" s="4" t="n"/>
-      <c r="AM54" s="4" t="n"/>
-      <c r="AN54" s="4" t="n"/>
+      <c r="AM54" s="2" t="n"/>
+      <c r="AN54" s="2" t="n"/>
       <c r="AO54" s="4" t="n"/>
-      <c r="AP54" s="2" t="n"/>
-      <c r="AQ54" s="2" t="n"/>
-      <c r="AR54" s="2" t="n"/>
+      <c r="AP54" s="4" t="n"/>
+      <c r="AQ54" s="4" t="n"/>
+      <c r="AR54" s="4" t="n"/>
       <c r="AS54" s="2" t="n"/>
+      <c r="AT54" s="2" t="n"/>
+      <c r="AU54" s="2" t="n"/>
+      <c r="AV54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -3666,18 +3860,21 @@
       <c r="AE55" s="2" t="n"/>
       <c r="AF55" s="2" t="n"/>
       <c r="AG55" s="2" t="n"/>
-      <c r="AH55" s="4" t="n"/>
-      <c r="AI55" s="4" t="n"/>
+      <c r="AH55" s="2" t="n"/>
+      <c r="AI55" s="2" t="n"/>
       <c r="AJ55" s="2" t="n"/>
-      <c r="AK55" s="2" t="n"/>
+      <c r="AK55" s="4" t="n"/>
       <c r="AL55" s="4" t="n"/>
-      <c r="AM55" s="4" t="n"/>
-      <c r="AN55" s="4" t="n"/>
+      <c r="AM55" s="2" t="n"/>
+      <c r="AN55" s="2" t="n"/>
       <c r="AO55" s="4" t="n"/>
-      <c r="AP55" s="2" t="n"/>
-      <c r="AQ55" s="2" t="n"/>
-      <c r="AR55" s="2" t="n"/>
+      <c r="AP55" s="4" t="n"/>
+      <c r="AQ55" s="4" t="n"/>
+      <c r="AR55" s="4" t="n"/>
       <c r="AS55" s="2" t="n"/>
+      <c r="AT55" s="2" t="n"/>
+      <c r="AU55" s="2" t="n"/>
+      <c r="AV55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -3713,18 +3910,21 @@
       <c r="AE56" s="2" t="n"/>
       <c r="AF56" s="2" t="n"/>
       <c r="AG56" s="2" t="n"/>
-      <c r="AH56" s="4" t="n"/>
-      <c r="AI56" s="4" t="n"/>
+      <c r="AH56" s="2" t="n"/>
+      <c r="AI56" s="2" t="n"/>
       <c r="AJ56" s="2" t="n"/>
-      <c r="AK56" s="2" t="n"/>
+      <c r="AK56" s="4" t="n"/>
       <c r="AL56" s="4" t="n"/>
-      <c r="AM56" s="4" t="n"/>
-      <c r="AN56" s="4" t="n"/>
+      <c r="AM56" s="2" t="n"/>
+      <c r="AN56" s="2" t="n"/>
       <c r="AO56" s="4" t="n"/>
-      <c r="AP56" s="2" t="n"/>
-      <c r="AQ56" s="2" t="n"/>
-      <c r="AR56" s="2" t="n"/>
+      <c r="AP56" s="4" t="n"/>
+      <c r="AQ56" s="4" t="n"/>
+      <c r="AR56" s="4" t="n"/>
       <c r="AS56" s="2" t="n"/>
+      <c r="AT56" s="2" t="n"/>
+      <c r="AU56" s="2" t="n"/>
+      <c r="AV56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -3760,18 +3960,21 @@
       <c r="AE57" s="2" t="n"/>
       <c r="AF57" s="2" t="n"/>
       <c r="AG57" s="2" t="n"/>
-      <c r="AH57" s="4" t="n"/>
-      <c r="AI57" s="4" t="n"/>
+      <c r="AH57" s="2" t="n"/>
+      <c r="AI57" s="2" t="n"/>
       <c r="AJ57" s="2" t="n"/>
-      <c r="AK57" s="2" t="n"/>
+      <c r="AK57" s="4" t="n"/>
       <c r="AL57" s="4" t="n"/>
-      <c r="AM57" s="4" t="n"/>
-      <c r="AN57" s="4" t="n"/>
+      <c r="AM57" s="2" t="n"/>
+      <c r="AN57" s="2" t="n"/>
       <c r="AO57" s="4" t="n"/>
-      <c r="AP57" s="2" t="n"/>
-      <c r="AQ57" s="2" t="n"/>
-      <c r="AR57" s="2" t="n"/>
+      <c r="AP57" s="4" t="n"/>
+      <c r="AQ57" s="4" t="n"/>
+      <c r="AR57" s="4" t="n"/>
       <c r="AS57" s="2" t="n"/>
+      <c r="AT57" s="2" t="n"/>
+      <c r="AU57" s="2" t="n"/>
+      <c r="AV57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -3807,18 +4010,21 @@
       <c r="AE58" s="2" t="n"/>
       <c r="AF58" s="2" t="n"/>
       <c r="AG58" s="2" t="n"/>
-      <c r="AH58" s="4" t="n"/>
-      <c r="AI58" s="4" t="n"/>
+      <c r="AH58" s="2" t="n"/>
+      <c r="AI58" s="2" t="n"/>
       <c r="AJ58" s="2" t="n"/>
-      <c r="AK58" s="2" t="n"/>
+      <c r="AK58" s="4" t="n"/>
       <c r="AL58" s="4" t="n"/>
-      <c r="AM58" s="4" t="n"/>
-      <c r="AN58" s="4" t="n"/>
+      <c r="AM58" s="2" t="n"/>
+      <c r="AN58" s="2" t="n"/>
       <c r="AO58" s="4" t="n"/>
-      <c r="AP58" s="2" t="n"/>
-      <c r="AQ58" s="2" t="n"/>
-      <c r="AR58" s="2" t="n"/>
+      <c r="AP58" s="4" t="n"/>
+      <c r="AQ58" s="4" t="n"/>
+      <c r="AR58" s="4" t="n"/>
       <c r="AS58" s="2" t="n"/>
+      <c r="AT58" s="2" t="n"/>
+      <c r="AU58" s="2" t="n"/>
+      <c r="AV58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -3854,18 +4060,21 @@
       <c r="AE59" s="2" t="n"/>
       <c r="AF59" s="2" t="n"/>
       <c r="AG59" s="2" t="n"/>
-      <c r="AH59" s="4" t="n"/>
-      <c r="AI59" s="4" t="n"/>
+      <c r="AH59" s="2" t="n"/>
+      <c r="AI59" s="2" t="n"/>
       <c r="AJ59" s="2" t="n"/>
-      <c r="AK59" s="2" t="n"/>
+      <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
-      <c r="AM59" s="4" t="n"/>
-      <c r="AN59" s="4" t="n"/>
+      <c r="AM59" s="2" t="n"/>
+      <c r="AN59" s="2" t="n"/>
       <c r="AO59" s="4" t="n"/>
-      <c r="AP59" s="2" t="n"/>
-      <c r="AQ59" s="2" t="n"/>
-      <c r="AR59" s="2" t="n"/>
+      <c r="AP59" s="4" t="n"/>
+      <c r="AQ59" s="4" t="n"/>
+      <c r="AR59" s="4" t="n"/>
       <c r="AS59" s="2" t="n"/>
+      <c r="AT59" s="2" t="n"/>
+      <c r="AU59" s="2" t="n"/>
+      <c r="AV59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -3901,31 +4110,34 @@
       <c r="AE60" s="2" t="n"/>
       <c r="AF60" s="2" t="n"/>
       <c r="AG60" s="2" t="n"/>
-      <c r="AH60" s="4" t="n"/>
-      <c r="AI60" s="4" t="n"/>
+      <c r="AH60" s="2" t="n"/>
+      <c r="AI60" s="2" t="n"/>
       <c r="AJ60" s="2" t="n"/>
-      <c r="AK60" s="2" t="n"/>
+      <c r="AK60" s="4" t="n"/>
       <c r="AL60" s="4" t="n"/>
-      <c r="AM60" s="4" t="n"/>
-      <c r="AN60" s="4" t="n"/>
+      <c r="AM60" s="2" t="n"/>
+      <c r="AN60" s="2" t="n"/>
       <c r="AO60" s="4" t="n"/>
-      <c r="AP60" s="2" t="n"/>
-      <c r="AQ60" s="2" t="n"/>
-      <c r="AR60" s="2" t="n"/>
+      <c r="AP60" s="4" t="n"/>
+      <c r="AQ60" s="4" t="n"/>
+      <c r="AR60" s="4" t="n"/>
       <c r="AS60" s="2" t="n"/>
+      <c r="AT60" s="2" t="n"/>
+      <c r="AU60" s="2" t="n"/>
+      <c r="AV60" s="2" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AI2:AI60">
+  <conditionalFormatting sqref="AL2:AL60">
     <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND(AI2&lt;&gt;"",NOT(OR(UPPER(AI2)="DC",AND(ISNUMBER(AI2),AI2&gt;=1,AI2&lt;=IF(AH2="",10,MIN(10,400/AH2))))))</formula>
+      <formula>AND(AL2&lt;&gt;"",NOT(OR(UPPER(AL2)="DC",AND(ISNUMBER(AL2),AL2&gt;=1,AL2&lt;=IF(AK2="",10,MIN(10,400/AK2))))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM60">
+  <conditionalFormatting sqref="AP2:AP60">
     <cfRule type="expression" priority="2" dxfId="0">
-      <formula>AND(ISNUMBER(AM2),ISNUMBER(AL2),OR(AM2&lt;1.6*AL2,AM2&gt;100-1.6*AL2))</formula>
+      <formula>AND(ISNUMBER(AP2),ISNUMBER(AO2),OR(AP2&lt;1.6*AO2,AP2&gt;100-1.6*AO2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="45">
+  <dataValidations count="48">
     <dataValidation sqref="A2:A60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행" promptTitle="#" prompt="단계 번호(1,2,3…). 대기(delay) 행은 비움. test = 장비를 쓰지 않고 process_time(분)만큼 기다리기만 하는 시험 행" type="custom">
       <formula1>IF(ISNUMBER(A2),AND(A2&gt;=1,A2&lt;=999,A2=INT(A2)),LOWER(A2)="test")</formula1>
     </dataValidation>
@@ -3984,92 +4196,92 @@
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="S2:S60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G1 사용" promptTitle="gun1 [T/F]" prompt="T=G1 사용" type="list">
+    <dataValidation sqref="V2:V60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G1 사용" promptTitle="gun1 [T/F]" prompt="T=G1 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G2 사용" promptTitle="gun2 [T/F]" prompt="T=G2 사용" type="list">
+    <dataValidation sqref="W2:W60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G2 사용" promptTitle="gun2 [T/F]" prompt="T=G2 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G3 사용" promptTitle="gun3 [T/F]" prompt="T=G3 사용" type="list">
+    <dataValidation sqref="X2:X60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=G3 사용" promptTitle="gun3 [T/F]" prompt="T=G3 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G1 타겟 이름(재고 DB 이름과 동일하게)" promptTitle="G1 Target" prompt="G1 타겟 이름(재고 DB 이름과 동일하게)" type="textLength" errorStyle="information">
+    <dataValidation sqref="Y2:Y60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G1 타겟 이름(재고 DB 이름과 동일하게)" promptTitle="G1 Target" prompt="G1 타겟 이름(재고 DB 이름과 동일하게)" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="W2:W60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G2 타겟 이름" promptTitle="G2 Target" prompt="G2 타겟 이름" type="textLength" errorStyle="information">
+    <dataValidation sqref="Z2:Z60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G2 타겟 이름" promptTitle="G2 Target" prompt="G2 타겟 이름" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="X2:X60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G3 타겟 이름" promptTitle="G3 Target" prompt="G3 타겟 이름" type="textLength" errorStyle="information">
+    <dataValidation sqref="AA2:AA60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="G3 타겟 이름" promptTitle="G3 Target" prompt="G3 타겟 이름" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="Y2:Y60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])" promptTitle="power_select [T/F]" prompt="RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])" type="list">
+    <dataValidation sqref="AB2:AB60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])" promptTitle="power_select [T/F]" prompt="RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="Z2:Z60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=DC1 연속 파워 사용" promptTitle="use_dc_power [T/F]" prompt="T=DC1 연속 파워 사용" type="list">
+    <dataValidation sqref="AC2:AC60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=DC1 연속 파워 사용" promptTitle="use_dc_power [T/F]" prompt="T=DC1 연속 파워 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA2:AA60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC1 설정 파워(&gt;0)" promptTitle="dc_power [W]" prompt="DC1 설정 파워(&gt;0)" type="decimal">
+    <dataValidation sqref="AD2:AD60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC1 설정 파워(&gt;0)" promptTitle="dc_power [W]" prompt="DC1 설정 파워(&gt;0)" type="decimal">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="AB2:AB60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" promptTitle="use_dc_power2 [T/F]" prompt="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" type="list">
+    <dataValidation sqref="AE2:AE60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" promptTitle="use_dc_power2 [T/F]" prompt="DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력" type="list">
       <formula1>"F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 비워 두세요" promptTitle="dc_power2 [W]" prompt="DC2 폐지 — 비워 두세요" type="decimal">
+    <dataValidation sqref="AF2:AF60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC2 폐지 — 비워 두세요" promptTitle="dc_power2 [W]" prompt="DC2 폐지 — 비워 두세요" type="decimal">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="AD2:AD60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=RF 연속 파워 사용" promptTitle="use_rf_power [T/F]" prompt="T=RF 연속 파워 사용" type="list">
+    <dataValidation sqref="AG2:AG60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=RF 연속 파워 사용" promptTitle="use_rf_power [T/F]" prompt="T=RF 연속 파워 사용" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AE2:AE60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF 설정 파워(&gt;0)" promptTitle="rf_power [W]" prompt="RF 설정 파워(&gt;0)" type="decimal">
+    <dataValidation sqref="AH2:AH60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF 설정 파워(&gt;0)" promptTitle="rf_power [W]" prompt="RF 설정 파워(&gt;0)" type="decimal">
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="AF2:AF60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨" promptTitle="use_dc_pulse [T/F]" prompt="T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨" type="list">
+    <dataValidation sqref="AI2:AI60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨" promptTitle="use_dc_pulse [T/F]" prompt="T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG2:AG60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)" promptTitle="dc_pulse_power [W]" prompt="DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)" type="decimal">
+    <dataValidation sqref="AJ2:AJ60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)" promptTitle="dc_pulse_power [W]" prompt="DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)" type="decimal">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="AH2:AH60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지" promptTitle="dc_pulse_freq [kHz]" prompt="정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지" type="whole">
+    <dataValidation sqref="AK2:AK60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지" promptTitle="dc_pulse_freq [kHz]" prompt="정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지" type="whole">
       <formula1>20</formula1>
       <formula2>150</formula2>
     </dataValidation>
-    <dataValidation sqref="AI2:AI60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지" promptTitle="dc_pulse_off_time [us]" prompt="Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지" type="custom">
-      <formula1>OR(UPPER(AI2)="DC",AND(ISNUMBER(AI2),AI2&gt;=1,AI2&lt;=IF(AH2="",10,MIN(10,400/AH2))))</formula1>
+    <dataValidation sqref="AL2:AL60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지" promptTitle="dc_pulse_off_time [us]" prompt="Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지" type="custom">
+      <formula1>OR(UPPER(AL2)="DC",AND(ISNUMBER(AL2),AL2&gt;=1,AL2&lt;=IF(AK2="",10,MIN(10,400/AK2))))</formula1>
     </dataValidation>
-    <dataValidation sqref="AJ2:AJ60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨" promptTitle="use_rf_pulse [T/F]" prompt="T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨" type="list">
+    <dataValidation sqref="AM2:AM60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨" promptTitle="use_rf_pulse [T/F]" prompt="T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AK2:AK60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF Pulse 설정 파워 1~1000" promptTitle="rf_pulse_power [W]" prompt="RF Pulse 설정 파워 1~1000" type="decimal">
+    <dataValidation sqref="AN2:AN60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RF Pulse 설정 파워 1~1000" promptTitle="rf_pulse_power [W]" prompt="RF Pulse 설정 파워 1~1000" type="decimal">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="AL2:AL60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지" promptTitle="rf_pulse_freq [kHz]" prompt="0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지" type="decimal">
+    <dataValidation sqref="AO2:AO60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지" promptTitle="rf_pulse_freq [kHz]" prompt="0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지" type="decimal">
       <formula1>0.001</formula1>
       <formula2>30</formula2>
     </dataValidation>
-    <dataValidation sqref="AM2:AM60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)" promptTitle="rf_pulse_duty_cycle [%]" prompt="정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)" type="whole">
+    <dataValidation sqref="AP2:AP60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)" promptTitle="rf_pulse_duty_cycle [%]" prompt="정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)" type="whole">
       <formula1>1</formula1>
       <formula2>99</formula2>
     </dataValidation>
-    <dataValidation sqref="AP2:AP60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" promptTitle="use_heater [T/F]" prompt="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" type="list">
+    <dataValidation sqref="AS2:AS60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" promptTitle="use_heater [T/F]" prompt="T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가" type="list">
       <formula1>"T,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="AQ2:AQ60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" promptTitle="heater_temp [°C]" prompt="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" type="decimal">
+    <dataValidation sqref="AT2:AT60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" promptTitle="heater_temp [°C]" prompt="목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수" type="decimal">
       <formula1>1</formula1>
       <formula2>900</formula2>
     </dataValidation>
-    <dataValidation sqref="AR2:AR60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)" promptTitle="heater_ramp [°C/min]" prompt="RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)" type="decimal">
+    <dataValidation sqref="AU2:AU60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)" promptTitle="heater_ramp [°C/min]" prompt="RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)" type="decimal">
       <formula1>0.1</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation sqref="AS2:AS60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" promptTitle="heater_soak [min]" prompt="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" type="decimal">
+    <dataValidation sqref="AV2:AV60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" promptTitle="heater_soak [min]" prompt="도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)" type="decimal">
       <formula1>0</formula1>
       <formula2>480</formula2>
     </dataValidation>
@@ -4081,12 +4293,24 @@
       <formula1>0</formula1>
       <formula2>100000</formula2>
     </dataValidation>
-    <dataValidation sqref="AN2:AN60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)" promptTitle="power_change_time" prompt="중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)" type="textLength" operator="between">
+    <dataValidation sqref="AQ2:AQ60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)" promptTitle="power_change_time" prompt="중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)" type="textLength" operator="between">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation sqref="AO2:AO60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용" promptTitle="change_power_value [W]" prompt="그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용" type="decimal" operator="greaterThan">
+    <dataValidation sqref="AR2:AR60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용" promptTitle="change_power_value [W]" prompt="그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용" type="decimal" operator="greaterThan">
       <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="Thickness 모드에서만 사용. 두께 모니터 tooling(10.0~399). 값이 있으면 레시피 값, 비우면 Factor 팝업의 chuck×건 tooling. Time 모드(thickness 비움)는 무시" promptTitle="tooling [%]" prompt="Thickness 모드에서만 사용. 두께 모니터 tooling(10.0~399). 값이 있으면 레시피 값, 비우면 Factor 팝업의 chuck×건 tooling. Time 모드(thickness 비움)는 무시" type="decimal" operator="between">
+      <formula1>10</formula1>
+      <formula2>399</formula2>
+    </dataValidation>
+    <dataValidation sqref="T2:T60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="Thickness 모드에서만 사용. 재료 밀도(0.500~99.99). 값이 있으면 레시피 값, 비우면 Factor 팝업에서 고른 건 재료의 density. Time 모드는 무시" promptTitle="density [g/cm3]" prompt="Thickness 모드에서만 사용. 재료 밀도(0.500~99.99). 값이 있으면 레시피 값, 비우면 Factor 팝업에서 고른 건 재료의 density. Time 모드는 무시" type="decimal" operator="between">
+      <formula1>0.5</formula1>
+      <formula2>99.99</formula2>
+    </dataValidation>
+    <dataValidation sqref="U2:U60" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="허용 범위 밖" error="Thickness 모드에서만 사용. 재료 Z-factor(0.100~9.999). 값이 있으면 레시피 값, 비우면 Factor 팝업에서 고른 건 재료의 Z. Time 모드는 무시" promptTitle="z_factor" prompt="Thickness 모드에서만 사용. 재료 Z-factor(0.100~9.999). 값이 있으면 레시피 값, 비우면 Factor 팝업에서 고른 건 재료의 Z. Time 모드는 무시" type="decimal" operator="between">
+      <formula1>0.1</formula1>
+      <formula2>9.999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4101,7 +4325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" style="9" min="1" max="1"/>
@@ -4474,70 +4698,82 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="25.5" customHeight="1" s="9">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>gun1</t>
+          <t>tooling</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>T/F</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>T=G1 사용</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n"/>
-    </row>
-    <row r="24">
+          <t>Thickness 모드에서만 사용. 두께 모니터 tooling(10.0~399). 값이 있으면 레시피 값, 비우면 Factor 팝업의 chuck×건 tooling. Time 모드(thickness 비움)는 무시</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>값마다 레시피 우선 · 비우면 Factor 팝업 값. 레시피·Factor 둘 다 없으면 E845 로 시작 거부. 범위 밖은 파일 로드 때 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25.5" customHeight="1" s="9">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>gun2</t>
+          <t>density</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>T/F</t>
+          <t>g/cm3</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>T=G2 사용</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n"/>
-    </row>
-    <row r="25">
+          <t>Thickness 모드에서만 사용. 재료 밀도(0.500~99.99). 값이 있으면 레시피 값, 비우면 Factor 팝업에서 고른 건 재료의 density. Time 모드는 무시</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>값마다 레시피 우선 · 비우면 Factor 팝업 재료 값(density·Z 각각 따로). 범위 밖은 파일 로드 때 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25.5" customHeight="1" s="9">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>gun3</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>T/F</t>
-        </is>
-      </c>
+          <t>z_factor</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>T=G3 사용</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n"/>
+          <t>Thickness 모드에서만 사용. 재료 Z-factor(0.100~9.999). 값이 있으면 레시피 값, 비우면 Factor 팝업에서 고른 건 재료의 Z. Time 모드는 무시</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>값마다 레시피 우선 · 비우면 Factor 팝업 재료 값. density·z_factor 를 모두 쓰면 Factor 에서 건 재료를 고르지 않아도 됨. 범위 밖은 파일 로드 때 거부</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>G1 Target</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
+          <t>gun1</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>G1 타겟 이름(재고 DB 이름과 동일하게)</t>
+          <t>T=G1 사용</t>
         </is>
       </c>
       <c r="D26" s="7" t="n"/>
@@ -4545,13 +4781,17 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>G2 Target</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
+          <t>gun2</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>G2 타겟 이름</t>
+          <t>T=G2 사용</t>
         </is>
       </c>
       <c r="D27" s="7" t="n"/>
@@ -4559,13 +4799,17 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>G3 Target</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n"/>
+          <t>gun3</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>G3 타겟 이름</t>
+          <t>T=G3 사용</t>
         </is>
       </c>
       <c r="D28" s="7" t="n"/>
@@ -4573,39 +4817,27 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>power_select</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>T/F</t>
-        </is>
-      </c>
+          <t>G1 Target</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>DC Pulse와 함께 T이면 과전류(8/25 사고)</t>
-        </is>
-      </c>
+          <t>G1 타겟 이름(재고 DB 이름과 동일하게)</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>use_dc_power</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>T/F</t>
-        </is>
-      </c>
+          <t>G2 Target</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n"/>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>T=DC1 연속 파워 사용</t>
+          <t>G2 타겟 이름</t>
         </is>
       </c>
       <c r="D30" s="7" t="n"/>
@@ -4613,17 +4845,13 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>dc_power</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
+          <t>G3 Target</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>DC1 설정 파워(&gt;0)</t>
+          <t>G3 타겟 이름</t>
         </is>
       </c>
       <c r="D31" s="7" t="n"/>
@@ -4631,7 +4859,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>use_dc_power2</t>
+          <t>power_select</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -4641,29 +4869,29 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력</t>
+          <t>RF 전용 경로 릴레이. DC Pulse 사용 시 반드시 F ([EL-026])</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>2026-10 CH2 히터 추가로 D/A CH3 를 히터가 씀</t>
+          <t>DC Pulse와 함께 T이면 과전류(8/25 사고)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>dc_power2</t>
+          <t>use_dc_power</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>T/F</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>DC2 폐지 — 비워 두세요</t>
+          <t>T=DC1 연속 파워 사용</t>
         </is>
       </c>
       <c r="D33" s="7" t="n"/>
@@ -4671,17 +4899,17 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>use_rf_power</t>
+          <t>dc_power</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>T/F</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>T=RF 연속 파워 사용</t>
+          <t>DC1 설정 파워(&gt;0)</t>
         </is>
       </c>
       <c r="D34" s="7" t="n"/>
@@ -4689,35 +4917,39 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>rf_power</t>
+          <t>use_dc_power2</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>T/F</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>RF 설정 파워(&gt;0)</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n"/>
+          <t>DC2 폐지 — 쓰지 않음(F 또는 공란). D/A CH3 는 CH2 히터 출력</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10 CH2 히터 추가로 D/A CH3 를 히터가 씀</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>use_dc_pulse</t>
+          <t>dc_power2</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>T/F</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨</t>
+          <t>DC2 폐지 — 비워 두세요</t>
         </is>
       </c>
       <c r="D36" s="7" t="n"/>
@@ -4725,17 +4957,17 @@
     <row r="37" s="9">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>dc_pulse_power</t>
+          <t>use_rf_power</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>T/F</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)</t>
+          <t>T=RF 연속 파워 사용</t>
         </is>
       </c>
       <c r="D37" s="7" t="n"/>
@@ -4743,61 +4975,53 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>dc_pulse_freq</t>
+          <t>rf_power</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>kHz</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>20 kHz → Off 최대 10.0 / 50 kHz → 8.0 / 100 kHz → 4.0 µs</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="25.5" customHeight="1" s="9">
+          <t>RF 설정 파워(&gt;0)</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n"/>
+    </row>
+    <row r="39" s="9">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>dc_pulse_off_time</t>
+          <t>use_dc_pulse</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>us</t>
+          <t>T/F</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>EnerPulse는 듀티가 아니라 Off Time(µs)을 설정값으로 씀. 듀티 = 1 − Off×kHz/1000</t>
-        </is>
-      </c>
+          <t>T=DC Pulse(EnerPulse) 사용. F이면 아래 3칸은 무시됨</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>use_rf_pulse</t>
+          <t>dc_pulse_power</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>T/F</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨</t>
+          <t>DC Pulse 설정 파워 1~1000 (settings DCP_MAX_POWER_W)</t>
         </is>
       </c>
       <c r="D40" s="7" t="n"/>
@@ -4805,184 +5029,246 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>rf_pulse_power</t>
+          <t>dc_pulse_freq</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>kHz</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>RF Pulse 설정 파워 1~1000</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="n"/>
-    </row>
-    <row r="42" s="9">
+          <t>정수 20~150 (EnerPulse 매뉴얼 p.12). 공란=장비 값 유지</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>20 kHz → Off 최대 10.0 / 50 kHz → 8.0 / 100 kHz → 4.0 µs</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25.5" customHeight="1" s="9">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>rf_pulse_freq</t>
+          <t>dc_pulse_off_time</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>kHz</t>
+          <t>us</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="n"/>
+          <t>Off Time 1.0~10.0 µs, 상한=MIN(10, 400/kHz) (매뉴얼 p.13 그림3). 'DC'=DC 모드, 공란=장비 값 유지</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>EnerPulse는 듀티가 아니라 Off Time(µs)을 설정값으로 씀. 듀티 = 1 − Off×kHz/1000</t>
+        </is>
+      </c>
     </row>
     <row r="43" s="9">
       <c r="A43" s="7" t="inlineStr">
         <is>
+          <t>use_rf_pulse</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>T=RF Pulse(CESAR) 사용. F이면 아래 3칸은 무시됨</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n"/>
+    </row>
+    <row r="44" s="9">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>rf_pulse_power</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>RF Pulse 설정 파워 1~1000</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n"/>
+    </row>
+    <row r="45" s="9">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>rf_pulse_freq</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>kHz</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>0.001~30 (CESAR 1310 사양 1 Hz~30 kHz). 공란=장비 값 유지</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n"/>
+    </row>
+    <row r="46" s="9">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
           <t>rf_pulse_duty_cycle</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>정수 1~99. On/Off 각 16 µs 이상 → 1.6×kHz ≤ duty ≤ 100−1.6×kHz 권장(CESAR 4-75)</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>범위 밖이면 장비가 CSR 51로 거부함</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="25.5" customHeight="1" s="9">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>power_change_time</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="n"/>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Shutter Delay 안 변경은 Thickness 모드에서도 가능. 메인 구간 안이면 E844 로 시작 거부</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="25.5" customHeight="1" s="9">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>change_power_value</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>DC/RF Pulse 를 동시에 쓰면 DC 우선</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="25.5" customHeight="1" s="9">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>use_heater</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>T/F</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>다음 공정 행도 use_heater=T 면 히터를 켠 채 넘어가고, 아니면 공정이 끝날 때 끈다</t>
         </is>
       </c>
     </row>
     <row r="47" ht="25.5" customHeight="1" s="9">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>heater_temp</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>°C</t>
-        </is>
-      </c>
+          <t>power_change_time</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n"/>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수</t>
+          <t>중간 펄스 전력 변경 시점(Shutter Delay 시작부터). 단위를 붙여 쓰세요: 90s / 10m / 1h30m (단위 없는 숫자는 '초'로 읽음). 공란 = 변경 없음. change_power_value 와 함께 입력. Thickness 모드에서는 메인 구간 안 시점을 쓸 수 없음(E844)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>목표 ±2°C 안에 60초 머물면 도달로 본다(HEATER_SOAK_*). 그 뒤 대기는 heater_soak</t>
+          <t>Shutter Delay 안 변경은 Thickness 모드에서도 가능. 메인 구간 안이면 E844 로 시작 거부</t>
         </is>
       </c>
     </row>
     <row r="48" ht="25.5" customHeight="1" s="9">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>heater_ramp</t>
+          <t>change_power_value</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>°C/min</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)</t>
+          <t>그 시점에 바꿀 펄스 전력(&gt;0). power_change_time 과 함께 입력, 공란 = 변경 없음. 쓰는 펄스(DC/RF Pulse)에 적용</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>목표 20°C 앞부터 감속해 1°C/min 로 도착(HEATER_APPROACH_*)</t>
+          <t>DC/RF Pulse 를 동시에 쓰면 DC 우선</t>
         </is>
       </c>
     </row>
     <row r="49" ht="25.5" customHeight="1" s="9">
       <c r="A49" s="7" t="inlineStr">
         <is>
+          <t>use_heater</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>T/F</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>T=CH2 히터 사용 — 공정 시작 전에 heater_temp 까지 올리고(RAMP) 도달 뒤 heater_soak 만큼 기다린(SOAK) 뒤 공정, 공정 중에도 유지. CH1 은 사용 불가</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>다음 공정 행도 use_heater=T 면 히터를 켠 채 넘어가고, 아니면 공정이 끝날 때 끈다</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="25.5" customHeight="1" s="9">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>heater_temp</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>목표 온도 1~900 (HEATER_MAX_TEMP·HEATER_SV_LIMIT_C). use_heater=T 이면 필수</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>목표 ±2°C 안에 60초 머물면 도달로 본다(HEATER_SOAK_*). 그 뒤 대기는 heater_soak</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="25.5" customHeight="1" s="9">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>heater_ramp</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>°C/min</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>RAMP 속도 0.1~60. 공란 = 기본값(HEATER_RAMP_RATE_C_PER_MIN, 6)</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>목표 20°C 앞부터 감속해 1°C/min 로 도착(HEATER_APPROACH_*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="25.5" customHeight="1" s="9">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
           <t>heater_soak</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>min</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>도달 뒤 SOAK 0~480분 — 시간만 센다(온도는 PID 가 계속 맞추고, 흔들려도 다시 세지 않음). 공란 = SOAK 없음(도달 확인 뒤 바로 공정)</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>SOAK 중에도 히터 이상·꺼짐·출력 무응답/끊김이면 공정 중단. ±2°C 밖으로 나가면 로그·도달 카드에 기록만. 행마다 따로 적용</t>
         </is>
